--- a/data/MetalliCan/pre_cleaned_data/energy_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/energy_df.xlsx
@@ -64,6 +64,33 @@
     <t>needs_factor</t>
   </si>
   <si>
+    <t>TECH-599152a0-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-599152a0-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-599152a0-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-599152a0-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-6b4800fe-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-6b4800fe-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-6b4800fe-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-6b4800fe-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-6b4800fe-2023.0-5.0</t>
+  </si>
+  <si>
     <t>TECH-857b7b89-2023.0-1.0</t>
   </si>
   <si>
@@ -88,6 +115,342 @@
     <t>TECH-857b7b89-2023.0-8.0</t>
   </si>
   <si>
+    <t>TECH-8eb8be0d-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-8eb8be0d-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-8eb8be0d-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-8eb8be0d-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-8eb8be0d-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-8eb8be0d-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-8eb8be0d-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-11.0</t>
+  </si>
+  <si>
+    <t>TECH-aa76f6f2-2023.0-13.0</t>
+  </si>
+  <si>
+    <t>TECH-ed23117f-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-ed23117f-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-ed23117f-nan-nan</t>
+  </si>
+  <si>
+    <t>TECH-ed23117f-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-ed23117f-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-ed23117f-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-b64bae7a-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-b64bae7a-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-b64bae7a-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-b64bae7a-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-b64bae7a-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-dd723db4-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-8b0264c9-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-8b0264c9-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-8b0264c9-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-8b0264c9-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-10.0</t>
+  </si>
+  <si>
+    <t>TECH-0aadf28f-2023.0-12.0</t>
+  </si>
+  <si>
+    <t>TECH-1f126a43-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-1f126a43-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-1f126a43-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-1f126a43-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-1f126a43-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-1f126a43-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-687b8c8d-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-687b8c8d-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-687b8c8d-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-687b8c8d-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-687b8c8d-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-6e9be24e-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-6e9be24e-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-7607a50e-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-7607a50e-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-7607a50e-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-7607a50e-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-7607a50e-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-7607a50e-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-7f050560-2024.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-7f050560-2024.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-7f050560-2024.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-7f050560-2024.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-7f050560-2024.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-a3c56a83-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-a3c56a83-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-a3c56a83-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-aeafbb59-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-aeafbb59-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-aeafbb59-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-aeafbb59-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-aeafbb59-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-cb85213a-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-cb85213a-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-cb85213a-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-cb85213a-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-cb85213a-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-12.0</t>
+  </si>
+  <si>
+    <t>TECH-fefeaee4-2023.0-14.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-7.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-8.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-9.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-12.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-17.0</t>
+  </si>
+  <si>
+    <t>TECH-02884fb5-2023.0-18.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-6dc537e6-2023.0-11.0</t>
+  </si>
+  <si>
+    <t>TECH-9de9bb0d-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-9de9bb0d-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-9de9bb0d-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-9de9bb0d-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-9de9bb0d-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-b86f7d07-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-b86f7d07-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-b86f7d07-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-b86f7d07-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-c0660aec-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-c0660aec-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-c0660aec-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-c0660aec-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-c0660aec-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-e51eda66-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-e51eda66-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-e51eda66-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-e51eda66-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-e51eda66-2023.0-5.0</t>
+  </si>
+  <si>
     <t>TECH-e7e6a960-2023.0-1.0</t>
   </si>
   <si>
@@ -103,130 +466,25 @@
     <t>TECH-e7e6a960-2023.0-5.0</t>
   </si>
   <si>
-    <t>TECH-dd723db4-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-b86f7d07-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-b86f7d07-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-b86f7d07-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-b86f7d07-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-599152a0-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-599152a0-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-599152a0-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-599152a0-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-aeafbb59-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-aeafbb59-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-aeafbb59-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-aeafbb59-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-aeafbb59-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-cb85213a-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-cb85213a-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-cb85213a-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-cb85213a-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-cb85213a-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-6dc537e6-2023.0-11.0</t>
-  </si>
-  <si>
-    <t>TECH-6b4800fe-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-6b4800fe-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-6b4800fe-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-6b4800fe-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-6b4800fe-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-c0660aec-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-c0660aec-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-c0660aec-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-c0660aec-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-c0660aec-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-6e9be24e-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-6e9be24e-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-687b8c8d-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-687b8c8d-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-687b8c8d-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-687b8c8d-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-687b8c8d-2023.0-5.0</t>
+    <t>TECH-f9e41c2a-2023.0-1.0</t>
+  </si>
+  <si>
+    <t>TECH-f9e41c2a-2023.0-2.0</t>
+  </si>
+  <si>
+    <t>TECH-f9e41c2a-2023.0-3.0</t>
+  </si>
+  <si>
+    <t>TECH-f9e41c2a-2023.0-4.0</t>
+  </si>
+  <si>
+    <t>TECH-f9e41c2a-2023.0-5.0</t>
+  </si>
+  <si>
+    <t>TECH-f9e41c2a-2023.0-6.0</t>
+  </si>
+  <si>
+    <t>TECH-f9e41c2a-2023.0-7.0</t>
   </si>
   <si>
     <t>TECH-44857446-2023.0-1.0</t>
@@ -241,84 +499,6 @@
     <t>TECH-44857446-2023.0-4.0</t>
   </si>
   <si>
-    <t>TECH-9de9bb0d-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-9de9bb0d-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-9de9bb0d-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-9de9bb0d-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-9de9bb0d-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-a3c56a83-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-a3c56a83-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-a3c56a83-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-f9e41c2a-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-f9e41c2a-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-f9e41c2a-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-f9e41c2a-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-f9e41c2a-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-f9e41c2a-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-f9e41c2a-2023.0-7.0</t>
-  </si>
-  <si>
-    <t>TECH-e51eda66-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-e51eda66-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-e51eda66-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-e51eda66-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-e51eda66-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-1f126a43-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-1f126a43-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-1f126a43-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-1f126a43-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-1f126a43-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-1f126a43-2023.0-6.0</t>
-  </si>
-  <si>
     <t>TECH-GRP-0a2c0d69-2023.0-1.0</t>
   </si>
   <si>
@@ -337,81 +517,6 @@
     <t>TECH-GRP-0a2c0d69-2023.0-6.0</t>
   </si>
   <si>
-    <t>TECH-8b0264c9-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-8b0264c9-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-8b0264c9-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-8b0264c9-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-ed23117f-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-ed23117f-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-ed23117f-nan-nan</t>
-  </si>
-  <si>
-    <t>TECH-ed23117f-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-ed23117f-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-ed23117f-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-7.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-12.0</t>
-  </si>
-  <si>
-    <t>TECH-fefeaee4-2023.0-14.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-7.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-9.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-11.0</t>
-  </si>
-  <si>
-    <t>TECH-aa76f6f2-2023.0-13.0</t>
-  </si>
-  <si>
     <t>TECH-GRP-0d911886-2023.0-1.0</t>
   </si>
   <si>
@@ -433,72 +538,6 @@
     <t>TECH-GRP-0d911886-2023.0-13.0</t>
   </si>
   <si>
-    <t>TECH-0aadf28f-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023.0-7.0</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023.0-8.0</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023.0-10.0</t>
-  </si>
-  <si>
-    <t>TECH-0aadf28f-2023.0-12.0</t>
-  </si>
-  <si>
-    <t>TECH-8eb8be0d-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-8eb8be0d-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-8eb8be0d-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-8eb8be0d-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-8eb8be0d-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-8eb8be0d-2023.0-6.0</t>
-  </si>
-  <si>
-    <t>TECH-8eb8be0d-2023.0-7.0</t>
-  </si>
-  <si>
-    <t>TECH-7f050560-2024.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-7f050560-2024.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-7f050560-2024.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-7f050560-2024.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-7f050560-2024.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-b64bae7a-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-b64bae7a-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-b64bae7a-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-b64bae7a-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-b64bae7a-2023.0-5.0</t>
-  </si>
-  <si>
     <t>TECH-GRP-14bfbb82-2023.0-1.0</t>
   </si>
   <si>
@@ -547,105 +586,87 @@
     <t>TECH-GRP-147b3123-2023.0-7.0</t>
   </si>
   <si>
-    <t>TECH-02884fb5-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-7.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-8.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-9.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-12.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-17.0</t>
-  </si>
-  <si>
-    <t>TECH-02884fb5-2023.0-18.0</t>
-  </si>
-  <si>
-    <t>TECH-7607a50e-2023.0-1.0</t>
-  </si>
-  <si>
-    <t>TECH-7607a50e-2023.0-2.0</t>
-  </si>
-  <si>
-    <t>TECH-7607a50e-2023.0-3.0</t>
-  </si>
-  <si>
-    <t>TECH-7607a50e-2023.0-4.0</t>
-  </si>
-  <si>
-    <t>TECH-7607a50e-2023.0-5.0</t>
-  </si>
-  <si>
-    <t>TECH-7607a50e-2023.0-6.0</t>
-  </si>
-  <si>
     <t>Energy</t>
   </si>
   <si>
+    <t>Diesel</t>
+  </si>
+  <si>
+    <t>Electricity consumption</t>
+  </si>
+  <si>
+    <t>Gasoline</t>
+  </si>
+  <si>
+    <t>Propane</t>
+  </si>
+  <si>
+    <t>Electricity consumption|Grid electricity</t>
+  </si>
+  <si>
+    <t>Natural gas</t>
+  </si>
+  <si>
     <t>Acetylene</t>
   </si>
   <si>
     <t>Aviation fuel</t>
   </si>
   <si>
-    <t>Diesel</t>
-  </si>
-  <si>
     <t>Electricity consumption|Generated on-site</t>
   </si>
   <si>
-    <t>Electricity consumption|Grid electricity</t>
-  </si>
-  <si>
-    <t>Gasoline</t>
-  </si>
-  <si>
-    <t>Propane</t>
-  </si>
-  <si>
     <t>Used oil</t>
   </si>
   <si>
+    <t>Explosives</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Energy use</t>
+  </si>
+  <si>
     <t>Light Fuel &amp; Gasoline</t>
   </si>
   <si>
-    <t>Natural gas</t>
-  </si>
-  <si>
-    <t>Energy use</t>
+    <t>Electricity consumption|Non-renewable electricity use</t>
+  </si>
+  <si>
+    <t>Non-renewable fuel use</t>
+  </si>
+  <si>
+    <t>Naphta</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>Electricity consumption|Not specified</t>
+  </si>
+  <si>
+    <t>Petrol</t>
+  </si>
+  <si>
+    <t>Biodiesel</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>ANFO</t>
+  </si>
+  <si>
+    <t>Emulsion ANFO</t>
   </si>
   <si>
     <t>Diesel|Mobile equipment</t>
   </si>
   <si>
-    <t>Electricity consumption|Not specified</t>
-  </si>
-  <si>
     <t>Gasoline|Mobile equipment</t>
   </si>
   <si>
-    <t>Electricity consumption</t>
-  </si>
-  <si>
-    <t>Explosives</t>
-  </si>
-  <si>
-    <t>Electricity consumption|Non-renewable electricity use</t>
-  </si>
-  <si>
-    <t>Non-renewable fuel use</t>
-  </si>
-  <si>
-    <t>Petrol</t>
-  </si>
-  <si>
     <t>Diesel|Stationary equipment</t>
   </si>
   <si>
@@ -658,18 +679,6 @@
     <t>Lubricating Oils &amp; Greases</t>
   </si>
   <si>
-    <t>Biodiesel</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>Oil</t>
-  </si>
-  <si>
     <t>Other</t>
   </si>
   <si>
@@ -682,156 +691,147 @@
     <t>Emulsions</t>
   </si>
   <si>
-    <t>ANFO</t>
-  </si>
-  <si>
-    <t>Emulsion ANFO</t>
-  </si>
-  <si>
-    <t>Naphta</t>
+    <t>TJ</t>
   </si>
   <si>
     <t>GJ</t>
   </si>
   <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>MWh</t>
+  </si>
+  <si>
     <t>kWh</t>
   </si>
   <si>
-    <t>MWh</t>
+    <t>kl</t>
+  </si>
+  <si>
+    <t>GWh</t>
+  </si>
+  <si>
+    <t>m3</t>
   </si>
   <si>
     <t>gallons</t>
   </si>
   <si>
-    <t>TJ</t>
-  </si>
-  <si>
-    <t>kl</t>
-  </si>
-  <si>
-    <t>m3</t>
-  </si>
-  <si>
-    <t>GWh</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>kg</t>
+    <t>Share of primary energy source derived from the all group</t>
+  </si>
+  <si>
+    <t>Data initially in tCO2eq; back calculated with emission factors: 74.1kgCO2eq/GJ for diesel, 69.9kgCO2eq/GJ for gasoline, 59.9kgCO2eq/GJ for propane, BC mix 12kgCO2eq/MWh</t>
+  </si>
+  <si>
+    <t>Data initially in tCO2eq; back calculated with emission factors: 74.1kgCO2eq/GJ for diesel, 69.9kgCO2eq/GJ for gasoline, 59.9kgCO2eq/GJ for propane, BC mix 12kgCO2eq/MWh. 62% of electricity come from the grid.</t>
+  </si>
+  <si>
+    <t>Data initially in tCO2eq; back calculated with emission factors: 74.1kgCO2eq/GJ for diesel, 69.9kgCO2eq/GJ for gasoline, 59.9kgCO2eq/GJ for propane, BC mix 12kgCO2eq/MWh, explosives 3.75GJ/tCO2</t>
   </si>
   <si>
     <t>No decomposition per energy type</t>
   </si>
   <si>
-    <t>Share of primary energy source derived from the all group</t>
-  </si>
-  <si>
     <t>Given in MW in the Excel file but does not make sense</t>
   </si>
   <si>
+    <t>Explosives, treated as energy consumption</t>
+  </si>
+  <si>
     <t>Expressed initially in kl</t>
   </si>
   <si>
-    <t>Data initially in tCO2eq; back calculated with emission factors: 74.1kgCO2eq/GJ for diesel, 69.9kgCO2eq/GJ for gasoline, 59.9kgCO2eq/GJ for propane, BC mix 12kgCO2eq/MWh</t>
-  </si>
-  <si>
-    <t>Data initially in tCO2eq; back calculated with emission factors: 74.1kgCO2eq/GJ for diesel, 69.9kgCO2eq/GJ for gasoline, 59.9kgCO2eq/GJ for propane, BC mix 12kgCO2eq/MWh. 62% of electricity come from the grid.</t>
-  </si>
-  <si>
-    <t>Data initially in tCO2eq; back calculated with emission factors: 74.1kgCO2eq/GJ for diesel, 69.9kgCO2eq/GJ for gasoline, 59.9kgCO2eq/GJ for propane, BC mix 12kgCO2eq/MWh, explosives 3.75GJ/tCO2</t>
-  </si>
-  <si>
     <t>Other types are electricity, diesel, natural gas, propane</t>
   </si>
   <si>
-    <t>Explosives, treated as energy consumption</t>
+    <t>BC-MAIN-599152a0</t>
+  </si>
+  <si>
+    <t>BC-MAIN-6b4800fe</t>
   </si>
   <si>
     <t>BC-MAIN-857b7b89</t>
   </si>
   <si>
+    <t>BC-MAIN-8eb8be0d</t>
+  </si>
+  <si>
+    <t>BC-MAIN-aa76f6f2</t>
+  </si>
+  <si>
+    <t>BC-MAIN-ed23117f</t>
+  </si>
+  <si>
+    <t>NL-MAIN-b64bae7a</t>
+  </si>
+  <si>
+    <t>NL-MAIN-dd723db4</t>
+  </si>
+  <si>
+    <t>NU-MAIN-8b0264c9</t>
+  </si>
+  <si>
+    <t>ON-MAIN-0aadf28f</t>
+  </si>
+  <si>
+    <t>ON-MAIN-1f126a43</t>
+  </si>
+  <si>
+    <t>ON-MAIN-687b8c8d</t>
+  </si>
+  <si>
+    <t>ON-MAIN-6e9be24e</t>
+  </si>
+  <si>
+    <t>ON-MAIN-7607a50e</t>
+  </si>
+  <si>
+    <t>ON-MAIN-7f050560</t>
+  </si>
+  <si>
+    <t>ON-MAIN-a3c56a83</t>
+  </si>
+  <si>
+    <t>ON-MAIN-aeafbb59</t>
+  </si>
+  <si>
+    <t>ON-MAIN-cb85213a</t>
+  </si>
+  <si>
+    <t>ON-MAIN-fefeaee4</t>
+  </si>
+  <si>
+    <t>QC-MAIN-02884fb5</t>
+  </si>
+  <si>
+    <t>QC-MAIN-6dc537e6</t>
+  </si>
+  <si>
+    <t>QC-MAIN-9de9bb0d</t>
+  </si>
+  <si>
+    <t>QC-MAIN-b86f7d07</t>
+  </si>
+  <si>
+    <t>QC-MAIN-c0660aec</t>
+  </si>
+  <si>
+    <t>QC-MAIN-e51eda66</t>
+  </si>
+  <si>
     <t>QC-MAIN-e7e6a960</t>
   </si>
   <si>
-    <t>NL-MAIN-dd723db4</t>
-  </si>
-  <si>
-    <t>QC-MAIN-b86f7d07</t>
-  </si>
-  <si>
-    <t>BC-MAIN-599152a0</t>
-  </si>
-  <si>
-    <t>ON-MAIN-aeafbb59</t>
-  </si>
-  <si>
-    <t>ON-MAIN-cb85213a</t>
-  </si>
-  <si>
-    <t>QC-MAIN-6dc537e6</t>
-  </si>
-  <si>
-    <t>BC-MAIN-6b4800fe</t>
-  </si>
-  <si>
-    <t>QC-MAIN-c0660aec</t>
-  </si>
-  <si>
-    <t>ON-MAIN-6e9be24e</t>
-  </si>
-  <si>
-    <t>ON-MAIN-687b8c8d</t>
+    <t>QC-MAIN-f9e41c2a</t>
   </si>
   <si>
     <t>YT-MAIN-44857446</t>
   </si>
   <si>
-    <t>QC-MAIN-9de9bb0d</t>
-  </si>
-  <si>
-    <t>ON-MAIN-a3c56a83</t>
-  </si>
-  <si>
-    <t>QC-MAIN-f9e41c2a</t>
-  </si>
-  <si>
-    <t>QC-MAIN-e51eda66</t>
-  </si>
-  <si>
-    <t>ON-MAIN-1f126a43</t>
-  </si>
-  <si>
-    <t>NU-MAIN-8b0264c9</t>
-  </si>
-  <si>
-    <t>BC-MAIN-ed23117f</t>
-  </si>
-  <si>
-    <t>ON-MAIN-fefeaee4</t>
-  </si>
-  <si>
-    <t>BC-MAIN-aa76f6f2</t>
-  </si>
-  <si>
-    <t>ON-MAIN-0aadf28f</t>
-  </si>
-  <si>
-    <t>BC-MAIN-8eb8be0d</t>
-  </si>
-  <si>
-    <t>ON-MAIN-7f050560</t>
-  </si>
-  <si>
-    <t>NL-MAIN-b64bae7a</t>
-  </si>
-  <si>
-    <t>QC-MAIN-02884fb5</t>
-  </si>
-  <si>
-    <t>ON-MAIN-7607a50e</t>
-  </si>
-  <si>
     <t>GRP-0a2c0d69</t>
   </si>
   <si>
@@ -847,117 +847,117 @@
     <t>GRP-147b3123</t>
   </si>
   <si>
+    <t>CMP-12afc634</t>
+  </si>
+  <si>
+    <t>CMP-e35f138c</t>
+  </si>
+  <si>
     <t>CMP-4a434d72</t>
   </si>
   <si>
+    <t>CMP-d94be190</t>
+  </si>
+  <si>
+    <t>CMP-fa032e20</t>
+  </si>
+  <si>
+    <t>CMP-8a99044e</t>
+  </si>
+  <si>
+    <t>CMP-2da4630a</t>
+  </si>
+  <si>
     <t>CMP-6265c407</t>
   </si>
   <si>
-    <t>CMP-2da4630a</t>
+    <t>CMP-3a4ccc7f</t>
+  </si>
+  <si>
+    <t>CMP-79bcdb91</t>
+  </si>
+  <si>
+    <t>CMP-ca642bce</t>
+  </si>
+  <si>
+    <t>CMP-967076a1</t>
+  </si>
+  <si>
+    <t>CMP-3d2c4955</t>
+  </si>
+  <si>
+    <t>CMP-3d0a95b7</t>
   </si>
   <si>
     <t>CMP-7e360a1f</t>
   </si>
   <si>
-    <t>CMP-12afc634</t>
-  </si>
-  <si>
-    <t>CMP-3d2c4955</t>
-  </si>
-  <si>
-    <t>CMP-e35f138c</t>
-  </si>
-  <si>
-    <t>CMP-79bcdb91</t>
-  </si>
-  <si>
-    <t>CMP-3a4ccc7f</t>
-  </si>
-  <si>
-    <t>CMP-967076a1</t>
-  </si>
-  <si>
     <t>CMP-64d60fd7</t>
   </si>
   <si>
-    <t>CMP-fa032e20</t>
-  </si>
-  <si>
-    <t>CMP-d94be190</t>
-  </si>
-  <si>
-    <t>CMP-ca642bce</t>
-  </si>
-  <si>
-    <t>CMP-8a99044e</t>
-  </si>
-  <si>
     <t>CMP-4a73c5f8</t>
   </si>
   <si>
     <t>CMP-48a36546</t>
   </si>
   <si>
-    <t>CMP-3d0a95b7</t>
+    <t>HudbayMineralsInc_Hudbay-2023-Integrated-Annual-Report-Performance-Data</t>
+  </si>
+  <si>
+    <t>TasekoMinesLimited_ESG_2023</t>
   </si>
   <si>
     <t>NewmontCorporation_2023-Performance-data</t>
   </si>
   <si>
+    <t>NewGoldInc_ESG_data_2023</t>
+  </si>
+  <si>
+    <t>CenterraGoldInc_Data</t>
+  </si>
+  <si>
+    <t>TacoraResourcesInc._SR_2024</t>
+  </si>
+  <si>
+    <t>TacoraResourcesInc._ESG_2024</t>
+  </si>
+  <si>
+    <t>IronOreCompanyofCanadaInc_SR_2023</t>
+  </si>
+  <si>
     <t>AgnicoEagleMinesLimited_2023-Sustainability-Performance_data</t>
   </si>
   <si>
-    <t>IronOreCompanyofCanadaInc_SR_2023</t>
+    <t>AlamosGoldInc_Data_2023</t>
+  </si>
+  <si>
+    <t>BarrickGoldCorporation_Barrick_2023_Performance-Data</t>
+  </si>
+  <si>
+    <t>EvolutionMiningLtd_EVN_FY24-ESG-Performance-Data_web</t>
+  </si>
+  <si>
+    <t>ImpalaCanadaLtd_ESG_2024</t>
+  </si>
+  <si>
+    <t>WesdomeGoldMinesLtd._ESG_data_2023</t>
+  </si>
+  <si>
+    <t>IAMGOLDCorporation_2023_iamgold-esg-performance-data-final_protected</t>
   </si>
   <si>
     <t>HeclaMiningCompany_SR_2023</t>
   </si>
   <si>
-    <t>HudbayMineralsInc_Hudbay-2023-Integrated-Annual-Report-Performance-Data</t>
-  </si>
-  <si>
-    <t>WesdomeGoldMinesLtd._ESG_data_2023</t>
-  </si>
-  <si>
-    <t>TasekoMinesLimited_ESG_2023</t>
-  </si>
-  <si>
-    <t>BarrickGoldCorporation_Barrick_2023_Performance-Data</t>
-  </si>
-  <si>
-    <t>AlamosGoldInc_Data_2023</t>
-  </si>
-  <si>
-    <t>ImpalaCanadaLtd_ESG_2024</t>
-  </si>
-  <si>
     <t>EldoradoGold_ESG_2023</t>
   </si>
   <si>
-    <t>CenterraGoldInc_Data</t>
-  </si>
-  <si>
-    <t>NewGoldInc_ESG_data_2023</t>
-  </si>
-  <si>
-    <t>EvolutionMiningLtd_EVN_FY24-ESG-Performance-Data_web</t>
-  </si>
-  <si>
-    <t>TacoraResourcesInc._SR_2024</t>
-  </si>
-  <si>
-    <t>TacoraResourcesInc._ESG_2024</t>
-  </si>
-  <si>
     <t>SSRMiningInc_ESG_2023</t>
   </si>
   <si>
     <t>PanAmericanSilverCorp_ESG_data_2023</t>
   </si>
   <si>
-    <t>IAMGOLDCorporation_2023_iamgold-esg-performance-data-final_protected</t>
-  </si>
-  <si>
     <t>direct_unit</t>
   </si>
   <si>
@@ -967,34 +967,34 @@
     <t>lhv_factor</t>
   </si>
   <si>
+    <t>tj→MJ factor=1000000.0</t>
+  </si>
+  <si>
     <t>gj→MJ factor=1000.0</t>
   </si>
   <si>
+    <t>diesel MJ/kg=43.0, dens=0.835 kg/L</t>
+  </si>
+  <si>
+    <t>explosives MJ/kg=4.0</t>
+  </si>
+  <si>
+    <t>gasoline MJ/kg=44.0, dens=0.745 kg/L</t>
+  </si>
+  <si>
+    <t>propane MJ/kg=46.4, dens=0.493 kg/L</t>
+  </si>
+  <si>
+    <t>mwh→MJ factor=3600.0</t>
+  </si>
+  <si>
     <t>kwh→MJ factor=3.6</t>
   </si>
   <si>
-    <t>mwh→MJ factor=3600.0</t>
-  </si>
-  <si>
-    <t>diesel MJ/kg=43.0, dens=0.835 kg/L</t>
-  </si>
-  <si>
-    <t>gasoline MJ/kg=44.0, dens=0.745 kg/L</t>
-  </si>
-  <si>
-    <t>propane MJ/kg=46.4, dens=0.493 kg/L</t>
-  </si>
-  <si>
-    <t>tj→MJ factor=1000000.0</t>
+    <t>gwh→MJ factor=3600000.0</t>
   </si>
   <si>
     <t>natural_gas MJ/m3=38.0</t>
-  </si>
-  <si>
-    <t>gwh→MJ factor=3600000.0</t>
-  </si>
-  <si>
-    <t>explosives MJ/kg=4.0</t>
   </si>
   <si>
     <t>MJ</t>
@@ -1425,7 +1425,10 @@
         <v>225</v>
       </c>
       <c r="F2">
-        <v>18.475650648</v>
+        <v>80.95999999999999</v>
+      </c>
+      <c r="G2" t="s">
+        <v>235</v>
       </c>
       <c r="H2" t="s">
         <v>244</v>
@@ -1437,7 +1440,7 @@
         <v>295</v>
       </c>
       <c r="L2">
-        <v>18475.650648</v>
+        <v>80960000</v>
       </c>
       <c r="M2" t="s">
         <v>314</v>
@@ -1469,7 +1472,7 @@
         <v>225</v>
       </c>
       <c r="F3">
-        <v>72676.1107896</v>
+        <v>1968</v>
       </c>
       <c r="H3" t="s">
         <v>244</v>
@@ -1481,7 +1484,7 @@
         <v>295</v>
       </c>
       <c r="L3">
-        <v>72676110.7896</v>
+        <v>1968000000</v>
       </c>
       <c r="M3" t="s">
         <v>314</v>
@@ -1513,7 +1516,10 @@
         <v>225</v>
       </c>
       <c r="F4">
-        <v>287042.447231542</v>
+        <v>0.368</v>
+      </c>
+      <c r="G4" t="s">
+        <v>235</v>
       </c>
       <c r="H4" t="s">
         <v>244</v>
@@ -1525,7 +1531,7 @@
         <v>295</v>
       </c>
       <c r="L4">
-        <v>287042447.2315421</v>
+        <v>368000</v>
       </c>
       <c r="M4" t="s">
         <v>314</v>
@@ -1557,7 +1563,10 @@
         <v>225</v>
       </c>
       <c r="F5">
-        <v>86225.1173956</v>
+        <v>10.12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>235</v>
       </c>
       <c r="H5" t="s">
         <v>244</v>
@@ -1569,7 +1578,7 @@
         <v>295</v>
       </c>
       <c r="L5">
-        <v>86225117.39559999</v>
+        <v>10120000</v>
       </c>
       <c r="M5" t="s">
         <v>314</v>
@@ -1595,31 +1604,31 @@
         <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F6">
-        <v>569009.5848</v>
+        <v>1683653</v>
       </c>
       <c r="H6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L6">
-        <v>569009584.8</v>
+        <v>1683653000</v>
       </c>
       <c r="M6" t="s">
         <v>314</v>
       </c>
       <c r="N6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O6" t="s">
         <v>327</v>
@@ -1639,31 +1648,31 @@
         <v>190</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F7">
-        <v>13568.45</v>
+        <v>1695665</v>
       </c>
       <c r="H7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L7">
-        <v>13568450</v>
+        <v>1695665000</v>
       </c>
       <c r="M7" t="s">
         <v>314</v>
       </c>
       <c r="N7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O7" t="s">
         <v>327</v>
@@ -1683,31 +1692,31 @@
         <v>190</v>
       </c>
       <c r="D8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F8">
-        <v>42071.0413</v>
+        <v>38791</v>
       </c>
       <c r="H8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L8">
-        <v>42071041.3</v>
+        <v>38791000</v>
       </c>
       <c r="M8" t="s">
         <v>314</v>
       </c>
       <c r="N8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O8" t="s">
         <v>327</v>
@@ -1727,31 +1736,31 @@
         <v>190</v>
       </c>
       <c r="D9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F9">
-        <v>2344.0244</v>
+        <v>186977</v>
       </c>
       <c r="H9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L9">
-        <v>2344024.4</v>
+        <v>186977000</v>
       </c>
       <c r="M9" t="s">
         <v>314</v>
       </c>
       <c r="N9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O9" t="s">
         <v>327</v>
@@ -1771,13 +1780,13 @@
         <v>190</v>
       </c>
       <c r="D10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F10">
-        <v>2557832</v>
+        <v>453</v>
       </c>
       <c r="H10" t="s">
         <v>245</v>
@@ -1789,13 +1798,13 @@
         <v>296</v>
       </c>
       <c r="L10">
-        <v>2557832000</v>
+        <v>453000</v>
       </c>
       <c r="M10" t="s">
         <v>314</v>
       </c>
       <c r="N10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O10" t="s">
         <v>327</v>
@@ -1815,25 +1824,25 @@
         <v>190</v>
       </c>
       <c r="D11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E11" t="s">
         <v>226</v>
       </c>
       <c r="F11">
-        <v>674524386</v>
+        <v>18.47565065</v>
       </c>
       <c r="H11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L11">
-        <v>2428287789.6</v>
+        <v>18475.65065</v>
       </c>
       <c r="M11" t="s">
         <v>314</v>
@@ -1859,31 +1868,31 @@
         <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F12">
-        <v>42833</v>
+        <v>72676.11079000001</v>
       </c>
       <c r="H12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L12">
-        <v>42833000</v>
+        <v>72676110.79000001</v>
       </c>
       <c r="M12" t="s">
         <v>314</v>
       </c>
       <c r="N12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O12" t="s">
         <v>327</v>
@@ -1903,31 +1912,31 @@
         <v>190</v>
       </c>
       <c r="D13" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F13">
-        <v>162805</v>
+        <v>287042.4472</v>
       </c>
       <c r="H13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L13">
-        <v>162805000</v>
+        <v>287042447.2</v>
       </c>
       <c r="M13" t="s">
         <v>314</v>
       </c>
       <c r="N13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O13" t="s">
         <v>327</v>
@@ -1947,31 +1956,31 @@
         <v>190</v>
       </c>
       <c r="D14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F14">
-        <v>1463.60937</v>
+        <v>86225.1174</v>
       </c>
       <c r="H14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L14">
-        <v>1463609.37</v>
+        <v>86225117.40000001</v>
       </c>
       <c r="M14" t="s">
         <v>314</v>
       </c>
       <c r="N14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O14" t="s">
         <v>327</v>
@@ -1991,16 +2000,13 @@
         <v>190</v>
       </c>
       <c r="D15" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F15">
-        <v>4145000</v>
-      </c>
-      <c r="G15" t="s">
-        <v>235</v>
+        <v>569009.5848</v>
       </c>
       <c r="H15" t="s">
         <v>246</v>
@@ -2012,13 +2018,13 @@
         <v>297</v>
       </c>
       <c r="L15">
-        <v>14922000000</v>
+        <v>569009584.8</v>
       </c>
       <c r="M15" t="s">
         <v>314</v>
       </c>
       <c r="N15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O15" t="s">
         <v>327</v>
@@ -2038,31 +2044,31 @@
         <v>190</v>
       </c>
       <c r="D16" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F16">
-        <v>2785135</v>
+        <v>13568.45</v>
       </c>
       <c r="H16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L16">
-        <v>378542030.2939668</v>
+        <v>13568450</v>
       </c>
       <c r="M16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N16" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="O16" t="s">
         <v>327</v>
@@ -2082,25 +2088,25 @@
         <v>190</v>
       </c>
       <c r="D17" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E17" t="s">
         <v>226</v>
       </c>
       <c r="F17">
-        <v>137676647</v>
+        <v>42071.0413</v>
       </c>
       <c r="H17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L17">
-        <v>495635929.2</v>
+        <v>42071041.3</v>
       </c>
       <c r="M17" t="s">
         <v>314</v>
@@ -2126,31 +2132,31 @@
         <v>190</v>
       </c>
       <c r="D18" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F18">
-        <v>144321</v>
+        <v>2344.0244</v>
       </c>
       <c r="H18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L18">
-        <v>17908178.0536758</v>
+        <v>2344024.4</v>
       </c>
       <c r="M18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N18" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O18" t="s">
         <v>327</v>
@@ -2173,28 +2179,28 @@
         <v>197</v>
       </c>
       <c r="E19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F19">
-        <v>494423</v>
+        <v>2</v>
       </c>
       <c r="H19" t="s">
         <v>247</v>
       </c>
       <c r="J19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L19">
-        <v>42813081.77158993</v>
+        <v>2000</v>
       </c>
       <c r="M19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N19" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="O19" t="s">
         <v>327</v>
@@ -2214,34 +2220,31 @@
         <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E20" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F20">
-        <v>80.95999999999999</v>
-      </c>
-      <c r="G20" t="s">
-        <v>236</v>
+        <v>121071.9154</v>
       </c>
       <c r="H20" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K20" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L20">
-        <v>80960000</v>
+        <v>121071915.4</v>
       </c>
       <c r="M20" t="s">
         <v>314</v>
       </c>
       <c r="N20" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O20" t="s">
         <v>327</v>
@@ -2261,31 +2264,31 @@
         <v>190</v>
       </c>
       <c r="D21" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F21">
-        <v>1968</v>
+        <v>1361713.858</v>
       </c>
       <c r="H21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J21" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K21" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L21">
-        <v>1968000000</v>
+        <v>1361713858</v>
       </c>
       <c r="M21" t="s">
         <v>314</v>
       </c>
       <c r="N21" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O21" t="s">
         <v>327</v>
@@ -2305,34 +2308,31 @@
         <v>190</v>
       </c>
       <c r="D22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E22" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F22">
-        <v>0.368</v>
-      </c>
-      <c r="G22" t="s">
-        <v>236</v>
+        <v>5528.5667</v>
       </c>
       <c r="H22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J22" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K22" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L22">
-        <v>368000</v>
+        <v>5528566.7</v>
       </c>
       <c r="M22" t="s">
         <v>314</v>
       </c>
       <c r="N22" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O22" t="s">
         <v>327</v>
@@ -2352,34 +2352,31 @@
         <v>190</v>
       </c>
       <c r="D23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E23" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F23">
-        <v>10.12</v>
-      </c>
-      <c r="G23" t="s">
-        <v>236</v>
+        <v>1274584.342</v>
       </c>
       <c r="H23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K23" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L23">
-        <v>10120000</v>
+        <v>1274584342</v>
       </c>
       <c r="M23" t="s">
         <v>314</v>
       </c>
       <c r="N23" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O23" t="s">
         <v>327</v>
@@ -2402,28 +2399,28 @@
         <v>193</v>
       </c>
       <c r="E24" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F24">
-        <v>3947008</v>
+        <v>25050.76</v>
       </c>
       <c r="H24" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J24" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K24" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L24">
-        <v>3947008000</v>
+        <v>25050760</v>
       </c>
       <c r="M24" t="s">
         <v>314</v>
       </c>
       <c r="N24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O24" t="s">
         <v>327</v>
@@ -2443,25 +2440,25 @@
         <v>190</v>
       </c>
       <c r="D25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E25" t="s">
         <v>226</v>
       </c>
       <c r="F25">
-        <v>830958937</v>
+        <v>80313.18580000001</v>
       </c>
       <c r="H25" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J25" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K25" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L25">
-        <v>2991452173.2</v>
+        <v>80313185.80000001</v>
       </c>
       <c r="M25" t="s">
         <v>314</v>
@@ -2487,31 +2484,31 @@
         <v>190</v>
       </c>
       <c r="D26" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E26" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F26">
-        <v>65074</v>
+        <v>4761600.1</v>
       </c>
       <c r="H26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J26" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K26" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L26">
-        <v>65074000</v>
+        <v>170965251.5905</v>
       </c>
       <c r="M26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N26" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O26" t="s">
         <v>327</v>
@@ -2534,28 +2531,28 @@
         <v>199</v>
       </c>
       <c r="E27" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F27">
-        <v>71904</v>
+        <v>56414.6765</v>
       </c>
       <c r="H27" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J27" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K27" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L27">
-        <v>71904000</v>
+        <v>56414676.5</v>
       </c>
       <c r="M27" t="s">
         <v>314</v>
       </c>
       <c r="N27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O27" t="s">
         <v>327</v>
@@ -2575,31 +2572,31 @@
         <v>190</v>
       </c>
       <c r="D28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E28" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F28">
-        <v>182468</v>
+        <v>171984.8235</v>
       </c>
       <c r="H28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J28" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L28">
-        <v>182468000</v>
+        <v>171984823.5</v>
       </c>
       <c r="M28" t="s">
         <v>314</v>
       </c>
       <c r="N28" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O28" t="s">
         <v>327</v>
@@ -2619,28 +2616,28 @@
         <v>190</v>
       </c>
       <c r="D29" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E29" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F29">
-        <v>2829</v>
+        <v>522600</v>
       </c>
       <c r="H29" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J29" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K29" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L29">
-        <v>101575245</v>
+        <v>2090400</v>
       </c>
       <c r="M29" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N29" t="s">
         <v>320</v>
@@ -2663,34 +2660,31 @@
         <v>190</v>
       </c>
       <c r="D30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E30" t="s">
         <v>227</v>
       </c>
       <c r="F30">
-        <v>34190.62</v>
-      </c>
-      <c r="G30" t="s">
-        <v>237</v>
+        <v>119418.4</v>
       </c>
       <c r="H30" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J30" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K30" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L30">
-        <v>123086232</v>
+        <v>3914535.152</v>
       </c>
       <c r="M30" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N30" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O30" t="s">
         <v>327</v>
@@ -2710,34 +2704,31 @@
         <v>190</v>
       </c>
       <c r="D31" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E31" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F31">
-        <v>38555.38</v>
-      </c>
-      <c r="G31" t="s">
-        <v>237</v>
+        <v>59198</v>
       </c>
       <c r="H31" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J31" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K31" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L31">
-        <v>138799368</v>
+        <v>59198000</v>
       </c>
       <c r="M31" t="s">
         <v>314</v>
       </c>
       <c r="N31" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O31" t="s">
         <v>327</v>
@@ -2757,31 +2748,31 @@
         <v>190</v>
       </c>
       <c r="D32" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E32" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F32">
-        <v>369</v>
+        <v>31049.5</v>
       </c>
       <c r="H32" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J32" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K32" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L32">
-        <v>12095820</v>
+        <v>710263.5224</v>
       </c>
       <c r="M32" t="s">
         <v>315</v>
       </c>
       <c r="N32" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O32" t="s">
         <v>327</v>
@@ -2801,31 +2792,34 @@
         <v>190</v>
       </c>
       <c r="D33" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E33" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F33">
-        <v>2528</v>
+        <v>929608.637</v>
+      </c>
+      <c r="G33" t="s">
+        <v>236</v>
       </c>
       <c r="H33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J33" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K33" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L33">
-        <v>57828505.6</v>
+        <v>929608637</v>
       </c>
       <c r="M33" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N33" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="O33" t="s">
         <v>327</v>
@@ -2845,31 +2839,34 @@
         <v>190</v>
       </c>
       <c r="D34" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E34" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F34">
-        <v>21662.09888</v>
+        <v>365541.6667</v>
+      </c>
+      <c r="G34" t="s">
+        <v>237</v>
       </c>
       <c r="H34" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J34" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K34" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="L34">
-        <v>21662098.88</v>
+        <v>365541666.7</v>
       </c>
       <c r="M34" t="s">
         <v>314</v>
       </c>
       <c r="N34" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O34" t="s">
         <v>327</v>
@@ -2882,38 +2879,38 @@
       <c r="A35" t="s">
         <v>49</v>
       </c>
-      <c r="B35">
-        <v>2023</v>
-      </c>
       <c r="C35" t="s">
         <v>190</v>
       </c>
       <c r="D35" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E35" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F35">
-        <v>385327.7974</v>
+        <v>36282.05128</v>
+      </c>
+      <c r="G35" t="s">
+        <v>237</v>
       </c>
       <c r="H35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J35" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K35" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="L35">
-        <v>385327797.4</v>
+        <v>36282051.28</v>
       </c>
       <c r="M35" t="s">
         <v>314</v>
       </c>
       <c r="N35" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O35" t="s">
         <v>327</v>
@@ -2933,31 +2930,34 @@
         <v>190</v>
       </c>
       <c r="D36" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E36" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F36">
-        <v>3531.1068</v>
+        <v>2587.5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>238</v>
       </c>
       <c r="H36" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J36" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K36" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="L36">
-        <v>3531106.8</v>
+        <v>2587500</v>
       </c>
       <c r="M36" t="s">
         <v>314</v>
       </c>
       <c r="N36" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O36" t="s">
         <v>327</v>
@@ -2977,31 +2977,34 @@
         <v>190</v>
       </c>
       <c r="D37" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E37" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F37">
-        <v>892229.95044</v>
+        <v>21012.14575</v>
+      </c>
+      <c r="G37" t="s">
+        <v>236</v>
       </c>
       <c r="H37" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J37" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K37" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="L37">
-        <v>892229950.4400001</v>
+        <v>21012145.75</v>
       </c>
       <c r="M37" t="s">
         <v>314</v>
       </c>
       <c r="N37" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O37" t="s">
         <v>327</v>
@@ -3021,31 +3024,34 @@
         <v>190</v>
       </c>
       <c r="D38" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E38" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F38">
-        <v>10018.1179</v>
+        <v>22737.89649</v>
+      </c>
+      <c r="G38" t="s">
+        <v>236</v>
       </c>
       <c r="H38" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J38" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K38" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="L38">
-        <v>10018117.9</v>
+        <v>22737896.49</v>
       </c>
       <c r="M38" t="s">
         <v>314</v>
       </c>
       <c r="N38" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O38" t="s">
         <v>327</v>
@@ -3065,25 +3071,25 @@
         <v>190</v>
       </c>
       <c r="D39" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
       </c>
       <c r="F39">
-        <v>142393.17415</v>
+        <v>432</v>
       </c>
       <c r="H39" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J39" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K39" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="L39">
-        <v>142393174.15</v>
+        <v>432000000</v>
       </c>
       <c r="M39" t="s">
         <v>314</v>
@@ -3109,25 +3115,25 @@
         <v>190</v>
       </c>
       <c r="D40" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E40" t="s">
         <v>225</v>
       </c>
       <c r="F40">
-        <v>1683653</v>
+        <v>1233</v>
       </c>
       <c r="H40" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J40" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K40" t="s">
         <v>301</v>
       </c>
       <c r="L40">
-        <v>1683653000</v>
+        <v>1233000000</v>
       </c>
       <c r="M40" t="s">
         <v>314</v>
@@ -3153,25 +3159,25 @@
         <v>190</v>
       </c>
       <c r="D41" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E41" t="s">
         <v>225</v>
       </c>
       <c r="F41">
-        <v>1695665</v>
+        <v>12</v>
       </c>
       <c r="H41" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L41">
-        <v>1695665000</v>
+        <v>12000000</v>
       </c>
       <c r="M41" t="s">
         <v>314</v>
@@ -3197,25 +3203,25 @@
         <v>190</v>
       </c>
       <c r="D42" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E42" t="s">
         <v>225</v>
       </c>
       <c r="F42">
-        <v>38791</v>
+        <v>1058</v>
       </c>
       <c r="H42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J42" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K42" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L42">
-        <v>38791000</v>
+        <v>1058000000</v>
       </c>
       <c r="M42" t="s">
         <v>314</v>
@@ -3241,25 +3247,25 @@
         <v>190</v>
       </c>
       <c r="D43" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E43" t="s">
         <v>225</v>
       </c>
       <c r="F43">
-        <v>186977</v>
+        <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J43" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K43" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L43">
-        <v>186977000</v>
+        <v>1000000</v>
       </c>
       <c r="M43" t="s">
         <v>314</v>
@@ -3285,31 +3291,34 @@
         <v>190</v>
       </c>
       <c r="D44" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E44" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F44">
-        <v>453</v>
+        <v>4145000</v>
+      </c>
+      <c r="G44" t="s">
+        <v>239</v>
       </c>
       <c r="H44" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J44" t="s">
         <v>283</v>
       </c>
       <c r="K44" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L44">
-        <v>453000</v>
+        <v>14922000000</v>
       </c>
       <c r="M44" t="s">
         <v>314</v>
       </c>
       <c r="N44" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="O44" t="s">
         <v>327</v>
@@ -3329,31 +3338,31 @@
         <v>190</v>
       </c>
       <c r="D45" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E45" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F45">
-        <v>129455</v>
+        <v>1944158</v>
       </c>
       <c r="H45" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J45" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="K45" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="L45">
-        <v>129455000</v>
+        <v>1944158000</v>
       </c>
       <c r="M45" t="s">
         <v>314</v>
       </c>
       <c r="N45" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O45" t="s">
         <v>327</v>
@@ -3373,31 +3382,31 @@
         <v>190</v>
       </c>
       <c r="D46" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E46" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F46">
-        <v>178921745</v>
+        <v>132709926</v>
       </c>
       <c r="H46" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J46" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="K46" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="L46">
-        <v>644118282</v>
+        <v>477755733.6</v>
       </c>
       <c r="M46" t="s">
         <v>314</v>
       </c>
       <c r="N46" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="O46" t="s">
         <v>327</v>
@@ -3417,31 +3426,31 @@
         <v>190</v>
       </c>
       <c r="D47" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E47" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F47">
-        <v>11047</v>
+        <v>18198</v>
       </c>
       <c r="H47" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J47" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="K47" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="L47">
-        <v>11047000</v>
+        <v>18198000</v>
       </c>
       <c r="M47" t="s">
         <v>314</v>
       </c>
       <c r="N47" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O47" t="s">
         <v>327</v>
@@ -3461,31 +3470,31 @@
         <v>190</v>
       </c>
       <c r="D48" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E48" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F48">
-        <v>1347</v>
+        <v>5290</v>
       </c>
       <c r="H48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J48" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="K48" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="L48">
-        <v>1347000</v>
+        <v>5290000</v>
       </c>
       <c r="M48" t="s">
         <v>314</v>
       </c>
       <c r="N48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O48" t="s">
         <v>327</v>
@@ -3505,31 +3514,31 @@
         <v>190</v>
       </c>
       <c r="D49" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E49" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F49">
-        <v>86234</v>
+        <v>42378137.86</v>
       </c>
       <c r="H49" t="s">
         <v>253</v>
       </c>
       <c r="J49" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K49" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L49">
-        <v>86234000</v>
+        <v>1521587039.8633</v>
       </c>
       <c r="M49" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N49" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O49" t="s">
         <v>327</v>
@@ -3549,31 +3558,31 @@
         <v>190</v>
       </c>
       <c r="D50" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F50">
-        <v>619000</v>
+        <v>2919222</v>
       </c>
       <c r="H50" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J50" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="K50" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="L50">
-        <v>619000000</v>
+        <v>2919222000</v>
       </c>
       <c r="M50" t="s">
         <v>314</v>
       </c>
       <c r="N50" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O50" t="s">
         <v>327</v>
@@ -3593,31 +3602,31 @@
         <v>190</v>
       </c>
       <c r="D51" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E51" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F51">
-        <v>301000</v>
+        <v>14805627</v>
       </c>
       <c r="H51" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J51" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="K51" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="L51">
-        <v>301000000</v>
+        <v>59222508</v>
       </c>
       <c r="M51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N51" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="O51" t="s">
         <v>327</v>
@@ -3640,28 +3649,28 @@
         <v>193</v>
       </c>
       <c r="E52" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F52">
-        <v>211308</v>
+        <v>1147190.1</v>
       </c>
       <c r="H52" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J52" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="K52" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="L52">
-        <v>211308000</v>
+        <v>37604891.478</v>
       </c>
       <c r="M52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N52" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="O52" t="s">
         <v>327</v>
@@ -3684,28 +3693,28 @@
         <v>194</v>
       </c>
       <c r="E53" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F53">
-        <v>717</v>
+        <v>3691412.93</v>
       </c>
       <c r="H53" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J53" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="K53" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="L53">
-        <v>717000</v>
+        <v>84441809.056336</v>
       </c>
       <c r="M53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N53" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="O53" t="s">
         <v>327</v>
@@ -3725,31 +3734,31 @@
         <v>190</v>
       </c>
       <c r="D54" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E54" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F54">
-        <v>334179</v>
+        <v>91423</v>
       </c>
       <c r="H54" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J54" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K54" t="s">
         <v>303</v>
       </c>
       <c r="L54">
-        <v>334179000</v>
+        <v>91423000</v>
       </c>
       <c r="M54" t="s">
         <v>314</v>
       </c>
       <c r="N54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O54" t="s">
         <v>327</v>
@@ -3769,31 +3778,31 @@
         <v>190</v>
       </c>
       <c r="D55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E55" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F55">
-        <v>14406</v>
+        <v>182554670</v>
       </c>
       <c r="H55" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J55" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K55" t="s">
         <v>303</v>
       </c>
       <c r="L55">
-        <v>14406000</v>
+        <v>657196812</v>
       </c>
       <c r="M55" t="s">
         <v>314</v>
       </c>
       <c r="N55" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="O55" t="s">
         <v>327</v>
@@ -3813,31 +3822,31 @@
         <v>190</v>
       </c>
       <c r="D56" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E56" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F56">
-        <v>72011</v>
+        <v>82576</v>
       </c>
       <c r="H56" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J56" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K56" t="s">
         <v>303</v>
       </c>
       <c r="L56">
-        <v>72011000</v>
+        <v>82576000</v>
       </c>
       <c r="M56" t="s">
         <v>314</v>
       </c>
       <c r="N56" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O56" t="s">
         <v>327</v>
@@ -3857,31 +3866,31 @@
         <v>190</v>
       </c>
       <c r="D57" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E57" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F57">
-        <v>409793</v>
+        <v>6440</v>
       </c>
       <c r="H57" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J57" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K57" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="L57">
-        <v>55697075.44526765</v>
+        <v>6440000</v>
       </c>
       <c r="M57" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N57" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="O57" t="s">
         <v>327</v>
@@ -3901,25 +3910,25 @@
         <v>190</v>
       </c>
       <c r="D58" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E58" t="s">
         <v>226</v>
       </c>
       <c r="F58">
-        <v>17595388</v>
+        <v>327090</v>
       </c>
       <c r="H58" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J58" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K58" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="L58">
-        <v>63343396.8</v>
+        <v>327090000</v>
       </c>
       <c r="M58" t="s">
         <v>314</v>
@@ -3945,31 +3954,31 @@
         <v>190</v>
       </c>
       <c r="D59" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="E59" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F59">
-        <v>67158</v>
+        <v>658</v>
       </c>
       <c r="H59" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J59" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K59" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="L59">
-        <v>8333350.1134884</v>
+        <v>658000</v>
       </c>
       <c r="M59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N59" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O59" t="s">
         <v>327</v>
@@ -3989,31 +3998,31 @@
         <v>190</v>
       </c>
       <c r="D60" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E60" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F60">
-        <v>422621</v>
+        <v>211308</v>
       </c>
       <c r="H60" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J60" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K60" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="L60">
-        <v>36595602.20983067</v>
+        <v>211308000</v>
       </c>
       <c r="M60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N60" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="O60" t="s">
         <v>327</v>
@@ -4033,31 +4042,31 @@
         <v>190</v>
       </c>
       <c r="D61" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E61" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F61">
-        <v>1188</v>
+        <v>717</v>
       </c>
       <c r="H61" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J61" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K61" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="L61">
-        <v>42655140</v>
+        <v>717000</v>
       </c>
       <c r="M61" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N61" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="O61" t="s">
         <v>327</v>
@@ -4077,34 +4086,31 @@
         <v>190</v>
       </c>
       <c r="D62" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E62" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F62">
-        <v>10684.5</v>
-      </c>
-      <c r="G62" t="s">
-        <v>237</v>
+        <v>334179</v>
       </c>
       <c r="H62" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J62" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K62" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="L62">
-        <v>38464200</v>
+        <v>334179000</v>
       </c>
       <c r="M62" t="s">
         <v>314</v>
       </c>
       <c r="N62" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O62" t="s">
         <v>327</v>
@@ -4124,34 +4130,31 @@
         <v>190</v>
       </c>
       <c r="D63" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E63" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F63">
-        <v>32053.5</v>
-      </c>
-      <c r="G63" t="s">
-        <v>237</v>
+        <v>14406</v>
       </c>
       <c r="H63" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J63" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K63" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="L63">
-        <v>115392600</v>
+        <v>14406000</v>
       </c>
       <c r="M63" t="s">
         <v>314</v>
       </c>
       <c r="N63" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O63" t="s">
         <v>327</v>
@@ -4171,31 +4174,31 @@
         <v>190</v>
       </c>
       <c r="D64" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E64" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F64">
-        <v>36</v>
+        <v>72011</v>
       </c>
       <c r="H64" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J64" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K64" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="L64">
-        <v>1180080</v>
+        <v>72011000</v>
       </c>
       <c r="M64" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N64" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O64" t="s">
         <v>327</v>
@@ -4215,34 +4218,31 @@
         <v>190</v>
       </c>
       <c r="D65" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E65" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F65">
-        <v>1528</v>
-      </c>
-      <c r="G65" t="s">
-        <v>238</v>
+        <v>619000</v>
       </c>
       <c r="H65" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J65" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K65" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="L65">
-        <v>58064</v>
+        <v>619000000</v>
       </c>
       <c r="M65" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="N65" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="O65" t="s">
         <v>327</v>
@@ -4262,31 +4262,31 @@
         <v>190</v>
       </c>
       <c r="D66" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="E66" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F66">
-        <v>13849</v>
+        <v>301000</v>
       </c>
       <c r="H66" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J66" t="s">
         <v>286</v>
       </c>
       <c r="K66" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L66">
-        <v>497248345</v>
+        <v>301000000</v>
       </c>
       <c r="M66" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N66" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="O66" t="s">
         <v>327</v>
@@ -4306,31 +4306,31 @@
         <v>190</v>
       </c>
       <c r="D67" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="E67" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F67">
-        <v>326</v>
+        <v>140100</v>
       </c>
       <c r="H67" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J67" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K67" t="s">
         <v>304</v>
       </c>
       <c r="L67">
-        <v>1173600000</v>
+        <v>140100000</v>
       </c>
       <c r="M67" t="s">
         <v>314</v>
       </c>
       <c r="N67" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O67" t="s">
         <v>327</v>
@@ -4350,31 +4350,31 @@
         <v>190</v>
       </c>
       <c r="D68" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="E68" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F68">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="H68" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J68" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K68" t="s">
         <v>304</v>
       </c>
       <c r="L68">
-        <v>13833160</v>
+        <v>475000</v>
       </c>
       <c r="M68" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N68" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O68" t="s">
         <v>327</v>
@@ -4394,31 +4394,31 @@
         <v>190</v>
       </c>
       <c r="D69" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E69" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F69">
-        <v>191632</v>
+        <v>960748</v>
       </c>
       <c r="H69" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J69" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K69" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L69">
-        <v>191632000</v>
+        <v>960748000</v>
       </c>
       <c r="M69" t="s">
         <v>314</v>
       </c>
       <c r="N69" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O69" t="s">
         <v>327</v>
@@ -4438,31 +4438,31 @@
         <v>190</v>
       </c>
       <c r="D70" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="E70" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F70">
-        <v>181</v>
+        <v>2124</v>
       </c>
       <c r="H70" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J70" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K70" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L70">
-        <v>181000</v>
+        <v>2124000</v>
       </c>
       <c r="M70" t="s">
         <v>314</v>
       </c>
       <c r="N70" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O70" t="s">
         <v>327</v>
@@ -4482,31 +4482,31 @@
         <v>190</v>
       </c>
       <c r="D71" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="E71" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F71">
-        <v>276713</v>
+        <v>6344</v>
       </c>
       <c r="H71" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J71" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K71" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L71">
-        <v>276713000</v>
+        <v>6344000</v>
       </c>
       <c r="M71" t="s">
         <v>314</v>
       </c>
       <c r="N71" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O71" t="s">
         <v>327</v>
@@ -4529,28 +4529,28 @@
         <v>196</v>
       </c>
       <c r="E72" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F72">
-        <v>3549</v>
+        <v>221612</v>
       </c>
       <c r="H72" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J72" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K72" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L72">
-        <v>3549000</v>
+        <v>221612000</v>
       </c>
       <c r="M72" t="s">
         <v>314</v>
       </c>
       <c r="N72" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O72" t="s">
         <v>327</v>
@@ -4564,37 +4564,37 @@
         <v>87</v>
       </c>
       <c r="B73">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C73" t="s">
         <v>190</v>
       </c>
       <c r="D73" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="E73" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F73">
-        <v>45</v>
+        <v>3116555.8</v>
       </c>
       <c r="H73" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J73" t="s">
         <v>287</v>
       </c>
       <c r="K73" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L73">
-        <v>45000</v>
+        <v>111899935.999</v>
       </c>
       <c r="M73" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N73" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O73" t="s">
         <v>327</v>
@@ -4608,37 +4608,37 @@
         <v>88</v>
       </c>
       <c r="B74">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C74" t="s">
         <v>190</v>
       </c>
       <c r="D74" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="E74" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F74">
-        <v>187</v>
+        <v>248298644.4</v>
       </c>
       <c r="H74" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J74" t="s">
         <v>287</v>
       </c>
       <c r="K74" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L74">
-        <v>187000</v>
+        <v>893875119.84</v>
       </c>
       <c r="M74" t="s">
         <v>314</v>
       </c>
       <c r="N74" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="O74" t="s">
         <v>327</v>
@@ -4652,37 +4652,37 @@
         <v>89</v>
       </c>
       <c r="B75">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C75" t="s">
         <v>190</v>
       </c>
       <c r="D75" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E75" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F75">
-        <v>76904</v>
+        <v>151631.5</v>
       </c>
       <c r="H75" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J75" t="s">
         <v>287</v>
       </c>
       <c r="K75" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L75">
-        <v>76904000</v>
+        <v>4970480.57</v>
       </c>
       <c r="M75" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N75" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="O75" t="s">
         <v>327</v>
@@ -4696,37 +4696,37 @@
         <v>90</v>
       </c>
       <c r="B76">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C76" t="s">
         <v>190</v>
       </c>
       <c r="D76" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="E76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F76">
-        <v>391146</v>
+        <v>640677.8</v>
       </c>
       <c r="H76" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J76" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="K76" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="L76">
-        <v>391146000</v>
+        <v>14655632.81056</v>
       </c>
       <c r="M76" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N76" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="O76" t="s">
         <v>327</v>
@@ -4740,31 +4740,31 @@
         <v>91</v>
       </c>
       <c r="B77">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C77" t="s">
         <v>190</v>
       </c>
       <c r="D77" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E77" t="s">
         <v>226</v>
       </c>
       <c r="F77">
-        <v>469220285</v>
+        <v>307233</v>
       </c>
       <c r="H77" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J77" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="K77" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="L77">
-        <v>1689193026</v>
+        <v>307233000</v>
       </c>
       <c r="M77" t="s">
         <v>314</v>
@@ -4790,31 +4790,31 @@
         <v>190</v>
       </c>
       <c r="D78" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E78" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F78">
-        <v>6280</v>
+        <v>13849</v>
       </c>
       <c r="H78" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J78" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="K78" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L78">
-        <v>6280000</v>
+        <v>497248345</v>
       </c>
       <c r="M78" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N78" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O78" t="s">
         <v>327</v>
@@ -4834,31 +4834,31 @@
         <v>190</v>
       </c>
       <c r="D79" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E79" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F79">
-        <v>8329</v>
+        <v>326</v>
       </c>
       <c r="H79" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J79" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="K79" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L79">
-        <v>8329000</v>
+        <v>1173600000</v>
       </c>
       <c r="M79" t="s">
         <v>314</v>
       </c>
       <c r="N79" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="O79" t="s">
         <v>327</v>
@@ -4878,31 +4878,31 @@
         <v>190</v>
       </c>
       <c r="D80" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E80" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F80">
-        <v>297435</v>
+        <v>422</v>
       </c>
       <c r="H80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J80" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="K80" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L80">
-        <v>297435000</v>
+        <v>13833160</v>
       </c>
       <c r="M80" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N80" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="O80" t="s">
         <v>327</v>
@@ -4922,31 +4922,31 @@
         <v>190</v>
       </c>
       <c r="D81" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F81">
-        <v>91423</v>
+        <v>3947008</v>
       </c>
       <c r="H81" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J81" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="K81" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="L81">
-        <v>91423000</v>
+        <v>3947008000</v>
       </c>
       <c r="M81" t="s">
         <v>314</v>
       </c>
       <c r="N81" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O81" t="s">
         <v>327</v>
@@ -4969,28 +4969,28 @@
         <v>195</v>
       </c>
       <c r="E82" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F82">
-        <v>182554670</v>
+        <v>830958937</v>
       </c>
       <c r="H82" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J82" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="K82" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="L82">
-        <v>657196812</v>
+        <v>2991452173.2</v>
       </c>
       <c r="M82" t="s">
         <v>314</v>
       </c>
       <c r="N82" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="O82" t="s">
         <v>327</v>
@@ -5010,31 +5010,31 @@
         <v>190</v>
       </c>
       <c r="D83" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E83" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F83">
-        <v>82576</v>
+        <v>65074</v>
       </c>
       <c r="H83" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J83" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="K83" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="L83">
-        <v>82576000</v>
+        <v>65074000</v>
       </c>
       <c r="M83" t="s">
         <v>314</v>
       </c>
       <c r="N83" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O83" t="s">
         <v>327</v>
@@ -5054,31 +5054,31 @@
         <v>190</v>
       </c>
       <c r="D84" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E84" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F84">
-        <v>6440</v>
+        <v>71904</v>
       </c>
       <c r="H84" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J84" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="K84" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="L84">
-        <v>6440000</v>
+        <v>71904000</v>
       </c>
       <c r="M84" t="s">
         <v>314</v>
       </c>
       <c r="N84" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O84" t="s">
         <v>327</v>
@@ -5098,31 +5098,31 @@
         <v>190</v>
       </c>
       <c r="D85" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E85" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F85">
-        <v>327090</v>
+        <v>182468</v>
       </c>
       <c r="H85" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J85" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="K85" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="L85">
-        <v>327090000</v>
+        <v>182468000</v>
       </c>
       <c r="M85" t="s">
         <v>314</v>
       </c>
       <c r="N85" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O85" t="s">
         <v>327</v>
@@ -5142,31 +5142,31 @@
         <v>190</v>
       </c>
       <c r="D86" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E86" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F86">
-        <v>658</v>
+        <v>2829</v>
       </c>
       <c r="H86" t="s">
         <v>261</v>
       </c>
       <c r="J86" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="K86" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L86">
-        <v>658000</v>
+        <v>101575245</v>
       </c>
       <c r="M86" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N86" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O86" t="s">
         <v>327</v>
@@ -5186,31 +5186,34 @@
         <v>190</v>
       </c>
       <c r="D87" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E87" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F87">
-        <v>3590887</v>
-      </c>
-      <c r="I87" t="s">
-        <v>272</v>
+        <v>34190.62</v>
+      </c>
+      <c r="G87" t="s">
+        <v>240</v>
+      </c>
+      <c r="H87" t="s">
+        <v>261</v>
       </c>
       <c r="J87" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="K87" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L87">
-        <v>3590887000</v>
+        <v>123086232</v>
       </c>
       <c r="M87" t="s">
         <v>314</v>
       </c>
       <c r="N87" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="O87" t="s">
         <v>327</v>
@@ -5230,31 +5233,34 @@
         <v>190</v>
       </c>
       <c r="D88" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E88" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F88">
-        <v>164987364</v>
-      </c>
-      <c r="I88" t="s">
-        <v>272</v>
+        <v>38555.38</v>
+      </c>
+      <c r="G88" t="s">
+        <v>240</v>
+      </c>
+      <c r="H88" t="s">
+        <v>261</v>
       </c>
       <c r="J88" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="K88" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L88">
-        <v>593954510.4</v>
+        <v>138799368</v>
       </c>
       <c r="M88" t="s">
         <v>314</v>
       </c>
       <c r="N88" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="O88" t="s">
         <v>327</v>
@@ -5274,31 +5280,31 @@
         <v>190</v>
       </c>
       <c r="D89" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="E89" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F89">
-        <v>45318</v>
-      </c>
-      <c r="I89" t="s">
-        <v>272</v>
+        <v>369</v>
+      </c>
+      <c r="H89" t="s">
+        <v>261</v>
       </c>
       <c r="J89" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="K89" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L89">
-        <v>45318000</v>
+        <v>12095820</v>
       </c>
       <c r="M89" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N89" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="O89" t="s">
         <v>327</v>
@@ -5318,31 +5324,31 @@
         <v>190</v>
       </c>
       <c r="D90" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E90" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F90">
-        <v>51161</v>
-      </c>
-      <c r="I90" t="s">
-        <v>272</v>
+        <v>2528</v>
+      </c>
+      <c r="H90" t="s">
+        <v>261</v>
       </c>
       <c r="J90" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="K90" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L90">
-        <v>51161000</v>
+        <v>57828505.6</v>
       </c>
       <c r="M90" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N90" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="O90" t="s">
         <v>327</v>
@@ -5362,31 +5368,31 @@
         <v>190</v>
       </c>
       <c r="D91" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="E91" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F91">
-        <v>7311</v>
-      </c>
-      <c r="I91" t="s">
-        <v>272</v>
+        <v>27653.22904</v>
+      </c>
+      <c r="H91" t="s">
+        <v>262</v>
       </c>
       <c r="J91" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K91" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L91">
-        <v>7311000</v>
+        <v>27653229.04</v>
       </c>
       <c r="M91" t="s">
         <v>314</v>
       </c>
       <c r="N91" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O91" t="s">
         <v>327</v>
@@ -5406,31 +5412,31 @@
         <v>190</v>
       </c>
       <c r="D92" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="E92" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F92">
-        <v>235</v>
-      </c>
-      <c r="I92" t="s">
-        <v>272</v>
+        <v>11770.37023</v>
+      </c>
+      <c r="H92" t="s">
+        <v>262</v>
       </c>
       <c r="J92" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K92" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L92">
-        <v>235000</v>
+        <v>11770370.23</v>
       </c>
       <c r="M92" t="s">
         <v>314</v>
       </c>
       <c r="N92" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O92" t="s">
         <v>327</v>
@@ -5450,31 +5456,31 @@
         <v>190</v>
       </c>
       <c r="D93" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E93" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F93">
-        <v>1944158</v>
+        <v>308614.7308</v>
       </c>
       <c r="H93" t="s">
         <v>262</v>
       </c>
       <c r="J93" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K93" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L93">
-        <v>1944158000</v>
+        <v>308614730.8</v>
       </c>
       <c r="M93" t="s">
         <v>314</v>
       </c>
       <c r="N93" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O93" t="s">
         <v>327</v>
@@ -5494,25 +5500,25 @@
         <v>190</v>
       </c>
       <c r="D94" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E94" t="s">
         <v>226</v>
       </c>
       <c r="F94">
-        <v>132709926</v>
+        <v>3808.984282</v>
       </c>
       <c r="H94" t="s">
         <v>262</v>
       </c>
       <c r="J94" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K94" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L94">
-        <v>477755733.6</v>
+        <v>3808984.282</v>
       </c>
       <c r="M94" t="s">
         <v>314</v>
@@ -5538,31 +5544,31 @@
         <v>190</v>
       </c>
       <c r="D95" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E95" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F95">
-        <v>18198</v>
+        <v>509889.6</v>
       </c>
       <c r="H95" t="s">
         <v>262</v>
       </c>
       <c r="J95" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L95">
-        <v>18198000</v>
+        <v>509889600</v>
       </c>
       <c r="M95" t="s">
         <v>314</v>
       </c>
       <c r="N95" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O95" t="s">
         <v>327</v>
@@ -5582,31 +5588,31 @@
         <v>190</v>
       </c>
       <c r="D96" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F96">
-        <v>5290</v>
+        <v>5437.635</v>
       </c>
       <c r="H96" t="s">
         <v>262</v>
       </c>
       <c r="J96" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K96" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L96">
-        <v>5290000</v>
+        <v>5437635</v>
       </c>
       <c r="M96" t="s">
         <v>314</v>
       </c>
       <c r="N96" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O96" t="s">
         <v>327</v>
@@ -5626,34 +5632,31 @@
         <v>190</v>
       </c>
       <c r="D97" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F97">
-        <v>929608.636977058</v>
-      </c>
-      <c r="G97" t="s">
-        <v>239</v>
+        <v>229891.869</v>
       </c>
       <c r="H97" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J97" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="K97" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="L97">
-        <v>929608636.9770581</v>
+        <v>229891869</v>
       </c>
       <c r="M97" t="s">
         <v>314</v>
       </c>
       <c r="N97" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O97" t="s">
         <v>327</v>
@@ -5673,34 +5676,31 @@
         <v>190</v>
       </c>
       <c r="D98" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F98">
-        <v>365541.6666666667</v>
-      </c>
-      <c r="G98" t="s">
-        <v>240</v>
+        <v>1483.2</v>
       </c>
       <c r="H98" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J98" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="K98" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="L98">
-        <v>365541666.6666667</v>
+        <v>1483200</v>
       </c>
       <c r="M98" t="s">
         <v>314</v>
       </c>
       <c r="N98" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O98" t="s">
         <v>327</v>
@@ -5713,38 +5713,41 @@
       <c r="A99" t="s">
         <v>113</v>
       </c>
+      <c r="B99">
+        <v>2023</v>
+      </c>
       <c r="C99" t="s">
         <v>190</v>
       </c>
       <c r="D99" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F99">
-        <v>36282.05128205128</v>
+        <v>1530.9</v>
       </c>
       <c r="G99" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H99" t="s">
         <v>263</v>
       </c>
       <c r="J99" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K99" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L99">
-        <v>36282051.28205128</v>
+        <v>1530900</v>
       </c>
       <c r="M99" t="s">
         <v>314</v>
       </c>
       <c r="N99" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O99" t="s">
         <v>327</v>
@@ -5764,34 +5767,31 @@
         <v>190</v>
       </c>
       <c r="D100" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F100">
-        <v>2587.5</v>
-      </c>
-      <c r="G100" t="s">
-        <v>241</v>
+        <v>206946</v>
       </c>
       <c r="H100" t="s">
         <v>263</v>
       </c>
       <c r="J100" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K100" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L100">
-        <v>2587500</v>
+        <v>206946000</v>
       </c>
       <c r="M100" t="s">
         <v>314</v>
       </c>
       <c r="N100" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O100" t="s">
         <v>327</v>
@@ -5811,34 +5811,31 @@
         <v>190</v>
       </c>
       <c r="D101" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F101">
-        <v>21012.14574898786</v>
-      </c>
-      <c r="G101" t="s">
-        <v>239</v>
+        <v>525946.7</v>
       </c>
       <c r="H101" t="s">
         <v>263</v>
       </c>
       <c r="J101" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K101" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L101">
-        <v>21012145.74898786</v>
+        <v>525946699.9999999</v>
       </c>
       <c r="M101" t="s">
         <v>314</v>
       </c>
       <c r="N101" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O101" t="s">
         <v>327</v>
@@ -5858,34 +5855,34 @@
         <v>190</v>
       </c>
       <c r="D102" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F102">
-        <v>22737.89649415693</v>
+        <v>4260.6</v>
       </c>
       <c r="G102" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H102" t="s">
         <v>263</v>
       </c>
       <c r="J102" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K102" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L102">
-        <v>22737896.49415693</v>
+        <v>4260600</v>
       </c>
       <c r="M102" t="s">
         <v>314</v>
       </c>
       <c r="N102" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O102" t="s">
         <v>327</v>
@@ -5905,31 +5902,31 @@
         <v>190</v>
       </c>
       <c r="D103" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F103">
-        <v>27653.22904</v>
+        <v>3350.8</v>
       </c>
       <c r="H103" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J103" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="K103" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="L103">
-        <v>27653229.04</v>
+        <v>3350800</v>
       </c>
       <c r="M103" t="s">
         <v>314</v>
       </c>
       <c r="N103" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O103" t="s">
         <v>327</v>
@@ -5949,31 +5946,31 @@
         <v>190</v>
       </c>
       <c r="D104" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F104">
-        <v>11770.3702287417</v>
+        <v>63958.3</v>
       </c>
       <c r="H104" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J104" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="K104" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="L104">
-        <v>11770370.2287417</v>
+        <v>63958300</v>
       </c>
       <c r="M104" t="s">
         <v>314</v>
       </c>
       <c r="N104" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O104" t="s">
         <v>327</v>
@@ -5993,31 +5990,31 @@
         <v>190</v>
       </c>
       <c r="D105" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F105">
-        <v>308614.730821</v>
+        <v>33</v>
       </c>
       <c r="H105" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J105" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="K105" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="L105">
-        <v>308614730.821</v>
+        <v>33000</v>
       </c>
       <c r="M105" t="s">
         <v>314</v>
       </c>
       <c r="N105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O105" t="s">
         <v>327</v>
@@ -6037,31 +6034,31 @@
         <v>190</v>
       </c>
       <c r="D106" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F106">
-        <v>3808.98428206273</v>
+        <v>21662.09888</v>
       </c>
       <c r="H106" t="s">
         <v>264</v>
       </c>
       <c r="J106" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K106" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L106">
-        <v>3808984.28206273</v>
+        <v>21662098.88</v>
       </c>
       <c r="M106" t="s">
         <v>314</v>
       </c>
       <c r="N106" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O106" t="s">
         <v>327</v>
@@ -6081,31 +6078,31 @@
         <v>190</v>
       </c>
       <c r="D107" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F107">
-        <v>509889.6</v>
+        <v>385327.7974</v>
       </c>
       <c r="H107" t="s">
         <v>264</v>
       </c>
       <c r="J107" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K107" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L107">
-        <v>509889600</v>
+        <v>385327797.4</v>
       </c>
       <c r="M107" t="s">
         <v>314</v>
       </c>
       <c r="N107" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O107" t="s">
         <v>327</v>
@@ -6125,31 +6122,31 @@
         <v>190</v>
       </c>
       <c r="D108" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F108">
-        <v>5437.635</v>
+        <v>3531.1068</v>
       </c>
       <c r="H108" t="s">
         <v>264</v>
       </c>
       <c r="J108" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K108" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L108">
-        <v>5437635</v>
+        <v>3531106.8</v>
       </c>
       <c r="M108" t="s">
         <v>314</v>
       </c>
       <c r="N108" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O108" t="s">
         <v>327</v>
@@ -6169,31 +6166,31 @@
         <v>190</v>
       </c>
       <c r="D109" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F109">
-        <v>229891.86895</v>
+        <v>892229.9504</v>
       </c>
       <c r="H109" t="s">
         <v>264</v>
       </c>
       <c r="J109" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K109" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L109">
-        <v>229891868.95</v>
+        <v>892229950.4</v>
       </c>
       <c r="M109" t="s">
         <v>314</v>
       </c>
       <c r="N109" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O109" t="s">
         <v>327</v>
@@ -6213,31 +6210,31 @@
         <v>190</v>
       </c>
       <c r="D110" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F110">
-        <v>1483.2</v>
+        <v>10018.1179</v>
       </c>
       <c r="H110" t="s">
         <v>264</v>
       </c>
       <c r="J110" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K110" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L110">
-        <v>1483200</v>
+        <v>10018117.9</v>
       </c>
       <c r="M110" t="s">
         <v>314</v>
       </c>
       <c r="N110" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O110" t="s">
         <v>327</v>
@@ -6257,31 +6254,31 @@
         <v>190</v>
       </c>
       <c r="D111" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E111" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F111">
-        <v>4761600.1</v>
+        <v>142393.1742</v>
       </c>
       <c r="H111" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J111" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="K111" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="L111">
-        <v>170965251.5905</v>
+        <v>142393174.2</v>
       </c>
       <c r="M111" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N111" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="O111" t="s">
         <v>327</v>
@@ -6301,13 +6298,13 @@
         <v>190</v>
       </c>
       <c r="D112" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F112">
-        <v>56414.6765</v>
+        <v>1188</v>
       </c>
       <c r="H112" t="s">
         <v>265</v>
@@ -6316,16 +6313,16 @@
         <v>289</v>
       </c>
       <c r="K112" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L112">
-        <v>56414676.5</v>
+        <v>42655140</v>
       </c>
       <c r="M112" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N112" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O112" t="s">
         <v>327</v>
@@ -6345,13 +6342,16 @@
         <v>190</v>
       </c>
       <c r="D113" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F113">
-        <v>171984.8235</v>
+        <v>10684.5</v>
+      </c>
+      <c r="G113" t="s">
+        <v>240</v>
       </c>
       <c r="H113" t="s">
         <v>265</v>
@@ -6360,16 +6360,16 @@
         <v>289</v>
       </c>
       <c r="K113" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L113">
-        <v>171984823.5</v>
+        <v>38464200</v>
       </c>
       <c r="M113" t="s">
         <v>314</v>
       </c>
       <c r="N113" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="O113" t="s">
         <v>327</v>
@@ -6389,13 +6389,16 @@
         <v>190</v>
       </c>
       <c r="D114" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E114" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F114">
-        <v>522600</v>
+        <v>32053.5</v>
+      </c>
+      <c r="G114" t="s">
+        <v>240</v>
       </c>
       <c r="H114" t="s">
         <v>265</v>
@@ -6404,16 +6407,16 @@
         <v>289</v>
       </c>
       <c r="K114" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L114">
-        <v>2090400</v>
+        <v>115392600</v>
       </c>
       <c r="M114" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="N114" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="O114" t="s">
         <v>327</v>
@@ -6433,13 +6436,13 @@
         <v>190</v>
       </c>
       <c r="D115" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E115" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F115">
-        <v>119418.4</v>
+        <v>36</v>
       </c>
       <c r="H115" t="s">
         <v>265</v>
@@ -6448,10 +6451,10 @@
         <v>289</v>
       </c>
       <c r="K115" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L115">
-        <v>3914535.152</v>
+        <v>1180080</v>
       </c>
       <c r="M115" t="s">
         <v>315</v>
@@ -6477,13 +6480,16 @@
         <v>190</v>
       </c>
       <c r="D116" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="F116">
-        <v>59198</v>
+        <v>1528</v>
+      </c>
+      <c r="G116" t="s">
+        <v>242</v>
       </c>
       <c r="H116" t="s">
         <v>265</v>
@@ -6492,16 +6498,16 @@
         <v>289</v>
       </c>
       <c r="K116" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L116">
-        <v>59198000</v>
+        <v>58064</v>
       </c>
       <c r="M116" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N116" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="O116" t="s">
         <v>327</v>
@@ -6521,31 +6527,31 @@
         <v>190</v>
       </c>
       <c r="D117" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="E117" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F117">
-        <v>31049.5</v>
+        <v>2785135</v>
       </c>
       <c r="H117" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J117" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K117" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L117">
-        <v>710263.5224</v>
+        <v>378542030.2939668</v>
       </c>
       <c r="M117" t="s">
         <v>315</v>
       </c>
       <c r="N117" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O117" t="s">
         <v>327</v>
@@ -6565,31 +6571,31 @@
         <v>190</v>
       </c>
       <c r="D118" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F118">
-        <v>23524.436671511</v>
-      </c>
-      <c r="I118" t="s">
-        <v>273</v>
+        <v>137676647</v>
+      </c>
+      <c r="H118" t="s">
+        <v>266</v>
       </c>
       <c r="J118" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="K118" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="L118">
-        <v>23524436.671511</v>
+        <v>495635929.2</v>
       </c>
       <c r="M118" t="s">
         <v>314</v>
       </c>
       <c r="N118" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="O118" t="s">
         <v>327</v>
@@ -6609,31 +6615,31 @@
         <v>190</v>
       </c>
       <c r="D119" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F119">
-        <v>623021.8686160001</v>
-      </c>
-      <c r="I119" t="s">
-        <v>273</v>
+        <v>144321</v>
+      </c>
+      <c r="H119" t="s">
+        <v>266</v>
       </c>
       <c r="J119" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="K119" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="L119">
-        <v>623021868.6160001</v>
+        <v>17908178.0536758</v>
       </c>
       <c r="M119" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N119" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="O119" t="s">
         <v>327</v>
@@ -6656,28 +6662,28 @@
         <v>194</v>
       </c>
       <c r="E120" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F120">
-        <v>91025.4822599152</v>
-      </c>
-      <c r="I120" t="s">
-        <v>273</v>
+        <v>494423</v>
+      </c>
+      <c r="H120" t="s">
+        <v>266</v>
       </c>
       <c r="J120" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="K120" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="L120">
-        <v>91025482.2599152</v>
+        <v>42813081.77158993</v>
       </c>
       <c r="M120" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N120" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="O120" t="s">
         <v>327</v>
@@ -6697,31 +6703,31 @@
         <v>190</v>
       </c>
       <c r="D121" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E121" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F121">
-        <v>723967.2</v>
-      </c>
-      <c r="I121" t="s">
-        <v>273</v>
+        <v>129455</v>
+      </c>
+      <c r="H121" t="s">
+        <v>267</v>
       </c>
       <c r="J121" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K121" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L121">
-        <v>723967200</v>
+        <v>129455000</v>
       </c>
       <c r="M121" t="s">
         <v>314</v>
       </c>
       <c r="N121" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O121" t="s">
         <v>327</v>
@@ -6741,31 +6747,31 @@
         <v>190</v>
       </c>
       <c r="D122" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E122" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F122">
-        <v>17195.8465</v>
-      </c>
-      <c r="I122" t="s">
-        <v>273</v>
+        <v>178921745</v>
+      </c>
+      <c r="H122" t="s">
+        <v>267</v>
       </c>
       <c r="J122" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K122" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L122">
-        <v>17195846.5</v>
+        <v>644118282</v>
       </c>
       <c r="M122" t="s">
         <v>314</v>
       </c>
       <c r="N122" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="O122" t="s">
         <v>327</v>
@@ -6785,31 +6791,31 @@
         <v>190</v>
       </c>
       <c r="D123" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E123" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F123">
-        <v>166705</v>
-      </c>
-      <c r="I123" t="s">
-        <v>273</v>
+        <v>11047</v>
+      </c>
+      <c r="H123" t="s">
+        <v>267</v>
       </c>
       <c r="J123" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K123" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L123">
-        <v>166705000</v>
+        <v>11047000</v>
       </c>
       <c r="M123" t="s">
         <v>314</v>
       </c>
       <c r="N123" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O123" t="s">
         <v>327</v>
@@ -6829,31 +6835,31 @@
         <v>190</v>
       </c>
       <c r="D124" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E124" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F124">
-        <v>6336.0580703</v>
-      </c>
-      <c r="I124" t="s">
-        <v>273</v>
+        <v>1347</v>
+      </c>
+      <c r="H124" t="s">
+        <v>267</v>
       </c>
       <c r="J124" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K124" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L124">
-        <v>6336058.0703</v>
+        <v>1347000</v>
       </c>
       <c r="M124" t="s">
         <v>314</v>
       </c>
       <c r="N124" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O124" t="s">
         <v>327</v>
@@ -6873,31 +6879,31 @@
         <v>190</v>
       </c>
       <c r="D125" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E125" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F125">
-        <v>42378137.86</v>
+        <v>86234</v>
       </c>
       <c r="H125" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J125" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="K125" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="L125">
-        <v>1521587039.8633</v>
+        <v>86234000</v>
       </c>
       <c r="M125" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N125" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="O125" t="s">
         <v>327</v>
@@ -6917,31 +6923,31 @@
         <v>190</v>
       </c>
       <c r="D126" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="E126" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F126">
-        <v>2919222</v>
+        <v>391146</v>
       </c>
       <c r="H126" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J126" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="K126" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="L126">
-        <v>2919222000</v>
+        <v>391146000</v>
       </c>
       <c r="M126" t="s">
         <v>314</v>
       </c>
       <c r="N126" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O126" t="s">
         <v>327</v>
@@ -6961,31 +6967,31 @@
         <v>190</v>
       </c>
       <c r="D127" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E127" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F127">
-        <v>14805627</v>
+        <v>469220285</v>
       </c>
       <c r="H127" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J127" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="K127" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="L127">
-        <v>59222508</v>
+        <v>1689193026</v>
       </c>
       <c r="M127" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="N127" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O127" t="s">
         <v>327</v>
@@ -7005,31 +7011,31 @@
         <v>190</v>
       </c>
       <c r="D128" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E128" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F128">
-        <v>1147190.1</v>
+        <v>6280</v>
       </c>
       <c r="H128" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J128" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="K128" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="L128">
-        <v>37604891.478</v>
+        <v>6280000</v>
       </c>
       <c r="M128" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N128" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O128" t="s">
         <v>327</v>
@@ -7049,31 +7055,31 @@
         <v>190</v>
       </c>
       <c r="D129" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E129" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F129">
-        <v>3691412.93</v>
+        <v>8329</v>
       </c>
       <c r="H129" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J129" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="K129" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="L129">
-        <v>84441809.056336</v>
+        <v>8329000</v>
       </c>
       <c r="M129" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N129" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="O129" t="s">
         <v>327</v>
@@ -7093,31 +7099,31 @@
         <v>190</v>
       </c>
       <c r="D130" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E130" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F130">
-        <v>2</v>
+        <v>297435</v>
       </c>
       <c r="H130" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J130" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K130" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L130">
-        <v>2000</v>
+        <v>297435000</v>
       </c>
       <c r="M130" t="s">
         <v>314</v>
       </c>
       <c r="N130" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O130" t="s">
         <v>327</v>
@@ -7137,31 +7143,31 @@
         <v>190</v>
       </c>
       <c r="D131" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E131" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F131">
-        <v>121071.915388</v>
+        <v>2557832</v>
       </c>
       <c r="H131" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J131" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K131" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L131">
-        <v>121071915.388</v>
+        <v>2557832000</v>
       </c>
       <c r="M131" t="s">
         <v>314</v>
       </c>
       <c r="N131" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O131" t="s">
         <v>327</v>
@@ -7181,31 +7187,31 @@
         <v>190</v>
       </c>
       <c r="D132" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E132" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F132">
-        <v>1361713.858312</v>
+        <v>674524386</v>
       </c>
       <c r="H132" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J132" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K132" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L132">
-        <v>1361713858.312</v>
+        <v>2428287789.6</v>
       </c>
       <c r="M132" t="s">
         <v>314</v>
       </c>
       <c r="N132" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="O132" t="s">
         <v>327</v>
@@ -7225,31 +7231,31 @@
         <v>190</v>
       </c>
       <c r="D133" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E133" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F133">
-        <v>5528.5667</v>
+        <v>42833</v>
       </c>
       <c r="H133" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J133" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K133" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L133">
-        <v>5528566.7</v>
+        <v>42833000</v>
       </c>
       <c r="M133" t="s">
         <v>314</v>
       </c>
       <c r="N133" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O133" t="s">
         <v>327</v>
@@ -7269,31 +7275,31 @@
         <v>190</v>
       </c>
       <c r="D134" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E134" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F134">
-        <v>1274584.3416</v>
+        <v>162805</v>
       </c>
       <c r="H134" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J134" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K134" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L134">
-        <v>1274584341.6</v>
+        <v>162805000</v>
       </c>
       <c r="M134" t="s">
         <v>314</v>
       </c>
       <c r="N134" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O134" t="s">
         <v>327</v>
@@ -7313,31 +7319,31 @@
         <v>190</v>
       </c>
       <c r="D135" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E135" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F135">
-        <v>25050.76</v>
+        <v>1463.60937</v>
       </c>
       <c r="H135" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J135" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K135" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L135">
-        <v>25050760</v>
+        <v>1463609.37</v>
       </c>
       <c r="M135" t="s">
         <v>314</v>
       </c>
       <c r="N135" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O135" t="s">
         <v>327</v>
@@ -7357,31 +7363,31 @@
         <v>190</v>
       </c>
       <c r="D136" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="E136" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F136">
-        <v>80313.18580000001</v>
+        <v>191632</v>
       </c>
       <c r="H136" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="J136" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="K136" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="L136">
-        <v>80313185.80000001</v>
+        <v>191632000</v>
       </c>
       <c r="M136" t="s">
         <v>314</v>
       </c>
       <c r="N136" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O136" t="s">
         <v>327</v>
@@ -7395,37 +7401,37 @@
         <v>151</v>
       </c>
       <c r="B137">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C137" t="s">
         <v>190</v>
       </c>
       <c r="D137" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="E137" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F137">
-        <v>3116555.8</v>
+        <v>181</v>
       </c>
       <c r="H137" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J137" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K137" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L137">
-        <v>111899935.999</v>
+        <v>181000</v>
       </c>
       <c r="M137" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N137" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="O137" t="s">
         <v>327</v>
@@ -7439,7 +7445,7 @@
         <v>152</v>
       </c>
       <c r="B138">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C138" t="s">
         <v>190</v>
@@ -7451,19 +7457,19 @@
         <v>226</v>
       </c>
       <c r="F138">
-        <v>248298644.3585</v>
+        <v>276713</v>
       </c>
       <c r="H138" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J138" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K138" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L138">
-        <v>893875119.6906</v>
+        <v>276713000</v>
       </c>
       <c r="M138" t="s">
         <v>314</v>
@@ -7483,37 +7489,37 @@
         <v>153</v>
       </c>
       <c r="B139">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C139" t="s">
         <v>190</v>
       </c>
       <c r="D139" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E139" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F139">
-        <v>151631.5</v>
+        <v>3549</v>
       </c>
       <c r="H139" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J139" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K139" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L139">
-        <v>4970480.57</v>
+        <v>3549000</v>
       </c>
       <c r="M139" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N139" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O139" t="s">
         <v>327</v>
@@ -7527,37 +7533,37 @@
         <v>154</v>
       </c>
       <c r="B140">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C140" t="s">
         <v>190</v>
       </c>
       <c r="D140" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E140" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F140">
-        <v>640677.799999999</v>
+        <v>45</v>
       </c>
       <c r="H140" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J140" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K140" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L140">
-        <v>14655632.81055998</v>
+        <v>45000</v>
       </c>
       <c r="M140" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N140" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="O140" t="s">
         <v>327</v>
@@ -7571,37 +7577,37 @@
         <v>155</v>
       </c>
       <c r="B141">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C141" t="s">
         <v>190</v>
       </c>
       <c r="D141" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E141" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F141">
-        <v>307233</v>
+        <v>187</v>
       </c>
       <c r="H141" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J141" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K141" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L141">
-        <v>307233000</v>
+        <v>187000</v>
       </c>
       <c r="M141" t="s">
         <v>314</v>
       </c>
       <c r="N141" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O141" t="s">
         <v>327</v>
@@ -7621,31 +7627,31 @@
         <v>190</v>
       </c>
       <c r="D142" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E142" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F142">
-        <v>432</v>
+        <v>76904</v>
       </c>
       <c r="H142" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J142" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K142" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L142">
-        <v>432000000</v>
+        <v>76904000</v>
       </c>
       <c r="M142" t="s">
         <v>314</v>
       </c>
       <c r="N142" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O142" t="s">
         <v>327</v>
@@ -7665,16 +7671,16 @@
         <v>190</v>
       </c>
       <c r="D143" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="E143" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F143">
-        <v>1233</v>
+        <v>409793</v>
       </c>
       <c r="H143" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J143" t="s">
         <v>291</v>
@@ -7683,13 +7689,13 @@
         <v>310</v>
       </c>
       <c r="L143">
-        <v>1233000000</v>
+        <v>55697075.44526765</v>
       </c>
       <c r="M143" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N143" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="O143" t="s">
         <v>327</v>
@@ -7709,31 +7715,31 @@
         <v>190</v>
       </c>
       <c r="D144" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="E144" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F144">
-        <v>12</v>
+        <v>17595388</v>
       </c>
       <c r="H144" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J144" t="s">
         <v>291</v>
       </c>
       <c r="K144" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L144">
-        <v>12000000</v>
+        <v>63343396.8</v>
       </c>
       <c r="M144" t="s">
         <v>314</v>
       </c>
       <c r="N144" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O144" t="s">
         <v>327</v>
@@ -7753,31 +7759,31 @@
         <v>190</v>
       </c>
       <c r="D145" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E145" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F145">
-        <v>1058</v>
+        <v>67158</v>
       </c>
       <c r="H145" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J145" t="s">
         <v>291</v>
       </c>
       <c r="K145" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L145">
-        <v>1058000000</v>
+        <v>8333350.1134884</v>
       </c>
       <c r="M145" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N145" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O145" t="s">
         <v>327</v>
@@ -7797,31 +7803,31 @@
         <v>190</v>
       </c>
       <c r="D146" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E146" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>422621</v>
       </c>
       <c r="H146" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J146" t="s">
         <v>291</v>
       </c>
       <c r="K146" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L146">
-        <v>1000000</v>
+        <v>36595602.20983067</v>
       </c>
       <c r="M146" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N146" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O146" t="s">
         <v>327</v>
@@ -7841,31 +7847,31 @@
         <v>190</v>
       </c>
       <c r="D147" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E147" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F147">
-        <v>131655</v>
+        <v>3590887</v>
       </c>
       <c r="I147" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J147" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="K147" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="L147">
-        <v>131655000</v>
+        <v>3590887000</v>
       </c>
       <c r="M147" t="s">
         <v>314</v>
       </c>
       <c r="N147" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O147" t="s">
         <v>327</v>
@@ -7885,31 +7891,31 @@
         <v>190</v>
       </c>
       <c r="D148" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E148" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F148">
-        <v>452775</v>
+        <v>164987364</v>
       </c>
       <c r="I148" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J148" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="K148" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="L148">
-        <v>1629990</v>
+        <v>593954510.4</v>
       </c>
       <c r="M148" t="s">
         <v>314</v>
       </c>
       <c r="N148" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="O148" t="s">
         <v>327</v>
@@ -7929,25 +7935,25 @@
         <v>190</v>
       </c>
       <c r="D149" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E149" t="s">
         <v>226</v>
       </c>
       <c r="F149">
-        <v>53673624</v>
+        <v>45318</v>
       </c>
       <c r="I149" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J149" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="K149" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="L149">
-        <v>193225046.4</v>
+        <v>45318000</v>
       </c>
       <c r="M149" t="s">
         <v>314</v>
@@ -7973,34 +7979,31 @@
         <v>190</v>
       </c>
       <c r="D150" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="E150" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F150">
-        <v>10277</v>
-      </c>
-      <c r="G150" t="s">
-        <v>242</v>
+        <v>51161</v>
       </c>
       <c r="I150" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J150" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="K150" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="L150">
-        <v>10277000</v>
+        <v>51161000</v>
       </c>
       <c r="M150" t="s">
         <v>314</v>
       </c>
       <c r="N150" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O150" t="s">
         <v>327</v>
@@ -8020,31 +8023,31 @@
         <v>190</v>
       </c>
       <c r="D151" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="E151" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F151">
-        <v>40177</v>
+        <v>7311</v>
       </c>
       <c r="I151" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J151" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="K151" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="L151">
-        <v>40177000</v>
+        <v>7311000</v>
       </c>
       <c r="M151" t="s">
         <v>314</v>
       </c>
       <c r="N151" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O151" t="s">
         <v>327</v>
@@ -8064,34 +8067,31 @@
         <v>190</v>
       </c>
       <c r="D152" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E152" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F152">
-        <v>387.2</v>
-      </c>
-      <c r="G152" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I152" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="J152" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K152" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L152">
-        <v>387200000</v>
+        <v>235000</v>
       </c>
       <c r="M152" t="s">
         <v>314</v>
       </c>
       <c r="N152" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O152" t="s">
         <v>327</v>
@@ -8111,31 +8111,31 @@
         <v>190</v>
       </c>
       <c r="D153" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E153" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F153">
-        <v>764</v>
+        <v>23524.43667</v>
       </c>
       <c r="I153" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J153" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K153" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L153">
-        <v>764000000</v>
+        <v>23524436.67</v>
       </c>
       <c r="M153" t="s">
         <v>314</v>
       </c>
       <c r="N153" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O153" t="s">
         <v>327</v>
@@ -8155,34 +8155,31 @@
         <v>190</v>
       </c>
       <c r="D154" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E154" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F154">
-        <v>1.76</v>
-      </c>
-      <c r="G154" t="s">
-        <v>236</v>
+        <v>623021.8686</v>
       </c>
       <c r="I154" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J154" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K154" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L154">
-        <v>1760000</v>
+        <v>623021868.6</v>
       </c>
       <c r="M154" t="s">
         <v>314</v>
       </c>
       <c r="N154" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O154" t="s">
         <v>327</v>
@@ -8202,34 +8199,31 @@
         <v>190</v>
       </c>
       <c r="D155" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E155" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F155">
-        <v>48.4</v>
-      </c>
-      <c r="G155" t="s">
-        <v>236</v>
+        <v>91025.48226</v>
       </c>
       <c r="I155" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J155" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K155" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L155">
-        <v>48400000</v>
+        <v>91025482.26000001</v>
       </c>
       <c r="M155" t="s">
         <v>314</v>
       </c>
       <c r="N155" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O155" t="s">
         <v>327</v>
@@ -8249,31 +8243,31 @@
         <v>190</v>
       </c>
       <c r="D156" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E156" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F156">
-        <v>20.7</v>
+        <v>723967.2</v>
       </c>
       <c r="I156" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J156" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="K156" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="L156">
-        <v>20700</v>
+        <v>723967200</v>
       </c>
       <c r="M156" t="s">
         <v>314</v>
       </c>
       <c r="N156" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O156" t="s">
         <v>327</v>
@@ -8296,28 +8290,28 @@
         <v>193</v>
       </c>
       <c r="E157" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F157">
-        <v>384285.8</v>
+        <v>17195.8465</v>
       </c>
       <c r="I157" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J157" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="K157" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="L157">
-        <v>384285800</v>
+        <v>17195846.5</v>
       </c>
       <c r="M157" t="s">
         <v>314</v>
       </c>
       <c r="N157" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O157" t="s">
         <v>327</v>
@@ -8337,31 +8331,31 @@
         <v>190</v>
       </c>
       <c r="D158" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="E158" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F158">
-        <v>4889.799999999999</v>
+        <v>166705</v>
       </c>
       <c r="I158" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J158" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="K158" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="L158">
-        <v>4889799.999999999</v>
+        <v>166705000</v>
       </c>
       <c r="M158" t="s">
         <v>314</v>
       </c>
       <c r="N158" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O158" t="s">
         <v>327</v>
@@ -8381,31 +8375,31 @@
         <v>190</v>
       </c>
       <c r="D159" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E159" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F159">
-        <v>738226.8</v>
+        <v>6336.05807</v>
       </c>
       <c r="I159" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J159" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="K159" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="L159">
-        <v>738226800</v>
+        <v>6336058.07</v>
       </c>
       <c r="M159" t="s">
         <v>314</v>
       </c>
       <c r="N159" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O159" t="s">
         <v>327</v>
@@ -8425,19 +8419,16 @@
         <v>190</v>
       </c>
       <c r="D160" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="E160" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F160">
-        <v>2026.3</v>
-      </c>
-      <c r="G160" t="s">
-        <v>243</v>
+        <v>131655</v>
       </c>
       <c r="I160" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J160" t="s">
         <v>293</v>
@@ -8446,13 +8437,13 @@
         <v>312</v>
       </c>
       <c r="L160">
-        <v>2026300</v>
+        <v>131655000</v>
       </c>
       <c r="M160" t="s">
         <v>314</v>
       </c>
       <c r="N160" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O160" t="s">
         <v>327</v>
@@ -8472,16 +8463,16 @@
         <v>190</v>
       </c>
       <c r="D161" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E161" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F161">
-        <v>2946.1</v>
+        <v>452775</v>
       </c>
       <c r="I161" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J161" t="s">
         <v>293</v>
@@ -8490,13 +8481,13 @@
         <v>312</v>
       </c>
       <c r="L161">
-        <v>2946100</v>
+        <v>1629990</v>
       </c>
       <c r="M161" t="s">
         <v>314</v>
       </c>
       <c r="N161" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="O161" t="s">
         <v>327</v>
@@ -8516,16 +8507,16 @@
         <v>190</v>
       </c>
       <c r="D162" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E162" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F162">
-        <v>159325.59885</v>
+        <v>53673624</v>
       </c>
       <c r="I162" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J162" t="s">
         <v>293</v>
@@ -8534,13 +8525,13 @@
         <v>312</v>
       </c>
       <c r="L162">
-        <v>159325598.85</v>
+        <v>193225046.4</v>
       </c>
       <c r="M162" t="s">
         <v>314</v>
       </c>
       <c r="N162" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="O162" t="s">
         <v>327</v>
@@ -8560,34 +8551,34 @@
         <v>190</v>
       </c>
       <c r="D163" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E163" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F163">
-        <v>1530.9</v>
+        <v>10277</v>
       </c>
       <c r="G163" t="s">
         <v>243</v>
       </c>
-      <c r="H163" t="s">
-        <v>270</v>
+      <c r="I163" t="s">
+        <v>274</v>
       </c>
       <c r="J163" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K163" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L163">
-        <v>1530900</v>
+        <v>10277000</v>
       </c>
       <c r="M163" t="s">
         <v>314</v>
       </c>
       <c r="N163" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O163" t="s">
         <v>327</v>
@@ -8607,31 +8598,31 @@
         <v>190</v>
       </c>
       <c r="D164" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E164" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F164">
-        <v>206946</v>
-      </c>
-      <c r="H164" t="s">
-        <v>270</v>
+        <v>40177</v>
+      </c>
+      <c r="I164" t="s">
+        <v>274</v>
       </c>
       <c r="J164" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K164" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L164">
-        <v>206946000</v>
+        <v>40177000</v>
       </c>
       <c r="M164" t="s">
         <v>314</v>
       </c>
       <c r="N164" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O164" t="s">
         <v>327</v>
@@ -8651,25 +8642,28 @@
         <v>190</v>
       </c>
       <c r="D165" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E165" t="s">
         <v>225</v>
       </c>
       <c r="F165">
-        <v>525946.7</v>
-      </c>
-      <c r="H165" t="s">
-        <v>270</v>
+        <v>387.2</v>
+      </c>
+      <c r="G165" t="s">
+        <v>235</v>
+      </c>
+      <c r="I165" t="s">
+        <v>275</v>
       </c>
       <c r="J165" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="K165" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="L165">
-        <v>525946699.9999999</v>
+        <v>387200000</v>
       </c>
       <c r="M165" t="s">
         <v>314</v>
@@ -8695,28 +8689,25 @@
         <v>190</v>
       </c>
       <c r="D166" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="E166" t="s">
         <v>225</v>
       </c>
       <c r="F166">
-        <v>4260.6</v>
-      </c>
-      <c r="G166" t="s">
-        <v>243</v>
-      </c>
-      <c r="H166" t="s">
-        <v>270</v>
+        <v>764</v>
+      </c>
+      <c r="I166" t="s">
+        <v>275</v>
       </c>
       <c r="J166" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="K166" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="L166">
-        <v>4260600</v>
+        <v>764000000</v>
       </c>
       <c r="M166" t="s">
         <v>314</v>
@@ -8742,25 +8733,28 @@
         <v>190</v>
       </c>
       <c r="D167" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E167" t="s">
         <v>225</v>
       </c>
       <c r="F167">
-        <v>3350.8</v>
-      </c>
-      <c r="H167" t="s">
-        <v>270</v>
+        <v>1.76</v>
+      </c>
+      <c r="G167" t="s">
+        <v>235</v>
+      </c>
+      <c r="I167" t="s">
+        <v>275</v>
       </c>
       <c r="J167" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="K167" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="L167">
-        <v>3350800</v>
+        <v>1760000</v>
       </c>
       <c r="M167" t="s">
         <v>314</v>
@@ -8786,25 +8780,28 @@
         <v>190</v>
       </c>
       <c r="D168" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E168" t="s">
         <v>225</v>
       </c>
       <c r="F168">
-        <v>63958.3</v>
-      </c>
-      <c r="H168" t="s">
-        <v>270</v>
+        <v>48.4</v>
+      </c>
+      <c r="G168" t="s">
+        <v>235</v>
+      </c>
+      <c r="I168" t="s">
+        <v>275</v>
       </c>
       <c r="J168" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="K168" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="L168">
-        <v>63958300</v>
+        <v>48400000</v>
       </c>
       <c r="M168" t="s">
         <v>314</v>
@@ -8830,16 +8827,16 @@
         <v>190</v>
       </c>
       <c r="D169" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="E169" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F169">
-        <v>33</v>
-      </c>
-      <c r="H169" t="s">
-        <v>270</v>
+        <v>20.7</v>
+      </c>
+      <c r="I169" t="s">
+        <v>276</v>
       </c>
       <c r="J169" t="s">
         <v>294</v>
@@ -8848,13 +8845,13 @@
         <v>313</v>
       </c>
       <c r="L169">
-        <v>33000</v>
+        <v>20700</v>
       </c>
       <c r="M169" t="s">
         <v>314</v>
       </c>
       <c r="N169" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O169" t="s">
         <v>327</v>
@@ -8874,31 +8871,31 @@
         <v>190</v>
       </c>
       <c r="D170" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E170" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F170">
-        <v>140100</v>
-      </c>
-      <c r="H170" t="s">
-        <v>271</v>
+        <v>384285.8</v>
+      </c>
+      <c r="I170" t="s">
+        <v>276</v>
       </c>
       <c r="J170" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="K170" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="L170">
-        <v>140100000</v>
+        <v>384285800</v>
       </c>
       <c r="M170" t="s">
         <v>314</v>
       </c>
       <c r="N170" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O170" t="s">
         <v>327</v>
@@ -8918,31 +8915,31 @@
         <v>190</v>
       </c>
       <c r="D171" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="E171" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F171">
-        <v>475</v>
-      </c>
-      <c r="H171" t="s">
-        <v>271</v>
+        <v>4889.8</v>
+      </c>
+      <c r="I171" t="s">
+        <v>276</v>
       </c>
       <c r="J171" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="K171" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="L171">
-        <v>475000</v>
+        <v>4889800</v>
       </c>
       <c r="M171" t="s">
         <v>314</v>
       </c>
       <c r="N171" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O171" t="s">
         <v>327</v>
@@ -8965,28 +8962,28 @@
         <v>195</v>
       </c>
       <c r="E172" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F172">
-        <v>960748</v>
-      </c>
-      <c r="H172" t="s">
-        <v>271</v>
+        <v>738226.8</v>
+      </c>
+      <c r="I172" t="s">
+        <v>276</v>
       </c>
       <c r="J172" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="K172" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="L172">
-        <v>960748000</v>
+        <v>738226800</v>
       </c>
       <c r="M172" t="s">
         <v>314</v>
       </c>
       <c r="N172" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O172" t="s">
         <v>327</v>
@@ -9006,31 +9003,34 @@
         <v>190</v>
       </c>
       <c r="D173" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="E173" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F173">
-        <v>2124</v>
-      </c>
-      <c r="H173" t="s">
-        <v>271</v>
+        <v>2026.3</v>
+      </c>
+      <c r="G173" t="s">
+        <v>241</v>
+      </c>
+      <c r="I173" t="s">
+        <v>276</v>
       </c>
       <c r="J173" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="K173" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="L173">
-        <v>2124000</v>
+        <v>2026300</v>
       </c>
       <c r="M173" t="s">
         <v>314</v>
       </c>
       <c r="N173" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O173" t="s">
         <v>327</v>
@@ -9050,31 +9050,31 @@
         <v>190</v>
       </c>
       <c r="D174" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="E174" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F174">
-        <v>6344</v>
-      </c>
-      <c r="H174" t="s">
-        <v>271</v>
+        <v>2946.1</v>
+      </c>
+      <c r="I174" t="s">
+        <v>276</v>
       </c>
       <c r="J174" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="K174" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="L174">
-        <v>6344000</v>
+        <v>2946100</v>
       </c>
       <c r="M174" t="s">
         <v>314</v>
       </c>
       <c r="N174" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O174" t="s">
         <v>327</v>
@@ -9094,31 +9094,31 @@
         <v>190</v>
       </c>
       <c r="D175" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E175" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F175">
-        <v>221612</v>
-      </c>
-      <c r="H175" t="s">
-        <v>271</v>
+        <v>159325.5989</v>
+      </c>
+      <c r="I175" t="s">
+        <v>276</v>
       </c>
       <c r="J175" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="K175" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="L175">
-        <v>221612000</v>
+        <v>159325598.9</v>
       </c>
       <c r="M175" t="s">
         <v>314</v>
       </c>
       <c r="N175" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O175" t="s">
         <v>327</v>

--- a/data/MetalliCan/pre_cleaned_data/energy_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/energy_df.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_06E102EAE69B89393F2C4C89E56F3D3778793165" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11E3CC33-E4E7-4161-8775-83D57390EA76}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1003,8 +1012,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1067,13 +1076,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1111,7 +1128,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1145,6 +1162,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1179,9 +1197,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1354,11 +1373,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P175"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="180.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="68.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1408,7 +1445,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1425,7 +1462,7 @@
         <v>225</v>
       </c>
       <c r="F2">
-        <v>80.95999999999999</v>
+        <v>80.959999999999994</v>
       </c>
       <c r="G2" t="s">
         <v>235</v>
@@ -1455,7 +1492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1499,7 +1536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1516,7 +1553,7 @@
         <v>225</v>
       </c>
       <c r="F4">
-        <v>0.368</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="G4" t="s">
         <v>235</v>
@@ -1546,7 +1583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1563,7 +1600,7 @@
         <v>225</v>
       </c>
       <c r="F5">
-        <v>10.12</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="G5" t="s">
         <v>235</v>
@@ -1593,7 +1630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1637,7 +1674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1681,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1725,7 +1762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1769,7 +1806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1813,7 +1850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1830,7 +1867,7 @@
         <v>226</v>
       </c>
       <c r="F11">
-        <v>18.47565065</v>
+        <v>18.475650649999999</v>
       </c>
       <c r="H11" t="s">
         <v>246</v>
@@ -1857,7 +1894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1874,7 +1911,7 @@
         <v>226</v>
       </c>
       <c r="F12">
-        <v>72676.11079000001</v>
+        <v>72676.110790000006</v>
       </c>
       <c r="H12" t="s">
         <v>246</v>
@@ -1886,7 +1923,7 @@
         <v>297</v>
       </c>
       <c r="L12">
-        <v>72676110.79000001</v>
+        <v>72676110.790000007</v>
       </c>
       <c r="M12" t="s">
         <v>314</v>
@@ -1901,7 +1938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -1930,7 +1967,7 @@
         <v>297</v>
       </c>
       <c r="L13">
-        <v>287042447.2</v>
+        <v>287042447.19999999</v>
       </c>
       <c r="M13" t="s">
         <v>314</v>
@@ -1945,7 +1982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1962,7 +1999,7 @@
         <v>226</v>
       </c>
       <c r="F14">
-        <v>86225.1174</v>
+        <v>86225.117400000003</v>
       </c>
       <c r="H14" t="s">
         <v>246</v>
@@ -1974,7 +2011,7 @@
         <v>297</v>
       </c>
       <c r="L14">
-        <v>86225117.40000001</v>
+        <v>86225117.400000006</v>
       </c>
       <c r="M14" t="s">
         <v>314</v>
@@ -1989,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -2006,7 +2043,7 @@
         <v>226</v>
       </c>
       <c r="F15">
-        <v>569009.5848</v>
+        <v>569009.58479999995</v>
       </c>
       <c r="H15" t="s">
         <v>246</v>
@@ -2018,7 +2055,7 @@
         <v>297</v>
       </c>
       <c r="L15">
-        <v>569009584.8</v>
+        <v>569009584.79999995</v>
       </c>
       <c r="M15" t="s">
         <v>314</v>
@@ -2033,7 +2070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2077,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -2094,7 +2131,7 @@
         <v>226</v>
       </c>
       <c r="F17">
-        <v>42071.0413</v>
+        <v>42071.041299999997</v>
       </c>
       <c r="H17" t="s">
         <v>246</v>
@@ -2106,7 +2143,7 @@
         <v>297</v>
       </c>
       <c r="L17">
-        <v>42071041.3</v>
+        <v>42071041.299999997</v>
       </c>
       <c r="M17" t="s">
         <v>314</v>
@@ -2121,7 +2158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -2138,7 +2175,7 @@
         <v>226</v>
       </c>
       <c r="F18">
-        <v>2344.0244</v>
+        <v>2344.0243999999998</v>
       </c>
       <c r="H18" t="s">
         <v>246</v>
@@ -2165,7 +2202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -2209,7 +2246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -2238,7 +2275,7 @@
         <v>297</v>
       </c>
       <c r="L20">
-        <v>121071915.4</v>
+        <v>121071915.40000001</v>
       </c>
       <c r="M20" t="s">
         <v>314</v>
@@ -2253,7 +2290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -2297,7 +2334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -2314,7 +2351,7 @@
         <v>226</v>
       </c>
       <c r="F22">
-        <v>5528.5667</v>
+        <v>5528.5667000000003</v>
       </c>
       <c r="H22" t="s">
         <v>247</v>
@@ -2326,7 +2363,7 @@
         <v>297</v>
       </c>
       <c r="L22">
-        <v>5528566.7</v>
+        <v>5528566.7000000002</v>
       </c>
       <c r="M22" t="s">
         <v>314</v>
@@ -2341,7 +2378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -2358,7 +2395,7 @@
         <v>226</v>
       </c>
       <c r="F23">
-        <v>1274584.342</v>
+        <v>1274584.3419999999</v>
       </c>
       <c r="H23" t="s">
         <v>247</v>
@@ -2385,7 +2422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -2429,7 +2466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -2446,7 +2483,7 @@
         <v>226</v>
       </c>
       <c r="F25">
-        <v>80313.18580000001</v>
+        <v>80313.185800000007</v>
       </c>
       <c r="H25" t="s">
         <v>247</v>
@@ -2458,7 +2495,7 @@
         <v>297</v>
       </c>
       <c r="L25">
-        <v>80313185.80000001</v>
+        <v>80313185.800000012</v>
       </c>
       <c r="M25" t="s">
         <v>314</v>
@@ -2473,7 +2510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -2490,7 +2527,7 @@
         <v>227</v>
       </c>
       <c r="F26">
-        <v>4761600.1</v>
+        <v>4761600.0999999996</v>
       </c>
       <c r="H26" t="s">
         <v>248</v>
@@ -2517,7 +2554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -2534,7 +2571,7 @@
         <v>226</v>
       </c>
       <c r="F27">
-        <v>56414.6765</v>
+        <v>56414.676500000001</v>
       </c>
       <c r="H27" t="s">
         <v>248</v>
@@ -2561,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2605,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -2649,7 +2686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -2678,7 +2715,7 @@
         <v>298</v>
       </c>
       <c r="L30">
-        <v>3914535.152</v>
+        <v>3914535.1519999998</v>
       </c>
       <c r="M30" t="s">
         <v>315</v>
@@ -2693,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -2737,7 +2774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -2766,7 +2803,7 @@
         <v>298</v>
       </c>
       <c r="L32">
-        <v>710263.5224</v>
+        <v>710263.52240000002</v>
       </c>
       <c r="M32" t="s">
         <v>315</v>
@@ -2781,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -2798,7 +2835,7 @@
         <v>226</v>
       </c>
       <c r="F33">
-        <v>929608.637</v>
+        <v>929608.63699999999</v>
       </c>
       <c r="G33" t="s">
         <v>236</v>
@@ -2828,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -2860,7 +2897,7 @@
         <v>299</v>
       </c>
       <c r="L34">
-        <v>365541666.7</v>
+        <v>365541666.69999999</v>
       </c>
       <c r="M34" t="s">
         <v>314</v>
@@ -2875,7 +2912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -2904,7 +2941,7 @@
         <v>299</v>
       </c>
       <c r="L35">
-        <v>36282051.28</v>
+        <v>36282051.280000001</v>
       </c>
       <c r="M35" t="s">
         <v>314</v>
@@ -2919,7 +2956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -2966,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -3013,7 +3050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>52</v>
       </c>
@@ -3030,7 +3067,7 @@
         <v>226</v>
       </c>
       <c r="F38">
-        <v>22737.89649</v>
+        <v>22737.896489999999</v>
       </c>
       <c r="G38" t="s">
         <v>236</v>
@@ -3045,7 +3082,7 @@
         <v>299</v>
       </c>
       <c r="L38">
-        <v>22737896.49</v>
+        <v>22737896.489999998</v>
       </c>
       <c r="M38" t="s">
         <v>314</v>
@@ -3060,7 +3097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -3104,7 +3141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -3148,7 +3185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -3192,7 +3229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>56</v>
       </c>
@@ -3236,7 +3273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>57</v>
       </c>
@@ -3280,7 +3317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -3327,7 +3364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -3371,7 +3408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -3400,7 +3437,7 @@
         <v>303</v>
       </c>
       <c r="L46">
-        <v>477755733.6</v>
+        <v>477755733.60000002</v>
       </c>
       <c r="M46" t="s">
         <v>314</v>
@@ -3415,7 +3452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -3459,7 +3496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>62</v>
       </c>
@@ -3503,7 +3540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>63</v>
       </c>
@@ -3520,7 +3557,7 @@
         <v>227</v>
       </c>
       <c r="F49">
-        <v>42378137.86</v>
+        <v>42378137.859999999</v>
       </c>
       <c r="H49" t="s">
         <v>253</v>
@@ -3532,7 +3569,7 @@
         <v>298</v>
       </c>
       <c r="L49">
-        <v>1521587039.8633</v>
+        <v>1521587039.8633001</v>
       </c>
       <c r="M49" t="s">
         <v>315</v>
@@ -3547,7 +3584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>64</v>
       </c>
@@ -3591,7 +3628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>65</v>
       </c>
@@ -3635,7 +3672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -3652,7 +3689,7 @@
         <v>227</v>
       </c>
       <c r="F52">
-        <v>1147190.1</v>
+        <v>1147190.1000000001</v>
       </c>
       <c r="H52" t="s">
         <v>253</v>
@@ -3679,7 +3716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>67</v>
       </c>
@@ -3708,7 +3745,7 @@
         <v>298</v>
       </c>
       <c r="L53">
-        <v>84441809.056336</v>
+        <v>84441809.056336001</v>
       </c>
       <c r="M53" t="s">
         <v>315</v>
@@ -3723,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -3767,7 +3804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>69</v>
       </c>
@@ -3811,7 +3848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -3855,7 +3892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>71</v>
       </c>
@@ -3899,7 +3936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -3943,7 +3980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>73</v>
       </c>
@@ -3987,7 +4024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -4031,7 +4068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>75</v>
       </c>
@@ -4075,7 +4112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>76</v>
       </c>
@@ -4119,7 +4156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -4163,7 +4200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>78</v>
       </c>
@@ -4207,7 +4244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>79</v>
       </c>
@@ -4251,7 +4288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>80</v>
       </c>
@@ -4295,7 +4332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>81</v>
       </c>
@@ -4339,7 +4376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>82</v>
       </c>
@@ -4383,7 +4420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -4427,7 +4464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>84</v>
       </c>
@@ -4471,7 +4508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>85</v>
       </c>
@@ -4515,7 +4552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>86</v>
       </c>
@@ -4559,7 +4596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>87</v>
       </c>
@@ -4603,7 +4640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>88</v>
       </c>
@@ -4620,7 +4657,7 @@
         <v>230</v>
       </c>
       <c r="F74">
-        <v>248298644.4</v>
+        <v>248298644.40000001</v>
       </c>
       <c r="H74" t="s">
         <v>258</v>
@@ -4632,7 +4669,7 @@
         <v>306</v>
       </c>
       <c r="L74">
-        <v>893875119.84</v>
+        <v>893875119.84000003</v>
       </c>
       <c r="M74" t="s">
         <v>314</v>
@@ -4647,7 +4684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>89</v>
       </c>
@@ -4691,7 +4728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>90</v>
       </c>
@@ -4708,7 +4745,7 @@
         <v>227</v>
       </c>
       <c r="F76">
-        <v>640677.8</v>
+        <v>640677.80000000005</v>
       </c>
       <c r="H76" t="s">
         <v>258</v>
@@ -4720,7 +4757,7 @@
         <v>306</v>
       </c>
       <c r="L76">
-        <v>14655632.81056</v>
+        <v>14655632.810559999</v>
       </c>
       <c r="M76" t="s">
         <v>315</v>
@@ -4735,7 +4772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>91</v>
       </c>
@@ -4779,7 +4816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>92</v>
       </c>
@@ -4823,7 +4860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>93</v>
       </c>
@@ -4867,7 +4904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -4911,7 +4948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>95</v>
       </c>
@@ -4955,7 +4992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>96</v>
       </c>
@@ -4984,7 +5021,7 @@
         <v>303</v>
       </c>
       <c r="L82">
-        <v>2991452173.2</v>
+        <v>2991452173.1999998</v>
       </c>
       <c r="M82" t="s">
         <v>314</v>
@@ -4999,7 +5036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>97</v>
       </c>
@@ -5043,7 +5080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -5087,7 +5124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>99</v>
       </c>
@@ -5131,7 +5168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>100</v>
       </c>
@@ -5175,7 +5212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>101</v>
       </c>
@@ -5192,7 +5229,7 @@
         <v>229</v>
       </c>
       <c r="F87">
-        <v>34190.62</v>
+        <v>34190.620000000003</v>
       </c>
       <c r="G87" t="s">
         <v>240</v>
@@ -5222,7 +5259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>102</v>
       </c>
@@ -5239,7 +5276,7 @@
         <v>229</v>
       </c>
       <c r="F88">
-        <v>38555.38</v>
+        <v>38555.379999999997</v>
       </c>
       <c r="G88" t="s">
         <v>240</v>
@@ -5269,7 +5306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>103</v>
       </c>
@@ -5313,7 +5350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>104</v>
       </c>
@@ -5342,7 +5379,7 @@
         <v>308</v>
       </c>
       <c r="L90">
-        <v>57828505.6</v>
+        <v>57828505.600000001</v>
       </c>
       <c r="M90" t="s">
         <v>315</v>
@@ -5357,7 +5394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>105</v>
       </c>
@@ -5374,7 +5411,7 @@
         <v>226</v>
       </c>
       <c r="F91">
-        <v>27653.22904</v>
+        <v>27653.229039999998</v>
       </c>
       <c r="H91" t="s">
         <v>262</v>
@@ -5386,7 +5423,7 @@
         <v>297</v>
       </c>
       <c r="L91">
-        <v>27653229.04</v>
+        <v>27653229.039999999</v>
       </c>
       <c r="M91" t="s">
         <v>314</v>
@@ -5401,7 +5438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>106</v>
       </c>
@@ -5445,7 +5482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>107</v>
       </c>
@@ -5462,7 +5499,7 @@
         <v>226</v>
       </c>
       <c r="F93">
-        <v>308614.7308</v>
+        <v>308614.73080000002</v>
       </c>
       <c r="H93" t="s">
         <v>262</v>
@@ -5474,7 +5511,7 @@
         <v>297</v>
       </c>
       <c r="L93">
-        <v>308614730.8</v>
+        <v>308614730.80000001</v>
       </c>
       <c r="M93" t="s">
         <v>314</v>
@@ -5489,7 +5526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>108</v>
       </c>
@@ -5506,7 +5543,7 @@
         <v>226</v>
       </c>
       <c r="F94">
-        <v>3808.984282</v>
+        <v>3808.9842819999999</v>
       </c>
       <c r="H94" t="s">
         <v>262</v>
@@ -5518,7 +5555,7 @@
         <v>297</v>
       </c>
       <c r="L94">
-        <v>3808984.282</v>
+        <v>3808984.2820000001</v>
       </c>
       <c r="M94" t="s">
         <v>314</v>
@@ -5533,7 +5570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>109</v>
       </c>
@@ -5577,7 +5614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>110</v>
       </c>
@@ -5594,7 +5631,7 @@
         <v>226</v>
       </c>
       <c r="F96">
-        <v>5437.635</v>
+        <v>5437.6350000000002</v>
       </c>
       <c r="H96" t="s">
         <v>262</v>
@@ -5621,7 +5658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>111</v>
       </c>
@@ -5638,7 +5675,7 @@
         <v>226</v>
       </c>
       <c r="F97">
-        <v>229891.869</v>
+        <v>229891.86900000001</v>
       </c>
       <c r="H97" t="s">
         <v>262</v>
@@ -5665,7 +5702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>112</v>
       </c>
@@ -5709,7 +5746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>113</v>
       </c>
@@ -5756,7 +5793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>114</v>
       </c>
@@ -5800,7 +5837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>115</v>
       </c>
@@ -5817,7 +5854,7 @@
         <v>226</v>
       </c>
       <c r="F101">
-        <v>525946.7</v>
+        <v>525946.69999999995</v>
       </c>
       <c r="H101" t="s">
         <v>263</v>
@@ -5829,7 +5866,7 @@
         <v>309</v>
       </c>
       <c r="L101">
-        <v>525946699.9999999</v>
+        <v>525946699.99999988</v>
       </c>
       <c r="M101" t="s">
         <v>314</v>
@@ -5844,7 +5881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>116</v>
       </c>
@@ -5861,7 +5898,7 @@
         <v>226</v>
       </c>
       <c r="F102">
-        <v>4260.6</v>
+        <v>4260.6000000000004</v>
       </c>
       <c r="G102" t="s">
         <v>241</v>
@@ -5891,7 +5928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>117</v>
       </c>
@@ -5935,7 +5972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>118</v>
       </c>
@@ -5979,7 +6016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>119</v>
       </c>
@@ -6023,7 +6060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>120</v>
       </c>
@@ -6040,7 +6077,7 @@
         <v>226</v>
       </c>
       <c r="F106">
-        <v>21662.09888</v>
+        <v>21662.098880000001</v>
       </c>
       <c r="H106" t="s">
         <v>264</v>
@@ -6052,7 +6089,7 @@
         <v>297</v>
       </c>
       <c r="L106">
-        <v>21662098.88</v>
+        <v>21662098.879999999</v>
       </c>
       <c r="M106" t="s">
         <v>314</v>
@@ -6067,7 +6104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>121</v>
       </c>
@@ -6084,7 +6121,7 @@
         <v>226</v>
       </c>
       <c r="F107">
-        <v>385327.7974</v>
+        <v>385327.79739999998</v>
       </c>
       <c r="H107" t="s">
         <v>264</v>
@@ -6096,7 +6133,7 @@
         <v>297</v>
       </c>
       <c r="L107">
-        <v>385327797.4</v>
+        <v>385327797.39999998</v>
       </c>
       <c r="M107" t="s">
         <v>314</v>
@@ -6111,7 +6148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>122</v>
       </c>
@@ -6155,7 +6192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>123</v>
       </c>
@@ -6172,7 +6209,7 @@
         <v>226</v>
       </c>
       <c r="F109">
-        <v>892229.9504</v>
+        <v>892229.95039999997</v>
       </c>
       <c r="H109" t="s">
         <v>264</v>
@@ -6184,7 +6221,7 @@
         <v>297</v>
       </c>
       <c r="L109">
-        <v>892229950.4</v>
+        <v>892229950.39999998</v>
       </c>
       <c r="M109" t="s">
         <v>314</v>
@@ -6199,7 +6236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>124</v>
       </c>
@@ -6216,7 +6253,7 @@
         <v>226</v>
       </c>
       <c r="F110">
-        <v>10018.1179</v>
+        <v>10018.117899999999</v>
       </c>
       <c r="H110" t="s">
         <v>264</v>
@@ -6243,7 +6280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>125</v>
       </c>
@@ -6260,7 +6297,7 @@
         <v>226</v>
       </c>
       <c r="F111">
-        <v>142393.1742</v>
+        <v>142393.17420000001</v>
       </c>
       <c r="H111" t="s">
         <v>264</v>
@@ -6272,7 +6309,7 @@
         <v>297</v>
       </c>
       <c r="L111">
-        <v>142393174.2</v>
+        <v>142393174.19999999</v>
       </c>
       <c r="M111" t="s">
         <v>314</v>
@@ -6287,7 +6324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>126</v>
       </c>
@@ -6331,7 +6368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>127</v>
       </c>
@@ -6378,7 +6415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>128</v>
       </c>
@@ -6425,7 +6462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>129</v>
       </c>
@@ -6469,7 +6506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>130</v>
       </c>
@@ -6516,7 +6553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>131</v>
       </c>
@@ -6545,7 +6582,7 @@
         <v>310</v>
       </c>
       <c r="L117">
-        <v>378542030.2939668</v>
+        <v>378542030.29396683</v>
       </c>
       <c r="M117" t="s">
         <v>315</v>
@@ -6560,7 +6597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>132</v>
       </c>
@@ -6589,7 +6626,7 @@
         <v>310</v>
       </c>
       <c r="L118">
-        <v>495635929.2</v>
+        <v>495635929.19999999</v>
       </c>
       <c r="M118" t="s">
         <v>314</v>
@@ -6604,7 +6641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>133</v>
       </c>
@@ -6633,7 +6670,7 @@
         <v>310</v>
       </c>
       <c r="L119">
-        <v>17908178.0536758</v>
+        <v>17908178.053675801</v>
       </c>
       <c r="M119" t="s">
         <v>315</v>
@@ -6648,7 +6685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>134</v>
       </c>
@@ -6677,7 +6714,7 @@
         <v>310</v>
       </c>
       <c r="L120">
-        <v>42813081.77158993</v>
+        <v>42813081.771589927</v>
       </c>
       <c r="M120" t="s">
         <v>315</v>
@@ -6692,7 +6729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>135</v>
       </c>
@@ -6736,7 +6773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>136</v>
       </c>
@@ -6780,7 +6817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>137</v>
       </c>
@@ -6824,7 +6861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>138</v>
       </c>
@@ -6868,7 +6905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>139</v>
       </c>
@@ -6912,7 +6949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>140</v>
       </c>
@@ -6956,7 +6993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>141</v>
       </c>
@@ -7000,7 +7037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>142</v>
       </c>
@@ -7044,7 +7081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>143</v>
       </c>
@@ -7088,7 +7125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>144</v>
       </c>
@@ -7132,7 +7169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -7176,7 +7213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>146</v>
       </c>
@@ -7205,7 +7242,7 @@
         <v>303</v>
       </c>
       <c r="L132">
-        <v>2428287789.6</v>
+        <v>2428287789.5999999</v>
       </c>
       <c r="M132" t="s">
         <v>314</v>
@@ -7220,7 +7257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>147</v>
       </c>
@@ -7264,7 +7301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>148</v>
       </c>
@@ -7308,7 +7345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>149</v>
       </c>
@@ -7325,7 +7362,7 @@
         <v>226</v>
       </c>
       <c r="F135">
-        <v>1463.60937</v>
+        <v>1463.6093699999999</v>
       </c>
       <c r="H135" t="s">
         <v>269</v>
@@ -7352,7 +7389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>150</v>
       </c>
@@ -7396,7 +7433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>151</v>
       </c>
@@ -7440,7 +7477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>152</v>
       </c>
@@ -7484,7 +7521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>153</v>
       </c>
@@ -7528,7 +7565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>154</v>
       </c>
@@ -7572,7 +7609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>155</v>
       </c>
@@ -7616,7 +7653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>156</v>
       </c>
@@ -7660,7 +7697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -7689,7 +7726,7 @@
         <v>310</v>
       </c>
       <c r="L143">
-        <v>55697075.44526765</v>
+        <v>55697075.445267648</v>
       </c>
       <c r="M143" t="s">
         <v>315</v>
@@ -7704,7 +7741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>158</v>
       </c>
@@ -7733,7 +7770,7 @@
         <v>310</v>
       </c>
       <c r="L144">
-        <v>63343396.8</v>
+        <v>63343396.799999997</v>
       </c>
       <c r="M144" t="s">
         <v>314</v>
@@ -7748,7 +7785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>159</v>
       </c>
@@ -7777,7 +7814,7 @@
         <v>310</v>
       </c>
       <c r="L145">
-        <v>8333350.1134884</v>
+        <v>8333350.1134884004</v>
       </c>
       <c r="M145" t="s">
         <v>315</v>
@@ -7792,7 +7829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>160</v>
       </c>
@@ -7821,7 +7858,7 @@
         <v>310</v>
       </c>
       <c r="L146">
-        <v>36595602.20983067</v>
+        <v>36595602.209830672</v>
       </c>
       <c r="M146" t="s">
         <v>315</v>
@@ -7836,7 +7873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>161</v>
       </c>
@@ -7880,7 +7917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>162</v>
       </c>
@@ -7909,7 +7946,7 @@
         <v>303</v>
       </c>
       <c r="L148">
-        <v>593954510.4</v>
+        <v>593954510.39999998</v>
       </c>
       <c r="M148" t="s">
         <v>314</v>
@@ -7924,7 +7961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>163</v>
       </c>
@@ -7968,7 +8005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>164</v>
       </c>
@@ -8012,7 +8049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>165</v>
       </c>
@@ -8056,7 +8093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>166</v>
       </c>
@@ -8100,7 +8137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>167</v>
       </c>
@@ -8117,7 +8154,7 @@
         <v>226</v>
       </c>
       <c r="F153">
-        <v>23524.43667</v>
+        <v>23524.436669999999</v>
       </c>
       <c r="I153" t="s">
         <v>273</v>
@@ -8129,7 +8166,7 @@
         <v>297</v>
       </c>
       <c r="L153">
-        <v>23524436.67</v>
+        <v>23524436.670000002</v>
       </c>
       <c r="M153" t="s">
         <v>314</v>
@@ -8144,7 +8181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>168</v>
       </c>
@@ -8161,7 +8198,7 @@
         <v>226</v>
       </c>
       <c r="F154">
-        <v>623021.8686</v>
+        <v>623021.86860000005</v>
       </c>
       <c r="I154" t="s">
         <v>273</v>
@@ -8173,7 +8210,7 @@
         <v>297</v>
       </c>
       <c r="L154">
-        <v>623021868.6</v>
+        <v>623021868.60000002</v>
       </c>
       <c r="M154" t="s">
         <v>314</v>
@@ -8188,7 +8225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>169</v>
       </c>
@@ -8205,7 +8242,7 @@
         <v>226</v>
       </c>
       <c r="F155">
-        <v>91025.48226</v>
+        <v>91025.482260000004</v>
       </c>
       <c r="I155" t="s">
         <v>273</v>
@@ -8217,7 +8254,7 @@
         <v>297</v>
       </c>
       <c r="L155">
-        <v>91025482.26000001</v>
+        <v>91025482.260000005</v>
       </c>
       <c r="M155" t="s">
         <v>314</v>
@@ -8232,7 +8269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>170</v>
       </c>
@@ -8276,7 +8313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>171</v>
       </c>
@@ -8320,7 +8357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>172</v>
       </c>
@@ -8364,7 +8401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>173</v>
       </c>
@@ -8393,7 +8430,7 @@
         <v>297</v>
       </c>
       <c r="L159">
-        <v>6336058.07</v>
+        <v>6336058.0700000003</v>
       </c>
       <c r="M159" t="s">
         <v>314</v>
@@ -8408,7 +8445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>174</v>
       </c>
@@ -8452,7 +8489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>175</v>
       </c>
@@ -8496,7 +8533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>176</v>
       </c>
@@ -8525,7 +8562,7 @@
         <v>312</v>
       </c>
       <c r="L162">
-        <v>193225046.4</v>
+        <v>193225046.40000001</v>
       </c>
       <c r="M162" t="s">
         <v>314</v>
@@ -8540,7 +8577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>177</v>
       </c>
@@ -8587,7 +8624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>178</v>
       </c>
@@ -8631,7 +8668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>179</v>
       </c>
@@ -8678,7 +8715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>180</v>
       </c>
@@ -8722,7 +8759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>181</v>
       </c>
@@ -8769,7 +8806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>182</v>
       </c>
@@ -8816,7 +8853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>183</v>
       </c>
@@ -8860,7 +8897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>184</v>
       </c>
@@ -8904,7 +8941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>185</v>
       </c>
@@ -8948,7 +8985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>186</v>
       </c>
@@ -8992,7 +9029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>187</v>
       </c>
@@ -9039,7 +9076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>188</v>
       </c>
@@ -9083,7 +9120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>189</v>
       </c>
@@ -9100,7 +9137,7 @@
         <v>226</v>
       </c>
       <c r="F175">
-        <v>159325.5989</v>
+        <v>159325.59890000001</v>
       </c>
       <c r="I175" t="s">
         <v>276</v>
@@ -9112,7 +9149,7 @@
         <v>313</v>
       </c>
       <c r="L175">
-        <v>159325598.9</v>
+        <v>159325598.90000001</v>
       </c>
       <c r="M175" t="s">
         <v>314</v>
@@ -9128,6 +9165,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MetalliCan/pre_cleaned_data/energy_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/energy_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="304">
   <si>
     <t>technosphere_id</t>
   </si>
@@ -136,9 +136,6 @@
     <t>TECH-aeafbb59-2023.0-2.0</t>
   </si>
   <si>
-    <t>TECH-aeafbb59-2023.0-3.0</t>
-  </si>
-  <si>
     <t>TECH-aeafbb59-2023.0-4.0</t>
   </si>
   <si>
@@ -199,9 +196,6 @@
     <t>TECH-c0660aec-2023.0-2.0</t>
   </si>
   <si>
-    <t>TECH-c0660aec-2023.0-3.0</t>
-  </si>
-  <si>
     <t>TECH-c0660aec-2023.0-4.0</t>
   </si>
   <si>
@@ -292,9 +286,6 @@
     <t>TECH-e51eda66-2023.0-2.0</t>
   </si>
   <si>
-    <t>TECH-e51eda66-2023.0-3.0</t>
-  </si>
-  <si>
     <t>TECH-e51eda66-2023.0-4.0</t>
   </si>
   <si>
@@ -307,9 +298,6 @@
     <t>TECH-1f126a43-2023.0-2.0</t>
   </si>
   <si>
-    <t>TECH-1f126a43-2023.0-3.0</t>
-  </si>
-  <si>
     <t>TECH-1f126a43-2023.0-4.0</t>
   </si>
   <si>
@@ -325,9 +313,6 @@
     <t>TECH-GRP-0a2c0d69-2023.0-2.0</t>
   </si>
   <si>
-    <t>TECH-GRP-0a2c0d69-2023.0-3.0</t>
-  </si>
-  <si>
     <t>TECH-GRP-0a2c0d69-2023.0-4.0</t>
   </si>
   <si>
@@ -343,9 +328,6 @@
     <t>TECH-8b0264c9-2023.0-2.0</t>
   </si>
   <si>
-    <t>TECH-8b0264c9-2023.0-3.0</t>
-  </si>
-  <si>
     <t>TECH-8b0264c9-2023.0-4.0</t>
   </si>
   <si>
@@ -358,9 +340,6 @@
     <t>TECH-ed23117f-nan-nan</t>
   </si>
   <si>
-    <t>TECH-ed23117f-2023.0-3.0</t>
-  </si>
-  <si>
     <t>TECH-ed23117f-2023.0-4.0</t>
   </si>
   <si>
@@ -400,9 +379,6 @@
     <t>TECH-aa76f6f2-2023.0-6.0</t>
   </si>
   <si>
-    <t>TECH-aa76f6f2-2023.0-7.0</t>
-  </si>
-  <si>
     <t>TECH-aa76f6f2-2023.0-9.0</t>
   </si>
   <si>
@@ -439,9 +415,6 @@
     <t>TECH-0aadf28f-2023.0-7.0</t>
   </si>
   <si>
-    <t>TECH-0aadf28f-2023.0-8.0</t>
-  </si>
-  <si>
     <t>TECH-0aadf28f-2023.0-10.0</t>
   </si>
   <si>
@@ -526,39 +499,24 @@
     <t>TECH-GRP-a13779f8-2023.0-4.0</t>
   </si>
   <si>
-    <t>TECH-GRP-147b3123-2023.0-1.0</t>
-  </si>
-  <si>
     <t>TECH-GRP-147b3123-2023.0-2.0</t>
   </si>
   <si>
-    <t>TECH-GRP-147b3123-2023.0-3.0</t>
-  </si>
-  <si>
     <t>TECH-GRP-147b3123-2023.0-4.0</t>
   </si>
   <si>
-    <t>TECH-GRP-147b3123-2023.0-5.0</t>
-  </si>
-  <si>
     <t>TECH-GRP-147b3123-2023.0-6.0</t>
   </si>
   <si>
     <t>TECH-GRP-147b3123-2023.0-7.0</t>
   </si>
   <si>
-    <t>TECH-02884fb5-2023.0-1.0</t>
-  </si>
-  <si>
     <t>TECH-02884fb5-2023.0-7.0</t>
   </si>
   <si>
     <t>TECH-02884fb5-2023.0-8.0</t>
   </si>
   <si>
-    <t>TECH-02884fb5-2023.0-9.0</t>
-  </si>
-  <si>
     <t>TECH-02884fb5-2023.0-12.0</t>
   </si>
   <si>
@@ -634,9 +592,6 @@
     <t>Electricity consumption</t>
   </si>
   <si>
-    <t>Explosives</t>
-  </si>
-  <si>
     <t>Electricity consumption|Non-renewable electricity use</t>
   </si>
   <si>
@@ -673,21 +628,6 @@
     <t>Other</t>
   </si>
   <si>
-    <t>Ammonium nitrate</t>
-  </si>
-  <si>
-    <t>Dynamite</t>
-  </si>
-  <si>
-    <t>Emulsions</t>
-  </si>
-  <si>
-    <t>ANFO</t>
-  </si>
-  <si>
-    <t>Emulsion ANFO</t>
-  </si>
-  <si>
     <t>Naphta</t>
   </si>
   <si>
@@ -718,9 +658,6 @@
     <t>l</t>
   </si>
   <si>
-    <t>kg</t>
-  </si>
-  <si>
     <t>No decomposition per energy type</t>
   </si>
   <si>
@@ -739,15 +676,9 @@
     <t>Data initially in tCO2eq; back calculated with emission factors: 74.1kgCO2eq/GJ for diesel, 69.9kgCO2eq/GJ for gasoline, 59.9kgCO2eq/GJ for propane, BC mix 12kgCO2eq/MWh. 62% of electricity come from the grid.</t>
   </si>
   <si>
-    <t>Data initially in tCO2eq; back calculated with emission factors: 74.1kgCO2eq/GJ for diesel, 69.9kgCO2eq/GJ for gasoline, 59.9kgCO2eq/GJ for propane, BC mix 12kgCO2eq/MWh, explosives 3.75GJ/tCO2</t>
-  </si>
-  <si>
     <t>Other types are electricity, diesel, natural gas, propane</t>
   </si>
   <si>
-    <t>Explosives, treated as energy consumption</t>
-  </si>
-  <si>
     <t>BC-MAIN-857b7b89</t>
   </si>
   <si>
@@ -992,9 +923,6 @@
   </si>
   <si>
     <t>gwh→MJ factor=3600000.0</t>
-  </si>
-  <si>
-    <t>explosives MJ/kg=4.0</t>
   </si>
   <si>
     <t>MJ</t>
@@ -1355,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P175"/>
+  <dimension ref="A1:P161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1416,37 +1344,37 @@
         <v>2023</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F2">
         <v>18.475650648</v>
       </c>
       <c r="H2" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="J2" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K2" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L2">
         <v>18475.650648</v>
       </c>
       <c r="M2" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N2" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O2" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -1460,37 +1388,37 @@
         <v>2023</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F3">
         <v>72676.1107896</v>
       </c>
       <c r="H3" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="J3" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K3" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L3">
         <v>72676110.7896</v>
       </c>
       <c r="M3" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N3" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O3" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -1504,37 +1432,37 @@
         <v>2023</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F4">
         <v>287042.447231542</v>
       </c>
       <c r="H4" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="J4" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K4" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L4">
         <v>287042447.2315421</v>
       </c>
       <c r="M4" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N4" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O4" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -1548,37 +1476,37 @@
         <v>2023</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D5" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F5">
         <v>86225.1173956</v>
       </c>
       <c r="H5" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="J5" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K5" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L5">
         <v>86225117.39559999</v>
       </c>
       <c r="M5" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N5" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O5" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -1592,37 +1520,37 @@
         <v>2023</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="E6" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F6">
         <v>569009.5848</v>
       </c>
       <c r="H6" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="J6" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K6" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L6">
         <v>569009584.8</v>
       </c>
       <c r="M6" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N6" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O6" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -1636,37 +1564,37 @@
         <v>2023</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E7" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F7">
         <v>13568.45</v>
       </c>
       <c r="H7" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="J7" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K7" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L7">
         <v>13568450</v>
       </c>
       <c r="M7" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N7" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O7" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -1680,37 +1608,37 @@
         <v>2023</v>
       </c>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D8" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="E8" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F8">
         <v>42071.0413</v>
       </c>
       <c r="H8" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="J8" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K8" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L8">
         <v>42071041.3</v>
       </c>
       <c r="M8" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N8" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O8" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -1724,37 +1652,37 @@
         <v>2023</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D9" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="E9" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F9">
         <v>2344.0244</v>
       </c>
       <c r="H9" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="J9" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K9" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L9">
         <v>2344024.4</v>
       </c>
       <c r="M9" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N9" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O9" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -1768,37 +1696,37 @@
         <v>2023</v>
       </c>
       <c r="C10" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D10" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E10" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F10">
         <v>2557832</v>
       </c>
       <c r="H10" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="J10" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K10" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L10">
         <v>2557832000</v>
       </c>
       <c r="M10" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N10" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O10" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -1812,37 +1740,37 @@
         <v>2023</v>
       </c>
       <c r="C11" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D11" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="E11" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="F11">
         <v>674524386</v>
       </c>
       <c r="H11" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="J11" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K11" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L11">
         <v>2428287789.6</v>
       </c>
       <c r="M11" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N11" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="O11" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
@@ -1856,37 +1784,37 @@
         <v>2023</v>
       </c>
       <c r="C12" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D12" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="E12" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F12">
         <v>42833</v>
       </c>
       <c r="H12" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="J12" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K12" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L12">
         <v>42833000</v>
       </c>
       <c r="M12" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N12" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O12" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -1900,37 +1828,37 @@
         <v>2023</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D13" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="E13" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F13">
         <v>162805</v>
       </c>
       <c r="H13" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="J13" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K13" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L13">
         <v>162805000</v>
       </c>
       <c r="M13" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N13" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O13" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
@@ -1944,37 +1872,37 @@
         <v>2023</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D14" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="E14" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F14">
         <v>1463.60937</v>
       </c>
       <c r="H14" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="J14" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K14" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L14">
         <v>1463609.37</v>
       </c>
       <c r="M14" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N14" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O14" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
@@ -1988,40 +1916,40 @@
         <v>2023</v>
       </c>
       <c r="C15" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D15" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="E15" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="F15">
         <v>4145000</v>
       </c>
       <c r="G15" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="H15" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="J15" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="K15" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="L15">
         <v>14922000000</v>
       </c>
       <c r="M15" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N15" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="O15" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -2035,37 +1963,37 @@
         <v>2023</v>
       </c>
       <c r="C16" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D16" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="E16" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="F16">
         <v>2785135</v>
       </c>
       <c r="H16" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="J16" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="K16" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="L16">
         <v>378542030.2939668</v>
       </c>
       <c r="M16" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="N16" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="O16" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
@@ -2079,37 +2007,37 @@
         <v>2023</v>
       </c>
       <c r="C17" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D17" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="E17" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="F17">
         <v>137676647</v>
       </c>
       <c r="H17" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="J17" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="K17" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="L17">
         <v>495635929.2</v>
       </c>
       <c r="M17" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N17" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="O17" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
@@ -2123,37 +2051,37 @@
         <v>2023</v>
       </c>
       <c r="C18" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" t="s">
         <v>190</v>
       </c>
-      <c r="D18" t="s">
-        <v>204</v>
-      </c>
       <c r="E18" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="F18">
         <v>144321</v>
       </c>
       <c r="H18" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="J18" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="K18" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="L18">
         <v>17908178.0536758</v>
       </c>
       <c r="M18" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="N18" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="O18" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -2167,37 +2095,37 @@
         <v>2023</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D19" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="E19" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="F19">
         <v>494423</v>
       </c>
       <c r="H19" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="J19" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="K19" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="L19">
         <v>42813081.77158993</v>
       </c>
       <c r="M19" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="N19" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="O19" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -2211,40 +2139,40 @@
         <v>2023</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E20" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="F20">
         <v>80.95999999999999</v>
       </c>
       <c r="G20" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="H20" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="J20" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="K20" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="L20">
         <v>80960000</v>
       </c>
       <c r="M20" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N20" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="O20" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
@@ -2258,37 +2186,37 @@
         <v>2023</v>
       </c>
       <c r="C21" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D21" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="F21">
         <v>1968</v>
       </c>
       <c r="H21" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="J21" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="K21" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="L21">
         <v>1968000000</v>
       </c>
       <c r="M21" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N21" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="O21" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
@@ -2302,40 +2230,40 @@
         <v>2023</v>
       </c>
       <c r="C22" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D22" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E22" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="F22">
         <v>0.368</v>
       </c>
       <c r="G22" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="H22" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="J22" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="K22" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="L22">
         <v>368000</v>
       </c>
       <c r="M22" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N22" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="O22" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P22" t="b">
         <v>0</v>
@@ -2349,40 +2277,40 @@
         <v>2023</v>
       </c>
       <c r="C23" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D23" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="E23" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="F23">
         <v>10.12</v>
       </c>
       <c r="G23" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="H23" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="J23" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="K23" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="L23">
         <v>10120000</v>
       </c>
       <c r="M23" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N23" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="O23" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
@@ -2396,37 +2324,37 @@
         <v>2023</v>
       </c>
       <c r="C24" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D24" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E24" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F24">
         <v>3947008</v>
       </c>
       <c r="H24" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="J24" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K24" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L24">
         <v>3947008000</v>
       </c>
       <c r="M24" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N24" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O24" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P24" t="b">
         <v>0</v>
@@ -2440,37 +2368,37 @@
         <v>2023</v>
       </c>
       <c r="C25" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D25" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="E25" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="F25">
         <v>830958937</v>
       </c>
       <c r="H25" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="J25" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K25" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L25">
         <v>2991452173.2</v>
       </c>
       <c r="M25" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N25" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="O25" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P25" t="b">
         <v>0</v>
@@ -2484,37 +2412,37 @@
         <v>2023</v>
       </c>
       <c r="C26" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D26" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="E26" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F26">
-        <v>65074</v>
+        <v>71904</v>
       </c>
       <c r="H26" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="J26" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K26" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L26">
-        <v>65074000</v>
+        <v>71904000</v>
       </c>
       <c r="M26" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N26" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O26" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P26" t="b">
         <v>0</v>
@@ -2528,37 +2456,37 @@
         <v>2023</v>
       </c>
       <c r="C27" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D27" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="E27" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F27">
-        <v>71904</v>
+        <v>182468</v>
       </c>
       <c r="H27" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="J27" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K27" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L27">
-        <v>71904000</v>
+        <v>182468000</v>
       </c>
       <c r="M27" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N27" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O27" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
@@ -2572,37 +2500,37 @@
         <v>2023</v>
       </c>
       <c r="C28" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D28" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="E28" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="F28">
-        <v>182468</v>
+        <v>2829</v>
       </c>
       <c r="H28" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="J28" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="K28" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="L28">
-        <v>182468000</v>
+        <v>101575245</v>
       </c>
       <c r="M28" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N28" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="O28" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
@@ -2616,37 +2544,40 @@
         <v>2023</v>
       </c>
       <c r="C29" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D29" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E29" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="F29">
-        <v>2829</v>
+        <v>34190.62</v>
+      </c>
+      <c r="G29" t="s">
+        <v>216</v>
       </c>
       <c r="H29" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="J29" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="K29" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="L29">
-        <v>101575245</v>
+        <v>123086232</v>
       </c>
       <c r="M29" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N29" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="O29" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P29" t="b">
         <v>0</v>
@@ -2660,40 +2591,40 @@
         <v>2023</v>
       </c>
       <c r="C30" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D30" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E30" t="s">
+        <v>207</v>
+      </c>
+      <c r="F30">
+        <v>38555.38</v>
+      </c>
+      <c r="G30" t="s">
+        <v>216</v>
+      </c>
+      <c r="H30" t="s">
         <v>227</v>
       </c>
-      <c r="F30">
-        <v>34190.62</v>
-      </c>
-      <c r="G30" t="s">
-        <v>237</v>
-      </c>
-      <c r="H30" t="s">
-        <v>250</v>
-      </c>
       <c r="J30" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="K30" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="L30">
-        <v>123086232</v>
+        <v>138799368</v>
       </c>
       <c r="M30" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N30" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="O30" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P30" t="b">
         <v>0</v>
@@ -2707,40 +2638,37 @@
         <v>2023</v>
       </c>
       <c r="C31" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D31" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E31" t="s">
+        <v>210</v>
+      </c>
+      <c r="F31">
+        <v>369</v>
+      </c>
+      <c r="H31" t="s">
         <v>227</v>
       </c>
-      <c r="F31">
-        <v>38555.38</v>
-      </c>
-      <c r="G31" t="s">
-        <v>237</v>
-      </c>
-      <c r="H31" t="s">
-        <v>250</v>
-      </c>
       <c r="J31" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="K31" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="L31">
-        <v>138799368</v>
+        <v>12095820</v>
       </c>
       <c r="M31" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N31" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="O31" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P31" t="b">
         <v>0</v>
@@ -2754,37 +2682,37 @@
         <v>2023</v>
       </c>
       <c r="C32" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D32" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E32" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="F32">
-        <v>369</v>
+        <v>2528</v>
       </c>
       <c r="H32" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="J32" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="K32" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="L32">
-        <v>12095820</v>
+        <v>57828505.6</v>
       </c>
       <c r="M32" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="N32" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="O32" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P32" t="b">
         <v>0</v>
@@ -2798,37 +2726,37 @@
         <v>2023</v>
       </c>
       <c r="C33" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D33" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="E33" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="F33">
-        <v>2528</v>
+        <v>21662.09888</v>
       </c>
       <c r="H33" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="J33" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="K33" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="L33">
-        <v>57828505.6</v>
+        <v>21662098.88</v>
       </c>
       <c r="M33" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N33" t="s">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="O33" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P33" t="b">
         <v>0</v>
@@ -2842,37 +2770,37 @@
         <v>2023</v>
       </c>
       <c r="C34" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D34" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E34" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F34">
-        <v>21662.09888</v>
+        <v>385327.7974</v>
       </c>
       <c r="H34" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="J34" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K34" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L34">
-        <v>21662098.88</v>
+        <v>385327797.4</v>
       </c>
       <c r="M34" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N34" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O34" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P34" t="b">
         <v>0</v>
@@ -2886,37 +2814,37 @@
         <v>2023</v>
       </c>
       <c r="C35" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D35" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E35" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F35">
-        <v>385327.7974</v>
+        <v>3531.1068</v>
       </c>
       <c r="H35" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="J35" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K35" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L35">
-        <v>385327797.4</v>
+        <v>3531106.8</v>
       </c>
       <c r="M35" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N35" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O35" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P35" t="b">
         <v>0</v>
@@ -2930,37 +2858,37 @@
         <v>2023</v>
       </c>
       <c r="C36" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D36" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E36" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F36">
-        <v>3531.1068</v>
+        <v>892229.95044</v>
       </c>
       <c r="H36" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="J36" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K36" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L36">
-        <v>3531106.8</v>
+        <v>892229950.4400001</v>
       </c>
       <c r="M36" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N36" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O36" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P36" t="b">
         <v>0</v>
@@ -2974,37 +2902,37 @@
         <v>2023</v>
       </c>
       <c r="C37" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D37" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E37" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F37">
-        <v>892229.95044</v>
+        <v>10018.1179</v>
       </c>
       <c r="H37" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="J37" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K37" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L37">
-        <v>892229950.4400001</v>
+        <v>10018117.9</v>
       </c>
       <c r="M37" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N37" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O37" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P37" t="b">
         <v>0</v>
@@ -3018,37 +2946,37 @@
         <v>2023</v>
       </c>
       <c r="C38" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D38" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E38" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F38">
-        <v>10018.1179</v>
+        <v>142393.17415</v>
       </c>
       <c r="H38" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="J38" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K38" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L38">
-        <v>10018117.9</v>
+        <v>142393174.15</v>
       </c>
       <c r="M38" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N38" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O38" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P38" t="b">
         <v>0</v>
@@ -3062,37 +2990,37 @@
         <v>2023</v>
       </c>
       <c r="C39" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D39" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="E39" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F39">
-        <v>142393.17415</v>
+        <v>1683653</v>
       </c>
       <c r="H39" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="J39" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="K39" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="L39">
-        <v>142393174.15</v>
+        <v>1683653000</v>
       </c>
       <c r="M39" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N39" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O39" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P39" t="b">
         <v>0</v>
@@ -3106,37 +3034,37 @@
         <v>2023</v>
       </c>
       <c r="C40" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D40" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E40" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F40">
-        <v>1683653</v>
+        <v>1695665</v>
       </c>
       <c r="H40" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="J40" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="K40" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="L40">
-        <v>1683653000</v>
+        <v>1695665000</v>
       </c>
       <c r="M40" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N40" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O40" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P40" t="b">
         <v>0</v>
@@ -3150,37 +3078,37 @@
         <v>2023</v>
       </c>
       <c r="C41" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D41" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E41" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F41">
-        <v>1695665</v>
+        <v>38791</v>
       </c>
       <c r="H41" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="J41" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="K41" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="L41">
-        <v>1695665000</v>
+        <v>38791000</v>
       </c>
       <c r="M41" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N41" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O41" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P41" t="b">
         <v>0</v>
@@ -3194,37 +3122,37 @@
         <v>2023</v>
       </c>
       <c r="C42" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D42" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E42" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F42">
-        <v>38791</v>
+        <v>186977</v>
       </c>
       <c r="H42" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="J42" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="K42" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="L42">
-        <v>38791000</v>
+        <v>186977000</v>
       </c>
       <c r="M42" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N42" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O42" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P42" t="b">
         <v>0</v>
@@ -3238,37 +3166,37 @@
         <v>2023</v>
       </c>
       <c r="C43" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D43" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E43" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F43">
-        <v>186977</v>
+        <v>453</v>
       </c>
       <c r="H43" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="J43" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="K43" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="L43">
-        <v>186977000</v>
+        <v>453000</v>
       </c>
       <c r="M43" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N43" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O43" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P43" t="b">
         <v>0</v>
@@ -3282,37 +3210,37 @@
         <v>2023</v>
       </c>
       <c r="C44" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D44" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="E44" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F44">
-        <v>453</v>
+        <v>129455</v>
       </c>
       <c r="H44" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="J44" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="K44" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="L44">
-        <v>453000</v>
+        <v>129455000</v>
       </c>
       <c r="M44" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N44" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O44" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P44" t="b">
         <v>0</v>
@@ -3326,37 +3254,37 @@
         <v>2023</v>
       </c>
       <c r="C45" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D45" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E45" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F45">
-        <v>129455</v>
+        <v>178921745</v>
       </c>
       <c r="H45" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="J45" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K45" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L45">
-        <v>129455000</v>
+        <v>644118282</v>
       </c>
       <c r="M45" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N45" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="O45" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P45" t="b">
         <v>0</v>
@@ -3370,37 +3298,37 @@
         <v>2023</v>
       </c>
       <c r="C46" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D46" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E46" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F46">
-        <v>178921745</v>
+        <v>1347</v>
       </c>
       <c r="H46" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="J46" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K46" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L46">
-        <v>644118282</v>
+        <v>1347000</v>
       </c>
       <c r="M46" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N46" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="O46" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P46" t="b">
         <v>0</v>
@@ -3414,37 +3342,37 @@
         <v>2023</v>
       </c>
       <c r="C47" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D47" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="E47" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F47">
-        <v>11047</v>
+        <v>86234</v>
       </c>
       <c r="H47" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="J47" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K47" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L47">
-        <v>11047000</v>
+        <v>86234000</v>
       </c>
       <c r="M47" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N47" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O47" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P47" t="b">
         <v>0</v>
@@ -3458,37 +3386,37 @@
         <v>2023</v>
       </c>
       <c r="C48" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D48" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E48" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F48">
-        <v>1347</v>
+        <v>619000</v>
       </c>
       <c r="H48" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="J48" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="K48" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="L48">
-        <v>1347000</v>
+        <v>619000000</v>
       </c>
       <c r="M48" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N48" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O48" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P48" t="b">
         <v>0</v>
@@ -3502,37 +3430,37 @@
         <v>2023</v>
       </c>
       <c r="C49" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D49" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E49" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F49">
-        <v>86234</v>
+        <v>301000</v>
       </c>
       <c r="H49" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="J49" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="K49" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="L49">
-        <v>86234000</v>
+        <v>301000000</v>
       </c>
       <c r="M49" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N49" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O49" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P49" t="b">
         <v>0</v>
@@ -3546,37 +3474,37 @@
         <v>2023</v>
       </c>
       <c r="C50" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D50" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E50" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F50">
-        <v>619000</v>
+        <v>211308</v>
       </c>
       <c r="H50" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="J50" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="K50" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="L50">
-        <v>619000000</v>
+        <v>211308000</v>
       </c>
       <c r="M50" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N50" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O50" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P50" t="b">
         <v>0</v>
@@ -3590,37 +3518,37 @@
         <v>2023</v>
       </c>
       <c r="C51" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D51" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="E51" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F51">
-        <v>301000</v>
+        <v>717</v>
       </c>
       <c r="H51" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="J51" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="K51" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="L51">
-        <v>301000000</v>
+        <v>717000</v>
       </c>
       <c r="M51" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N51" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O51" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P51" t="b">
         <v>0</v>
@@ -3634,37 +3562,37 @@
         <v>2023</v>
       </c>
       <c r="C52" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D52" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E52" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F52">
-        <v>211308</v>
+        <v>334179</v>
       </c>
       <c r="H52" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="J52" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="K52" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="L52">
-        <v>211308000</v>
+        <v>334179000</v>
       </c>
       <c r="M52" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N52" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O52" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P52" t="b">
         <v>0</v>
@@ -3678,37 +3606,37 @@
         <v>2023</v>
       </c>
       <c r="C53" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D53" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E53" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F53">
-        <v>717</v>
+        <v>14406</v>
       </c>
       <c r="H53" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="J53" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="K53" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="L53">
-        <v>717000</v>
+        <v>14406000</v>
       </c>
       <c r="M53" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N53" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O53" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P53" t="b">
         <v>0</v>
@@ -3722,37 +3650,37 @@
         <v>2023</v>
       </c>
       <c r="C54" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D54" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E54" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F54">
-        <v>334179</v>
+        <v>72011</v>
       </c>
       <c r="H54" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="J54" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="K54" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="L54">
-        <v>334179000</v>
+        <v>72011000</v>
       </c>
       <c r="M54" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N54" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O54" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P54" t="b">
         <v>0</v>
@@ -3766,37 +3694,37 @@
         <v>2023</v>
       </c>
       <c r="C55" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D55" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E55" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="F55">
-        <v>14406</v>
+        <v>409793</v>
       </c>
       <c r="H55" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="J55" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="K55" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="L55">
-        <v>14406000</v>
+        <v>55697075.44526765</v>
       </c>
       <c r="M55" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N55" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="O55" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P55" t="b">
         <v>0</v>
@@ -3810,37 +3738,37 @@
         <v>2023</v>
       </c>
       <c r="C56" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D56" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="E56" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F56">
-        <v>72011</v>
+        <v>17595388</v>
       </c>
       <c r="H56" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="J56" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="K56" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="L56">
-        <v>72011000</v>
+        <v>63343396.8</v>
       </c>
       <c r="M56" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N56" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="O56" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P56" t="b">
         <v>0</v>
@@ -3854,37 +3782,37 @@
         <v>2023</v>
       </c>
       <c r="C57" t="s">
+        <v>176</v>
+      </c>
+      <c r="D57" t="s">
         <v>190</v>
       </c>
-      <c r="D57" t="s">
-        <v>202</v>
-      </c>
       <c r="E57" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="F57">
-        <v>409793</v>
+        <v>67158</v>
       </c>
       <c r="H57" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="J57" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="K57" t="s">
+        <v>275</v>
+      </c>
+      <c r="L57">
+        <v>8333350.1134884</v>
+      </c>
+      <c r="M57" t="s">
+        <v>292</v>
+      </c>
+      <c r="N57" t="s">
         <v>298</v>
       </c>
-      <c r="L57">
-        <v>55697075.44526765</v>
-      </c>
-      <c r="M57" t="s">
-        <v>315</v>
-      </c>
-      <c r="N57" t="s">
-        <v>320</v>
-      </c>
       <c r="O57" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P57" t="b">
         <v>0</v>
@@ -3898,37 +3826,37 @@
         <v>2023</v>
       </c>
       <c r="C58" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D58" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E58" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="F58">
-        <v>17595388</v>
+        <v>422621</v>
       </c>
       <c r="H58" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="J58" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="K58" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="L58">
-        <v>63343396.8</v>
+        <v>36595602.20983067</v>
       </c>
       <c r="M58" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N58" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="O58" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P58" t="b">
         <v>0</v>
@@ -3942,37 +3870,37 @@
         <v>2023</v>
       </c>
       <c r="C59" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D59" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="E59" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="F59">
-        <v>67158</v>
+        <v>1188</v>
       </c>
       <c r="H59" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="J59" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="K59" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="L59">
-        <v>8333350.1134884</v>
+        <v>42655140</v>
       </c>
       <c r="M59" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="N59" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="O59" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P59" t="b">
         <v>0</v>
@@ -3986,37 +3914,40 @@
         <v>2023</v>
       </c>
       <c r="C60" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D60" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="E60" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="F60">
-        <v>422621</v>
+        <v>10684.5</v>
+      </c>
+      <c r="G60" t="s">
+        <v>216</v>
       </c>
       <c r="H60" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="J60" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="K60" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="L60">
-        <v>36595602.20983067</v>
+        <v>38464200</v>
       </c>
       <c r="M60" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N60" t="s">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="O60" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P60" t="b">
         <v>0</v>
@@ -4030,37 +3961,40 @@
         <v>2023</v>
       </c>
       <c r="C61" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D61" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E61" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="F61">
-        <v>1188</v>
+        <v>32053.5</v>
+      </c>
+      <c r="G61" t="s">
+        <v>216</v>
       </c>
       <c r="H61" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="J61" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="K61" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="L61">
-        <v>42655140</v>
+        <v>115392600</v>
       </c>
       <c r="M61" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N61" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="O61" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P61" t="b">
         <v>0</v>
@@ -4074,40 +4008,37 @@
         <v>2023</v>
       </c>
       <c r="C62" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D62" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E62" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="F62">
-        <v>10684.5</v>
-      </c>
-      <c r="G62" t="s">
-        <v>237</v>
+        <v>36</v>
       </c>
       <c r="H62" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="J62" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="K62" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="L62">
-        <v>38464200</v>
+        <v>1180080</v>
       </c>
       <c r="M62" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N62" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="O62" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P62" t="b">
         <v>0</v>
@@ -4121,40 +4052,40 @@
         <v>2023</v>
       </c>
       <c r="C63" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D63" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E63" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="F63">
-        <v>32053.5</v>
+        <v>1528</v>
       </c>
       <c r="G63" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="H63" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="J63" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="K63" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="L63">
-        <v>115392600</v>
+        <v>58064</v>
       </c>
       <c r="M63" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="N63" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="O63" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P63" t="b">
         <v>0</v>
@@ -4168,37 +4099,37 @@
         <v>2023</v>
       </c>
       <c r="C64" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D64" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="E64" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="F64">
-        <v>36</v>
+        <v>13849</v>
       </c>
       <c r="H64" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="J64" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="K64" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="L64">
-        <v>1180080</v>
+        <v>497248345</v>
       </c>
       <c r="M64" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="N64" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="O64" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P64" t="b">
         <v>0</v>
@@ -4212,40 +4143,37 @@
         <v>2023</v>
       </c>
       <c r="C65" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D65" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E65" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="F65">
-        <v>1528</v>
-      </c>
-      <c r="G65" t="s">
-        <v>238</v>
+        <v>326</v>
       </c>
       <c r="H65" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="J65" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="K65" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="L65">
-        <v>58064</v>
+        <v>1173600000</v>
       </c>
       <c r="M65" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="N65" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="O65" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P65" t="b">
         <v>0</v>
@@ -4259,37 +4187,37 @@
         <v>2023</v>
       </c>
       <c r="C66" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D66" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E66" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="F66">
-        <v>13849</v>
+        <v>422</v>
       </c>
       <c r="H66" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="J66" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="K66" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="L66">
-        <v>497248345</v>
+        <v>13833160</v>
       </c>
       <c r="M66" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="N66" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="O66" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P66" t="b">
         <v>0</v>
@@ -4303,37 +4231,37 @@
         <v>2023</v>
       </c>
       <c r="C67" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D67" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="E67" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="F67">
-        <v>326</v>
+        <v>191632</v>
       </c>
       <c r="H67" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="J67" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="K67" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="L67">
-        <v>1173600000</v>
+        <v>191632000</v>
       </c>
       <c r="M67" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N67" t="s">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="O67" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P67" t="b">
         <v>0</v>
@@ -4347,37 +4275,37 @@
         <v>2023</v>
       </c>
       <c r="C68" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D68" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="E68" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="F68">
-        <v>422</v>
+        <v>181</v>
       </c>
       <c r="H68" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="J68" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="K68" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="L68">
-        <v>13833160</v>
+        <v>181000</v>
       </c>
       <c r="M68" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N68" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="O68" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P68" t="b">
         <v>0</v>
@@ -4391,37 +4319,37 @@
         <v>2023</v>
       </c>
       <c r="C69" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D69" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="E69" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F69">
-        <v>191632</v>
+        <v>276713</v>
       </c>
       <c r="H69" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J69" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="K69" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="L69">
-        <v>191632000</v>
+        <v>276713000</v>
       </c>
       <c r="M69" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N69" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O69" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P69" t="b">
         <v>0</v>
@@ -4435,37 +4363,37 @@
         <v>2023</v>
       </c>
       <c r="C70" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D70" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="E70" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F70">
-        <v>181</v>
+        <v>3549</v>
       </c>
       <c r="H70" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J70" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="K70" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="L70">
-        <v>181000</v>
+        <v>3549000</v>
       </c>
       <c r="M70" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N70" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O70" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P70" t="b">
         <v>0</v>
@@ -4479,37 +4407,37 @@
         <v>2023</v>
       </c>
       <c r="C71" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D71" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E71" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F71">
-        <v>276713</v>
+        <v>45</v>
       </c>
       <c r="H71" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J71" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="K71" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="L71">
-        <v>276713000</v>
+        <v>45000</v>
       </c>
       <c r="M71" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N71" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O71" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P71" t="b">
         <v>0</v>
@@ -4523,37 +4451,37 @@
         <v>2023</v>
       </c>
       <c r="C72" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D72" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E72" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F72">
-        <v>3549</v>
+        <v>187</v>
       </c>
       <c r="H72" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J72" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="K72" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="L72">
-        <v>3549000</v>
+        <v>187000</v>
       </c>
       <c r="M72" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N72" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O72" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P72" t="b">
         <v>0</v>
@@ -4567,37 +4495,37 @@
         <v>2023</v>
       </c>
       <c r="C73" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D73" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="E73" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F73">
-        <v>45</v>
+        <v>76904</v>
       </c>
       <c r="H73" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J73" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="K73" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="L73">
-        <v>45000</v>
+        <v>76904000</v>
       </c>
       <c r="M73" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N73" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O73" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P73" t="b">
         <v>0</v>
@@ -4611,37 +4539,37 @@
         <v>2023</v>
       </c>
       <c r="C74" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D74" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="E74" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F74">
-        <v>187</v>
+        <v>391146</v>
       </c>
       <c r="H74" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="J74" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="K74" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="L74">
-        <v>187000</v>
+        <v>391146000</v>
       </c>
       <c r="M74" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N74" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O74" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P74" t="b">
         <v>0</v>
@@ -4655,37 +4583,37 @@
         <v>2023</v>
       </c>
       <c r="C75" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D75" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="E75" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F75">
-        <v>76904</v>
+        <v>469220285</v>
       </c>
       <c r="H75" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="J75" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="K75" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="L75">
-        <v>76904000</v>
+        <v>1689193026</v>
       </c>
       <c r="M75" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N75" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="O75" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P75" t="b">
         <v>0</v>
@@ -4699,37 +4627,37 @@
         <v>2023</v>
       </c>
       <c r="C76" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D76" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E76" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F76">
-        <v>391146</v>
+        <v>8329</v>
       </c>
       <c r="H76" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="J76" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K76" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L76">
-        <v>391146000</v>
+        <v>8329000</v>
       </c>
       <c r="M76" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N76" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O76" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P76" t="b">
         <v>0</v>
@@ -4743,37 +4671,37 @@
         <v>2023</v>
       </c>
       <c r="C77" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D77" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E77" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F77">
-        <v>469220285</v>
+        <v>297435</v>
       </c>
       <c r="H77" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="J77" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K77" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L77">
-        <v>1689193026</v>
+        <v>297435000</v>
       </c>
       <c r="M77" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N77" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="O77" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P77" t="b">
         <v>0</v>
@@ -4787,37 +4715,37 @@
         <v>2023</v>
       </c>
       <c r="C78" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D78" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="E78" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F78">
-        <v>6280</v>
+        <v>91423</v>
       </c>
       <c r="H78" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="J78" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K78" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L78">
-        <v>6280000</v>
+        <v>91423000</v>
       </c>
       <c r="M78" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N78" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O78" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P78" t="b">
         <v>0</v>
@@ -4831,37 +4759,37 @@
         <v>2023</v>
       </c>
       <c r="C79" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D79" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="E79" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F79">
-        <v>8329</v>
+        <v>182554670</v>
       </c>
       <c r="H79" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="J79" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K79" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L79">
-        <v>8329000</v>
+        <v>657196812</v>
       </c>
       <c r="M79" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N79" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="O79" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P79" t="b">
         <v>0</v>
@@ -4875,37 +4803,37 @@
         <v>2023</v>
       </c>
       <c r="C80" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D80" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="E80" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F80">
-        <v>297435</v>
+        <v>6440</v>
       </c>
       <c r="H80" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="J80" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K80" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L80">
-        <v>297435000</v>
+        <v>6440000</v>
       </c>
       <c r="M80" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N80" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O80" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P80" t="b">
         <v>0</v>
@@ -4919,37 +4847,37 @@
         <v>2023</v>
       </c>
       <c r="C81" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D81" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E81" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F81">
-        <v>91423</v>
+        <v>327090</v>
       </c>
       <c r="H81" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="J81" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K81" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L81">
-        <v>91423000</v>
+        <v>327090000</v>
       </c>
       <c r="M81" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N81" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O81" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P81" t="b">
         <v>0</v>
@@ -4963,37 +4891,37 @@
         <v>2023</v>
       </c>
       <c r="C82" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D82" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E82" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F82">
-        <v>182554670</v>
+        <v>658</v>
       </c>
       <c r="H82" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="J82" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K82" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L82">
-        <v>657196812</v>
+        <v>658000</v>
       </c>
       <c r="M82" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N82" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="O82" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P82" t="b">
         <v>0</v>
@@ -5007,37 +4935,37 @@
         <v>2023</v>
       </c>
       <c r="C83" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D83" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="E83" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F83">
-        <v>82576</v>
-      </c>
-      <c r="H83" t="s">
-        <v>261</v>
+        <v>3590887</v>
+      </c>
+      <c r="I83" t="s">
+        <v>249</v>
       </c>
       <c r="J83" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K83" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L83">
-        <v>82576000</v>
+        <v>3590887000</v>
       </c>
       <c r="M83" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N83" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O83" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P83" t="b">
         <v>0</v>
@@ -5051,37 +4979,37 @@
         <v>2023</v>
       </c>
       <c r="C84" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D84" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="E84" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F84">
-        <v>6440</v>
-      </c>
-      <c r="H84" t="s">
-        <v>261</v>
+        <v>164987364</v>
+      </c>
+      <c r="I84" t="s">
+        <v>249</v>
       </c>
       <c r="J84" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K84" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L84">
-        <v>6440000</v>
+        <v>593954510.4</v>
       </c>
       <c r="M84" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N84" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="O84" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P84" t="b">
         <v>0</v>
@@ -5095,37 +5023,37 @@
         <v>2023</v>
       </c>
       <c r="C85" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D85" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="E85" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F85">
-        <v>327090</v>
-      </c>
-      <c r="H85" t="s">
-        <v>261</v>
+        <v>51161</v>
+      </c>
+      <c r="I85" t="s">
+        <v>249</v>
       </c>
       <c r="J85" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K85" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L85">
-        <v>327090000</v>
+        <v>51161000</v>
       </c>
       <c r="M85" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N85" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O85" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P85" t="b">
         <v>0</v>
@@ -5139,37 +5067,37 @@
         <v>2023</v>
       </c>
       <c r="C86" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D86" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F86">
-        <v>658</v>
-      </c>
-      <c r="H86" t="s">
-        <v>261</v>
+        <v>7311</v>
+      </c>
+      <c r="I86" t="s">
+        <v>249</v>
       </c>
       <c r="J86" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K86" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L86">
-        <v>658000</v>
+        <v>7311000</v>
       </c>
       <c r="M86" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N86" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O86" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P86" t="b">
         <v>0</v>
@@ -5183,37 +5111,37 @@
         <v>2023</v>
       </c>
       <c r="C87" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D87" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E87" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F87">
-        <v>3590887</v>
+        <v>235</v>
       </c>
       <c r="I87" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="J87" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K87" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L87">
-        <v>3590887000</v>
+        <v>235000</v>
       </c>
       <c r="M87" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N87" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O87" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P87" t="b">
         <v>0</v>
@@ -5227,37 +5155,37 @@
         <v>2023</v>
       </c>
       <c r="C88" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D88" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="E88" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F88">
-        <v>164987364</v>
-      </c>
-      <c r="I88" t="s">
-        <v>272</v>
+        <v>1944158</v>
+      </c>
+      <c r="H88" t="s">
+        <v>239</v>
       </c>
       <c r="J88" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K88" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L88">
-        <v>593954510.4</v>
+        <v>1944158000</v>
       </c>
       <c r="M88" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N88" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="O88" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P88" t="b">
         <v>0</v>
@@ -5271,37 +5199,37 @@
         <v>2023</v>
       </c>
       <c r="C89" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D89" t="s">
+        <v>180</v>
+      </c>
+      <c r="E89" t="s">
         <v>206</v>
       </c>
-      <c r="E89" t="s">
-        <v>225</v>
-      </c>
       <c r="F89">
-        <v>45318</v>
-      </c>
-      <c r="I89" t="s">
-        <v>272</v>
+        <v>132709926</v>
+      </c>
+      <c r="H89" t="s">
+        <v>239</v>
       </c>
       <c r="J89" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K89" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L89">
-        <v>45318000</v>
+        <v>477755733.6</v>
       </c>
       <c r="M89" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N89" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="O89" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P89" t="b">
         <v>0</v>
@@ -5315,37 +5243,37 @@
         <v>2023</v>
       </c>
       <c r="C90" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D90" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="E90" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F90">
-        <v>51161</v>
-      </c>
-      <c r="I90" t="s">
-        <v>272</v>
+        <v>5290</v>
+      </c>
+      <c r="H90" t="s">
+        <v>239</v>
       </c>
       <c r="J90" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="K90" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="L90">
-        <v>51161000</v>
+        <v>5290000</v>
       </c>
       <c r="M90" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N90" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O90" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P90" t="b">
         <v>0</v>
@@ -5359,37 +5287,40 @@
         <v>2023</v>
       </c>
       <c r="C91" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D91" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="E91" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F91">
-        <v>7311</v>
-      </c>
-      <c r="I91" t="s">
-        <v>272</v>
+        <v>929608.636977058</v>
+      </c>
+      <c r="G91" t="s">
+        <v>218</v>
+      </c>
+      <c r="H91" t="s">
+        <v>240</v>
       </c>
       <c r="J91" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="K91" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="L91">
-        <v>7311000</v>
+        <v>929608636.9770581</v>
       </c>
       <c r="M91" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N91" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O91" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P91" t="b">
         <v>0</v>
@@ -5403,37 +5334,40 @@
         <v>2023</v>
       </c>
       <c r="C92" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D92" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="E92" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F92">
-        <v>235</v>
-      </c>
-      <c r="I92" t="s">
-        <v>272</v>
+        <v>365541.6666666667</v>
+      </c>
+      <c r="G92" t="s">
+        <v>219</v>
+      </c>
+      <c r="H92" t="s">
+        <v>240</v>
       </c>
       <c r="J92" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="K92" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="L92">
-        <v>235000</v>
+        <v>365541666.6666667</v>
       </c>
       <c r="M92" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N92" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O92" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P92" t="b">
         <v>0</v>
@@ -5443,41 +5377,41 @@
       <c r="A93" t="s">
         <v>107</v>
       </c>
-      <c r="B93">
-        <v>2023</v>
-      </c>
       <c r="C93" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D93" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E93" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F93">
-        <v>1944158</v>
+        <v>36282.05128205128</v>
+      </c>
+      <c r="G93" t="s">
+        <v>219</v>
       </c>
       <c r="H93" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="J93" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="K93" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="L93">
-        <v>1944158000</v>
+        <v>36282051.28205128</v>
       </c>
       <c r="M93" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N93" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O93" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P93" t="b">
         <v>0</v>
@@ -5491,37 +5425,40 @@
         <v>2023</v>
       </c>
       <c r="C94" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D94" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E94" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F94">
-        <v>132709926</v>
+        <v>21012.14574898786</v>
+      </c>
+      <c r="G94" t="s">
+        <v>218</v>
       </c>
       <c r="H94" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="J94" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="K94" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="L94">
-        <v>477755733.6</v>
+        <v>21012145.74898786</v>
       </c>
       <c r="M94" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N94" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="O94" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P94" t="b">
         <v>0</v>
@@ -5535,37 +5472,40 @@
         <v>2023</v>
       </c>
       <c r="C95" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D95" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="E95" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F95">
-        <v>18198</v>
+        <v>22737.89649415693</v>
+      </c>
+      <c r="G95" t="s">
+        <v>218</v>
       </c>
       <c r="H95" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="J95" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="K95" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="L95">
-        <v>18198000</v>
+        <v>22737896.49415693</v>
       </c>
       <c r="M95" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N95" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O95" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P95" t="b">
         <v>0</v>
@@ -5579,37 +5519,37 @@
         <v>2023</v>
       </c>
       <c r="C96" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D96" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F96">
-        <v>5290</v>
+        <v>27653.22904</v>
       </c>
       <c r="H96" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="J96" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="K96" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="L96">
-        <v>5290000</v>
+        <v>27653229.04</v>
       </c>
       <c r="M96" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N96" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O96" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P96" t="b">
         <v>0</v>
@@ -5623,40 +5563,37 @@
         <v>2023</v>
       </c>
       <c r="C97" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D97" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F97">
-        <v>929608.636977058</v>
-      </c>
-      <c r="G97" t="s">
-        <v>239</v>
+        <v>11770.3702287417</v>
       </c>
       <c r="H97" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="J97" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="K97" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="L97">
-        <v>929608636.9770581</v>
+        <v>11770370.2287417</v>
       </c>
       <c r="M97" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N97" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O97" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P97" t="b">
         <v>0</v>
@@ -5670,40 +5607,37 @@
         <v>2023</v>
       </c>
       <c r="C98" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D98" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F98">
-        <v>365541.6666666667</v>
-      </c>
-      <c r="G98" t="s">
-        <v>240</v>
+        <v>308614.730821</v>
       </c>
       <c r="H98" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="J98" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="K98" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="L98">
-        <v>365541666.6666667</v>
+        <v>308614730.821</v>
       </c>
       <c r="M98" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N98" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O98" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P98" t="b">
         <v>0</v>
@@ -5713,41 +5647,41 @@
       <c r="A99" t="s">
         <v>113</v>
       </c>
+      <c r="B99">
+        <v>2023</v>
+      </c>
       <c r="C99" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D99" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F99">
-        <v>36282.05128205128</v>
-      </c>
-      <c r="G99" t="s">
-        <v>240</v>
+        <v>3808.98428206273</v>
       </c>
       <c r="H99" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="J99" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="K99" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="L99">
-        <v>36282051.28205128</v>
+        <v>3808984.28206273</v>
       </c>
       <c r="M99" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N99" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O99" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P99" t="b">
         <v>0</v>
@@ -5761,40 +5695,37 @@
         <v>2023</v>
       </c>
       <c r="C100" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D100" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F100">
-        <v>2587.5</v>
-      </c>
-      <c r="G100" t="s">
+        <v>509889.6</v>
+      </c>
+      <c r="H100" t="s">
         <v>241</v>
       </c>
-      <c r="H100" t="s">
-        <v>263</v>
-      </c>
       <c r="J100" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="K100" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="L100">
-        <v>2587500</v>
+        <v>509889600</v>
       </c>
       <c r="M100" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N100" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O100" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P100" t="b">
         <v>0</v>
@@ -5808,40 +5739,37 @@
         <v>2023</v>
       </c>
       <c r="C101" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D101" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F101">
-        <v>21012.14574898786</v>
-      </c>
-      <c r="G101" t="s">
-        <v>239</v>
+        <v>5437.635</v>
       </c>
       <c r="H101" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="J101" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="K101" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="L101">
-        <v>21012145.74898786</v>
+        <v>5437635</v>
       </c>
       <c r="M101" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N101" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O101" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P101" t="b">
         <v>0</v>
@@ -5855,40 +5783,37 @@
         <v>2023</v>
       </c>
       <c r="C102" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D102" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F102">
-        <v>22737.89649415693</v>
-      </c>
-      <c r="G102" t="s">
-        <v>239</v>
+        <v>229891.86895</v>
       </c>
       <c r="H102" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="J102" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="K102" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="L102">
-        <v>22737896.49415693</v>
+        <v>229891868.95</v>
       </c>
       <c r="M102" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N102" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O102" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P102" t="b">
         <v>0</v>
@@ -5902,37 +5827,37 @@
         <v>2023</v>
       </c>
       <c r="C103" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D103" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F103">
-        <v>27653.22904</v>
+        <v>1483.2</v>
       </c>
       <c r="H103" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="J103" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K103" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L103">
-        <v>27653229.04</v>
+        <v>1483200</v>
       </c>
       <c r="M103" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N103" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O103" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P103" t="b">
         <v>0</v>
@@ -5946,37 +5871,37 @@
         <v>2023</v>
       </c>
       <c r="C104" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D104" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F104">
-        <v>11770.3702287417</v>
+        <v>4761600.1</v>
       </c>
       <c r="H104" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="J104" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="K104" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="L104">
-        <v>11770370.2287417</v>
+        <v>170965251.5905</v>
       </c>
       <c r="M104" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N104" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="O104" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P104" t="b">
         <v>0</v>
@@ -5990,37 +5915,37 @@
         <v>2023</v>
       </c>
       <c r="C105" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D105" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F105">
-        <v>308614.730821</v>
+        <v>56414.6765</v>
       </c>
       <c r="H105" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="J105" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="K105" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="L105">
-        <v>308614730.821</v>
+        <v>56414676.5</v>
       </c>
       <c r="M105" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N105" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O105" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P105" t="b">
         <v>0</v>
@@ -6034,37 +5959,37 @@
         <v>2023</v>
       </c>
       <c r="C106" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D106" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F106">
-        <v>3808.98428206273</v>
+        <v>171984.8235</v>
       </c>
       <c r="H106" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="J106" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="K106" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="L106">
-        <v>3808984.28206273</v>
+        <v>171984823.5</v>
       </c>
       <c r="M106" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N106" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O106" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P106" t="b">
         <v>0</v>
@@ -6078,37 +6003,37 @@
         <v>2023</v>
       </c>
       <c r="C107" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D107" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F107">
-        <v>509889.6</v>
+        <v>119418.4</v>
       </c>
       <c r="H107" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="J107" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="K107" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="L107">
-        <v>509889600</v>
+        <v>3914535.152</v>
       </c>
       <c r="M107" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N107" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="O107" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P107" t="b">
         <v>0</v>
@@ -6122,37 +6047,37 @@
         <v>2023</v>
       </c>
       <c r="C108" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D108" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F108">
-        <v>5437.635</v>
+        <v>59198</v>
       </c>
       <c r="H108" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="J108" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="K108" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="L108">
-        <v>5437635</v>
+        <v>59198000</v>
       </c>
       <c r="M108" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N108" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O108" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P108" t="b">
         <v>0</v>
@@ -6166,37 +6091,37 @@
         <v>2023</v>
       </c>
       <c r="C109" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D109" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F109">
-        <v>229891.86895</v>
+        <v>31049.5</v>
       </c>
       <c r="H109" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="J109" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="K109" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="L109">
-        <v>229891868.95</v>
+        <v>710263.5224</v>
       </c>
       <c r="M109" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N109" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="O109" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P109" t="b">
         <v>0</v>
@@ -6210,37 +6135,37 @@
         <v>2023</v>
       </c>
       <c r="C110" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D110" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F110">
-        <v>1483.2</v>
-      </c>
-      <c r="H110" t="s">
-        <v>264</v>
+        <v>23524.436671511</v>
+      </c>
+      <c r="I110" t="s">
+        <v>250</v>
       </c>
       <c r="J110" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K110" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L110">
-        <v>1483200</v>
+        <v>23524436.671511</v>
       </c>
       <c r="M110" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N110" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O110" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P110" t="b">
         <v>0</v>
@@ -6254,37 +6179,37 @@
         <v>2023</v>
       </c>
       <c r="C111" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D111" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E111" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="F111">
-        <v>4761600.1</v>
-      </c>
-      <c r="H111" t="s">
-        <v>265</v>
+        <v>623021.8686160001</v>
+      </c>
+      <c r="I111" t="s">
+        <v>250</v>
       </c>
       <c r="J111" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="K111" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="L111">
-        <v>170965251.5905</v>
+        <v>623021868.6160001</v>
       </c>
       <c r="M111" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N111" t="s">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="O111" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P111" t="b">
         <v>0</v>
@@ -6298,37 +6223,37 @@
         <v>2023</v>
       </c>
       <c r="C112" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D112" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F112">
-        <v>56414.6765</v>
-      </c>
-      <c r="H112" t="s">
-        <v>265</v>
+        <v>91025.4822599152</v>
+      </c>
+      <c r="I112" t="s">
+        <v>250</v>
       </c>
       <c r="J112" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="K112" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="L112">
-        <v>56414676.5</v>
+        <v>91025482.2599152</v>
       </c>
       <c r="M112" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N112" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O112" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P112" t="b">
         <v>0</v>
@@ -6342,37 +6267,37 @@
         <v>2023</v>
       </c>
       <c r="C113" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D113" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F113">
-        <v>171984.8235</v>
-      </c>
-      <c r="H113" t="s">
-        <v>265</v>
+        <v>723967.2</v>
+      </c>
+      <c r="I113" t="s">
+        <v>250</v>
       </c>
       <c r="J113" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="K113" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="L113">
-        <v>171984823.5</v>
+        <v>723967200</v>
       </c>
       <c r="M113" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N113" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O113" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P113" t="b">
         <v>0</v>
@@ -6386,37 +6311,37 @@
         <v>2023</v>
       </c>
       <c r="C114" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D114" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="E114" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="F114">
-        <v>522600</v>
-      </c>
-      <c r="H114" t="s">
-        <v>265</v>
+        <v>17195.8465</v>
+      </c>
+      <c r="I114" t="s">
+        <v>250</v>
       </c>
       <c r="J114" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="K114" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="L114">
-        <v>2090400</v>
+        <v>17195846.5</v>
       </c>
       <c r="M114" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="N114" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="O114" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P114" t="b">
         <v>0</v>
@@ -6430,37 +6355,37 @@
         <v>2023</v>
       </c>
       <c r="C115" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D115" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E115" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="F115">
-        <v>119418.4</v>
-      </c>
-      <c r="H115" t="s">
-        <v>265</v>
+        <v>166705</v>
+      </c>
+      <c r="I115" t="s">
+        <v>250</v>
       </c>
       <c r="J115" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="K115" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="L115">
-        <v>3914535.152</v>
+        <v>166705000</v>
       </c>
       <c r="M115" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N115" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="O115" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P115" t="b">
         <v>0</v>
@@ -6474,37 +6399,37 @@
         <v>2023</v>
       </c>
       <c r="C116" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D116" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F116">
-        <v>59198</v>
-      </c>
-      <c r="H116" t="s">
-        <v>265</v>
+        <v>6336.0580703</v>
+      </c>
+      <c r="I116" t="s">
+        <v>250</v>
       </c>
       <c r="J116" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="K116" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="L116">
-        <v>59198000</v>
+        <v>6336058.0703</v>
       </c>
       <c r="M116" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N116" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O116" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P116" t="b">
         <v>0</v>
@@ -6518,37 +6443,37 @@
         <v>2023</v>
       </c>
       <c r="C117" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D117" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="E117" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="F117">
-        <v>31049.5</v>
+        <v>42378137.86</v>
       </c>
       <c r="H117" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="J117" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="K117" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="L117">
-        <v>710263.5224</v>
+        <v>1521587039.8633</v>
       </c>
       <c r="M117" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="N117" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="O117" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P117" t="b">
         <v>0</v>
@@ -6562,37 +6487,37 @@
         <v>2023</v>
       </c>
       <c r="C118" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D118" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F118">
-        <v>23524.436671511</v>
-      </c>
-      <c r="I118" t="s">
-        <v>273</v>
+        <v>2919222</v>
+      </c>
+      <c r="H118" t="s">
+        <v>243</v>
       </c>
       <c r="J118" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="K118" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="L118">
-        <v>23524436.671511</v>
+        <v>2919222000</v>
       </c>
       <c r="M118" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N118" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O118" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P118" t="b">
         <v>0</v>
@@ -6606,37 +6531,37 @@
         <v>2023</v>
       </c>
       <c r="C119" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D119" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F119">
-        <v>623021.8686160001</v>
-      </c>
-      <c r="I119" t="s">
-        <v>273</v>
+        <v>1147190.1</v>
+      </c>
+      <c r="H119" t="s">
+        <v>243</v>
       </c>
       <c r="J119" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="K119" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="L119">
-        <v>623021868.6160001</v>
+        <v>37604891.478</v>
       </c>
       <c r="M119" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N119" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="O119" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P119" t="b">
         <v>0</v>
@@ -6650,37 +6575,37 @@
         <v>2023</v>
       </c>
       <c r="C120" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D120" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E120" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F120">
-        <v>91025.4822599152</v>
-      </c>
-      <c r="I120" t="s">
-        <v>273</v>
+        <v>3691412.93</v>
+      </c>
+      <c r="H120" t="s">
+        <v>243</v>
       </c>
       <c r="J120" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="K120" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="L120">
-        <v>91025482.2599152</v>
+        <v>84441809.056336</v>
       </c>
       <c r="M120" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N120" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="O120" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P120" t="b">
         <v>0</v>
@@ -6694,37 +6619,37 @@
         <v>2023</v>
       </c>
       <c r="C121" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D121" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="E121" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F121">
-        <v>723967.2</v>
-      </c>
-      <c r="I121" t="s">
-        <v>273</v>
+        <v>2</v>
+      </c>
+      <c r="H121" t="s">
+        <v>244</v>
       </c>
       <c r="J121" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K121" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L121">
-        <v>723967200</v>
+        <v>2000</v>
       </c>
       <c r="M121" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N121" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O121" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P121" t="b">
         <v>0</v>
@@ -6738,37 +6663,37 @@
         <v>2023</v>
       </c>
       <c r="C122" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D122" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="E122" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F122">
-        <v>17195.8465</v>
-      </c>
-      <c r="I122" t="s">
-        <v>273</v>
+        <v>121071.915388</v>
+      </c>
+      <c r="H122" t="s">
+        <v>244</v>
       </c>
       <c r="J122" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K122" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L122">
-        <v>17195846.5</v>
+        <v>121071915.388</v>
       </c>
       <c r="M122" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N122" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O122" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P122" t="b">
         <v>0</v>
@@ -6782,37 +6707,37 @@
         <v>2023</v>
       </c>
       <c r="C123" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D123" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="E123" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F123">
-        <v>166705</v>
-      </c>
-      <c r="I123" t="s">
-        <v>273</v>
+        <v>1361713.858312</v>
+      </c>
+      <c r="H123" t="s">
+        <v>244</v>
       </c>
       <c r="J123" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K123" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L123">
-        <v>166705000</v>
+        <v>1361713858.312</v>
       </c>
       <c r="M123" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N123" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O123" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P123" t="b">
         <v>0</v>
@@ -6826,37 +6751,37 @@
         <v>2023</v>
       </c>
       <c r="C124" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D124" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="E124" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F124">
-        <v>6336.0580703</v>
-      </c>
-      <c r="I124" t="s">
-        <v>273</v>
+        <v>5528.5667</v>
+      </c>
+      <c r="H124" t="s">
+        <v>244</v>
       </c>
       <c r="J124" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="K124" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="L124">
-        <v>6336058.0703</v>
+        <v>5528566.7</v>
       </c>
       <c r="M124" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N124" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O124" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P124" t="b">
         <v>0</v>
@@ -6870,37 +6795,37 @@
         <v>2023</v>
       </c>
       <c r="C125" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D125" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E125" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="F125">
-        <v>42378137.86</v>
+        <v>1274584.3416</v>
       </c>
       <c r="H125" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="J125" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="K125" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="L125">
-        <v>1521587039.8633</v>
+        <v>1274584341.6</v>
       </c>
       <c r="M125" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N125" t="s">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="O125" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P125" t="b">
         <v>0</v>
@@ -6914,37 +6839,37 @@
         <v>2023</v>
       </c>
       <c r="C126" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D126" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="E126" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F126">
-        <v>2919222</v>
+        <v>25050.76</v>
       </c>
       <c r="H126" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="J126" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="K126" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="L126">
-        <v>2919222000</v>
+        <v>25050760</v>
       </c>
       <c r="M126" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N126" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O126" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P126" t="b">
         <v>0</v>
@@ -6958,37 +6883,37 @@
         <v>2023</v>
       </c>
       <c r="C127" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D127" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="E127" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="F127">
-        <v>14805627</v>
+        <v>80313.18580000001</v>
       </c>
       <c r="H127" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="J127" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="K127" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="L127">
-        <v>59222508</v>
+        <v>80313185.80000001</v>
       </c>
       <c r="M127" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="N127" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="O127" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P127" t="b">
         <v>0</v>
@@ -6999,40 +6924,40 @@
         <v>142</v>
       </c>
       <c r="B128">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C128" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D128" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="E128" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="F128">
-        <v>1147190.1</v>
+        <v>3116555.8</v>
       </c>
       <c r="H128" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="J128" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="K128" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="L128">
-        <v>37604891.478</v>
+        <v>111899935.999</v>
       </c>
       <c r="M128" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="N128" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="O128" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P128" t="b">
         <v>0</v>
@@ -7043,40 +6968,40 @@
         <v>143</v>
       </c>
       <c r="B129">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C129" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D129" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="E129" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="F129">
-        <v>3691412.93</v>
+        <v>248298644.3585</v>
       </c>
       <c r="H129" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="J129" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="K129" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="L129">
-        <v>84441809.056336</v>
+        <v>893875119.6906</v>
       </c>
       <c r="M129" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N129" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="O129" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P129" t="b">
         <v>0</v>
@@ -7087,40 +7012,40 @@
         <v>144</v>
       </c>
       <c r="B130">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C130" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D130" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E130" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F130">
-        <v>2</v>
+        <v>151631.5</v>
       </c>
       <c r="H130" t="s">
+        <v>245</v>
+      </c>
+      <c r="J130" t="s">
         <v>267</v>
       </c>
-      <c r="J130" t="s">
-        <v>277</v>
-      </c>
       <c r="K130" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="L130">
-        <v>2000</v>
+        <v>4970480.57</v>
       </c>
       <c r="M130" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N130" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="O130" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P130" t="b">
         <v>0</v>
@@ -7131,40 +7056,40 @@
         <v>145</v>
       </c>
       <c r="B131">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C131" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D131" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="E131" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F131">
-        <v>121071.915388</v>
+        <v>640677.799999999</v>
       </c>
       <c r="H131" t="s">
+        <v>245</v>
+      </c>
+      <c r="J131" t="s">
         <v>267</v>
       </c>
-      <c r="J131" t="s">
-        <v>277</v>
-      </c>
       <c r="K131" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="L131">
-        <v>121071915.388</v>
+        <v>14655632.81055998</v>
       </c>
       <c r="M131" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="N131" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="O131" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P131" t="b">
         <v>0</v>
@@ -7175,40 +7100,40 @@
         <v>146</v>
       </c>
       <c r="B132">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C132" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D132" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E132" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F132">
-        <v>1361713.858312</v>
+        <v>307233</v>
       </c>
       <c r="H132" t="s">
+        <v>245</v>
+      </c>
+      <c r="J132" t="s">
         <v>267</v>
       </c>
-      <c r="J132" t="s">
-        <v>277</v>
-      </c>
       <c r="K132" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="L132">
-        <v>1361713858.312</v>
+        <v>307233000</v>
       </c>
       <c r="M132" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N132" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O132" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P132" t="b">
         <v>0</v>
@@ -7222,37 +7147,37 @@
         <v>2023</v>
       </c>
       <c r="C133" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D133" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="E133" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F133">
-        <v>5528.5667</v>
+        <v>432</v>
       </c>
       <c r="H133" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="J133" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="K133" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="L133">
-        <v>5528566.7</v>
+        <v>432000000</v>
       </c>
       <c r="M133" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N133" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="O133" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P133" t="b">
         <v>0</v>
@@ -7266,37 +7191,37 @@
         <v>2023</v>
       </c>
       <c r="C134" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D134" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="E134" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F134">
-        <v>1274584.3416</v>
+        <v>1233</v>
       </c>
       <c r="H134" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="J134" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="K134" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="L134">
-        <v>1274584341.6</v>
+        <v>1233000000</v>
       </c>
       <c r="M134" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N134" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="O134" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P134" t="b">
         <v>0</v>
@@ -7310,37 +7235,37 @@
         <v>2023</v>
       </c>
       <c r="C135" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D135" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E135" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F135">
-        <v>25050.76</v>
+        <v>12</v>
       </c>
       <c r="H135" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="J135" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="K135" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="L135">
-        <v>25050760</v>
+        <v>12000000</v>
       </c>
       <c r="M135" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N135" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="O135" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P135" t="b">
         <v>0</v>
@@ -7354,37 +7279,37 @@
         <v>2023</v>
       </c>
       <c r="C136" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D136" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E136" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F136">
-        <v>80313.18580000001</v>
+        <v>1058</v>
       </c>
       <c r="H136" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="J136" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="K136" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="L136">
-        <v>80313185.80000001</v>
+        <v>1058000000</v>
       </c>
       <c r="M136" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N136" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="O136" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P136" t="b">
         <v>0</v>
@@ -7395,40 +7320,40 @@
         <v>151</v>
       </c>
       <c r="B137">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C137" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D137" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E137" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="F137">
-        <v>3116555.8</v>
+        <v>1</v>
       </c>
       <c r="H137" t="s">
+        <v>246</v>
+      </c>
+      <c r="J137" t="s">
         <v>268</v>
       </c>
-      <c r="J137" t="s">
-        <v>290</v>
-      </c>
       <c r="K137" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="L137">
-        <v>111899935.999</v>
+        <v>1000000</v>
       </c>
       <c r="M137" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N137" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="O137" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P137" t="b">
         <v>0</v>
@@ -7439,40 +7364,40 @@
         <v>152</v>
       </c>
       <c r="B138">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C138" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D138" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="E138" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F138">
-        <v>248298644.3585</v>
-      </c>
-      <c r="H138" t="s">
-        <v>268</v>
+        <v>131655</v>
+      </c>
+      <c r="I138" t="s">
+        <v>251</v>
       </c>
       <c r="J138" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="K138" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="L138">
-        <v>893875119.6906</v>
+        <v>131655000</v>
       </c>
       <c r="M138" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N138" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="O138" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P138" t="b">
         <v>0</v>
@@ -7483,40 +7408,40 @@
         <v>153</v>
       </c>
       <c r="B139">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C139" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D139" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="E139" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="F139">
-        <v>151631.5</v>
-      </c>
-      <c r="H139" t="s">
-        <v>268</v>
+        <v>452775</v>
+      </c>
+      <c r="I139" t="s">
+        <v>251</v>
       </c>
       <c r="J139" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="K139" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="L139">
-        <v>4970480.57</v>
+        <v>1629990</v>
       </c>
       <c r="M139" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N139" t="s">
-        <v>321</v>
+        <v>295</v>
       </c>
       <c r="O139" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P139" t="b">
         <v>0</v>
@@ -7527,40 +7452,40 @@
         <v>154</v>
       </c>
       <c r="B140">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C140" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D140" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="E140" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="F140">
-        <v>640677.799999999</v>
-      </c>
-      <c r="H140" t="s">
-        <v>268</v>
+        <v>53673624</v>
+      </c>
+      <c r="I140" t="s">
+        <v>251</v>
       </c>
       <c r="J140" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="K140" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="L140">
-        <v>14655632.81055998</v>
+        <v>193225046.4</v>
       </c>
       <c r="M140" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="N140" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="O140" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P140" t="b">
         <v>0</v>
@@ -7571,40 +7496,43 @@
         <v>155</v>
       </c>
       <c r="B141">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C141" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D141" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E141" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F141">
-        <v>307233</v>
-      </c>
-      <c r="H141" t="s">
-        <v>268</v>
+        <v>10277</v>
+      </c>
+      <c r="G141" t="s">
+        <v>220</v>
+      </c>
+      <c r="I141" t="s">
+        <v>251</v>
       </c>
       <c r="J141" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="K141" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="L141">
-        <v>307233000</v>
+        <v>10277000</v>
       </c>
       <c r="M141" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N141" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O141" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P141" t="b">
         <v>0</v>
@@ -7618,37 +7546,37 @@
         <v>2023</v>
       </c>
       <c r="C142" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D142" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E142" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="F142">
-        <v>432</v>
-      </c>
-      <c r="H142" t="s">
+        <v>40177</v>
+      </c>
+      <c r="I142" t="s">
+        <v>251</v>
+      </c>
+      <c r="J142" t="s">
         <v>269</v>
       </c>
-      <c r="J142" t="s">
-        <v>291</v>
-      </c>
       <c r="K142" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="L142">
-        <v>432000000</v>
+        <v>40177000</v>
       </c>
       <c r="M142" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N142" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="O142" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P142" t="b">
         <v>0</v>
@@ -7662,37 +7590,40 @@
         <v>2023</v>
       </c>
       <c r="C143" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D143" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="E143" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="F143">
-        <v>1233</v>
-      </c>
-      <c r="H143" t="s">
-        <v>269</v>
+        <v>387.2</v>
+      </c>
+      <c r="G143" t="s">
+        <v>215</v>
+      </c>
+      <c r="I143" t="s">
+        <v>252</v>
       </c>
       <c r="J143" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="K143" t="s">
-        <v>310</v>
+        <v>276</v>
       </c>
       <c r="L143">
-        <v>1233000000</v>
+        <v>387200000</v>
       </c>
       <c r="M143" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N143" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="O143" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P143" t="b">
         <v>0</v>
@@ -7706,37 +7637,37 @@
         <v>2023</v>
       </c>
       <c r="C144" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D144" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E144" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="F144">
-        <v>12</v>
-      </c>
-      <c r="H144" t="s">
-        <v>269</v>
+        <v>764</v>
+      </c>
+      <c r="I144" t="s">
+        <v>252</v>
       </c>
       <c r="J144" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="K144" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="L144">
-        <v>12000000</v>
+        <v>764000000</v>
       </c>
       <c r="M144" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N144" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="O144" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P144" t="b">
         <v>0</v>
@@ -7750,37 +7681,40 @@
         <v>2023</v>
       </c>
       <c r="C145" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D145" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="E145" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="F145">
-        <v>1058</v>
-      </c>
-      <c r="H145" t="s">
-        <v>269</v>
+        <v>1.76</v>
+      </c>
+      <c r="G145" t="s">
+        <v>215</v>
+      </c>
+      <c r="I145" t="s">
+        <v>252</v>
       </c>
       <c r="J145" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="K145" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="L145">
-        <v>1058000000</v>
+        <v>1760000</v>
       </c>
       <c r="M145" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N145" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="O145" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P145" t="b">
         <v>0</v>
@@ -7794,37 +7728,40 @@
         <v>2023</v>
       </c>
       <c r="C146" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D146" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="E146" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="F146">
-        <v>1</v>
-      </c>
-      <c r="H146" t="s">
-        <v>269</v>
+        <v>48.4</v>
+      </c>
+      <c r="G146" t="s">
+        <v>215</v>
+      </c>
+      <c r="I146" t="s">
+        <v>252</v>
       </c>
       <c r="J146" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="K146" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="L146">
-        <v>1000000</v>
+        <v>48400000</v>
       </c>
       <c r="M146" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N146" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="O146" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P146" t="b">
         <v>0</v>
@@ -7838,37 +7775,37 @@
         <v>2023</v>
       </c>
       <c r="C147" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D147" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E147" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F147">
-        <v>131655</v>
+        <v>384285.8</v>
       </c>
       <c r="I147" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="J147" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="K147" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="L147">
-        <v>131655000</v>
+        <v>384285800</v>
       </c>
       <c r="M147" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N147" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O147" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P147" t="b">
         <v>0</v>
@@ -7882,37 +7819,37 @@
         <v>2023</v>
       </c>
       <c r="C148" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D148" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E148" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F148">
-        <v>452775</v>
+        <v>738226.8</v>
       </c>
       <c r="I148" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="J148" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="K148" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="L148">
-        <v>1629990</v>
+        <v>738226800</v>
       </c>
       <c r="M148" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N148" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="O148" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P148" t="b">
         <v>0</v>
@@ -7926,37 +7863,37 @@
         <v>2023</v>
       </c>
       <c r="C149" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D149" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E149" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F149">
-        <v>53673624</v>
+        <v>2946.1</v>
       </c>
       <c r="I149" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="J149" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="K149" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="L149">
-        <v>193225046.4</v>
+        <v>2946100</v>
       </c>
       <c r="M149" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N149" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="O149" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P149" t="b">
         <v>0</v>
@@ -7970,40 +7907,37 @@
         <v>2023</v>
       </c>
       <c r="C150" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D150" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="E150" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F150">
-        <v>10277</v>
-      </c>
-      <c r="G150" t="s">
-        <v>242</v>
+        <v>159325.59885</v>
       </c>
       <c r="I150" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="J150" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="K150" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="L150">
-        <v>10277000</v>
+        <v>159325598.85</v>
       </c>
       <c r="M150" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N150" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O150" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P150" t="b">
         <v>0</v>
@@ -8017,37 +7951,37 @@
         <v>2023</v>
       </c>
       <c r="C151" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D151" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="E151" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F151">
-        <v>40177</v>
-      </c>
-      <c r="I151" t="s">
-        <v>274</v>
+        <v>206946</v>
+      </c>
+      <c r="H151" t="s">
+        <v>247</v>
       </c>
       <c r="J151" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="K151" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="L151">
-        <v>40177000</v>
+        <v>206946000</v>
       </c>
       <c r="M151" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N151" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O151" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P151" t="b">
         <v>0</v>
@@ -8061,40 +7995,37 @@
         <v>2023</v>
       </c>
       <c r="C152" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D152" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E152" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="F152">
-        <v>387.2</v>
-      </c>
-      <c r="G152" t="s">
-        <v>236</v>
-      </c>
-      <c r="I152" t="s">
-        <v>275</v>
+        <v>525946.7</v>
+      </c>
+      <c r="H152" t="s">
+        <v>247</v>
       </c>
       <c r="J152" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="K152" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="L152">
-        <v>387200000</v>
+        <v>525946699.9999999</v>
       </c>
       <c r="M152" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N152" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="O152" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P152" t="b">
         <v>0</v>
@@ -8108,37 +8039,37 @@
         <v>2023</v>
       </c>
       <c r="C153" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D153" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="E153" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="F153">
-        <v>764</v>
-      </c>
-      <c r="I153" t="s">
-        <v>275</v>
+        <v>3350.8</v>
+      </c>
+      <c r="H153" t="s">
+        <v>247</v>
       </c>
       <c r="J153" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="K153" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="L153">
-        <v>764000000</v>
+        <v>3350800</v>
       </c>
       <c r="M153" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N153" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="O153" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P153" t="b">
         <v>0</v>
@@ -8152,40 +8083,37 @@
         <v>2023</v>
       </c>
       <c r="C154" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D154" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E154" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="F154">
-        <v>1.76</v>
-      </c>
-      <c r="G154" t="s">
-        <v>236</v>
-      </c>
-      <c r="I154" t="s">
-        <v>275</v>
+        <v>63958.3</v>
+      </c>
+      <c r="H154" t="s">
+        <v>247</v>
       </c>
       <c r="J154" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="K154" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="L154">
-        <v>1760000</v>
+        <v>63958300</v>
       </c>
       <c r="M154" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N154" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="O154" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P154" t="b">
         <v>0</v>
@@ -8199,40 +8127,37 @@
         <v>2023</v>
       </c>
       <c r="C155" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D155" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="E155" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="F155">
-        <v>48.4</v>
-      </c>
-      <c r="G155" t="s">
-        <v>236</v>
-      </c>
-      <c r="I155" t="s">
-        <v>275</v>
+        <v>33</v>
+      </c>
+      <c r="H155" t="s">
+        <v>247</v>
       </c>
       <c r="J155" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="K155" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="L155">
-        <v>48400000</v>
+        <v>33000</v>
       </c>
       <c r="M155" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N155" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="O155" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P155" t="b">
         <v>0</v>
@@ -8246,37 +8171,37 @@
         <v>2023</v>
       </c>
       <c r="C156" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D156" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="E156" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F156">
-        <v>20.7</v>
-      </c>
-      <c r="I156" t="s">
-        <v>276</v>
+        <v>140100</v>
+      </c>
+      <c r="H156" t="s">
+        <v>248</v>
       </c>
       <c r="J156" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="K156" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="L156">
-        <v>20700</v>
+        <v>140100000</v>
       </c>
       <c r="M156" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N156" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O156" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P156" t="b">
         <v>0</v>
@@ -8290,37 +8215,37 @@
         <v>2023</v>
       </c>
       <c r="C157" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D157" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E157" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F157">
-        <v>384285.8</v>
-      </c>
-      <c r="I157" t="s">
-        <v>276</v>
+        <v>475</v>
+      </c>
+      <c r="H157" t="s">
+        <v>248</v>
       </c>
       <c r="J157" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="K157" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="L157">
-        <v>384285800</v>
+        <v>475000</v>
       </c>
       <c r="M157" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N157" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O157" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P157" t="b">
         <v>0</v>
@@ -8334,37 +8259,37 @@
         <v>2023</v>
       </c>
       <c r="C158" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D158" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="E158" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F158">
-        <v>4889.799999999999</v>
-      </c>
-      <c r="I158" t="s">
-        <v>276</v>
+        <v>960748</v>
+      </c>
+      <c r="H158" t="s">
+        <v>248</v>
       </c>
       <c r="J158" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="K158" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="L158">
-        <v>4889799.999999999</v>
+        <v>960748000</v>
       </c>
       <c r="M158" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N158" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O158" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P158" t="b">
         <v>0</v>
@@ -8378,37 +8303,37 @@
         <v>2023</v>
       </c>
       <c r="C159" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D159" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E159" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F159">
-        <v>738226.8</v>
-      </c>
-      <c r="I159" t="s">
-        <v>276</v>
+        <v>2124</v>
+      </c>
+      <c r="H159" t="s">
+        <v>248</v>
       </c>
       <c r="J159" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="K159" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="L159">
-        <v>738226800</v>
+        <v>2124000</v>
       </c>
       <c r="M159" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N159" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O159" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P159" t="b">
         <v>0</v>
@@ -8422,40 +8347,37 @@
         <v>2023</v>
       </c>
       <c r="C160" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D160" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="E160" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F160">
-        <v>2026.3</v>
-      </c>
-      <c r="G160" t="s">
-        <v>243</v>
-      </c>
-      <c r="I160" t="s">
-        <v>276</v>
+        <v>6344</v>
+      </c>
+      <c r="H160" t="s">
+        <v>248</v>
       </c>
       <c r="J160" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="K160" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="L160">
-        <v>2026300</v>
+        <v>6344000</v>
       </c>
       <c r="M160" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N160" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O160" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P160" t="b">
         <v>0</v>
@@ -8469,661 +8391,39 @@
         <v>2023</v>
       </c>
       <c r="C161" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D161" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E161" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F161">
-        <v>2946.1</v>
-      </c>
-      <c r="I161" t="s">
-        <v>276</v>
+        <v>221612</v>
+      </c>
+      <c r="H161" t="s">
+        <v>248</v>
       </c>
       <c r="J161" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="K161" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="L161">
-        <v>2946100</v>
+        <v>221612000</v>
       </c>
       <c r="M161" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N161" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="O161" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="P161" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:16">
-      <c r="A162" t="s">
-        <v>176</v>
-      </c>
-      <c r="B162">
-        <v>2023</v>
-      </c>
-      <c r="C162" t="s">
-        <v>190</v>
-      </c>
-      <c r="D162" t="s">
-        <v>200</v>
-      </c>
-      <c r="E162" t="s">
-        <v>225</v>
-      </c>
-      <c r="F162">
-        <v>159325.59885</v>
-      </c>
-      <c r="I162" t="s">
-        <v>276</v>
-      </c>
-      <c r="J162" t="s">
-        <v>293</v>
-      </c>
-      <c r="K162" t="s">
-        <v>312</v>
-      </c>
-      <c r="L162">
-        <v>159325598.85</v>
-      </c>
-      <c r="M162" t="s">
-        <v>314</v>
-      </c>
-      <c r="N162" t="s">
-        <v>317</v>
-      </c>
-      <c r="O162" t="s">
-        <v>327</v>
-      </c>
-      <c r="P162" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16">
-      <c r="A163" t="s">
-        <v>177</v>
-      </c>
-      <c r="B163">
-        <v>2023</v>
-      </c>
-      <c r="C163" t="s">
-        <v>190</v>
-      </c>
-      <c r="D163" t="s">
-        <v>222</v>
-      </c>
-      <c r="E163" t="s">
-        <v>225</v>
-      </c>
-      <c r="F163">
-        <v>1530.9</v>
-      </c>
-      <c r="G163" t="s">
-        <v>243</v>
-      </c>
-      <c r="H163" t="s">
-        <v>270</v>
-      </c>
-      <c r="J163" t="s">
-        <v>294</v>
-      </c>
-      <c r="K163" t="s">
-        <v>313</v>
-      </c>
-      <c r="L163">
-        <v>1530900</v>
-      </c>
-      <c r="M163" t="s">
-        <v>314</v>
-      </c>
-      <c r="N163" t="s">
-        <v>317</v>
-      </c>
-      <c r="O163" t="s">
-        <v>327</v>
-      </c>
-      <c r="P163" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16">
-      <c r="A164" t="s">
-        <v>178</v>
-      </c>
-      <c r="B164">
-        <v>2023</v>
-      </c>
-      <c r="C164" t="s">
-        <v>190</v>
-      </c>
-      <c r="D164" t="s">
-        <v>193</v>
-      </c>
-      <c r="E164" t="s">
-        <v>225</v>
-      </c>
-      <c r="F164">
-        <v>206946</v>
-      </c>
-      <c r="H164" t="s">
-        <v>270</v>
-      </c>
-      <c r="J164" t="s">
-        <v>294</v>
-      </c>
-      <c r="K164" t="s">
-        <v>313</v>
-      </c>
-      <c r="L164">
-        <v>206946000</v>
-      </c>
-      <c r="M164" t="s">
-        <v>314</v>
-      </c>
-      <c r="N164" t="s">
-        <v>317</v>
-      </c>
-      <c r="O164" t="s">
-        <v>327</v>
-      </c>
-      <c r="P164" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16">
-      <c r="A165" t="s">
-        <v>179</v>
-      </c>
-      <c r="B165">
-        <v>2023</v>
-      </c>
-      <c r="C165" t="s">
-        <v>190</v>
-      </c>
-      <c r="D165" t="s">
-        <v>195</v>
-      </c>
-      <c r="E165" t="s">
-        <v>225</v>
-      </c>
-      <c r="F165">
-        <v>525946.7</v>
-      </c>
-      <c r="H165" t="s">
-        <v>270</v>
-      </c>
-      <c r="J165" t="s">
-        <v>294</v>
-      </c>
-      <c r="K165" t="s">
-        <v>313</v>
-      </c>
-      <c r="L165">
-        <v>525946699.9999999</v>
-      </c>
-      <c r="M165" t="s">
-        <v>314</v>
-      </c>
-      <c r="N165" t="s">
-        <v>317</v>
-      </c>
-      <c r="O165" t="s">
-        <v>327</v>
-      </c>
-      <c r="P165" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:16">
-      <c r="A166" t="s">
-        <v>180</v>
-      </c>
-      <c r="B166">
-        <v>2023</v>
-      </c>
-      <c r="C166" t="s">
-        <v>190</v>
-      </c>
-      <c r="D166" t="s">
-        <v>223</v>
-      </c>
-      <c r="E166" t="s">
-        <v>225</v>
-      </c>
-      <c r="F166">
-        <v>4260.6</v>
-      </c>
-      <c r="G166" t="s">
-        <v>243</v>
-      </c>
-      <c r="H166" t="s">
-        <v>270</v>
-      </c>
-      <c r="J166" t="s">
-        <v>294</v>
-      </c>
-      <c r="K166" t="s">
-        <v>313</v>
-      </c>
-      <c r="L166">
-        <v>4260600</v>
-      </c>
-      <c r="M166" t="s">
-        <v>314</v>
-      </c>
-      <c r="N166" t="s">
-        <v>317</v>
-      </c>
-      <c r="O166" t="s">
-        <v>327</v>
-      </c>
-      <c r="P166" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16">
-      <c r="A167" t="s">
-        <v>181</v>
-      </c>
-      <c r="B167">
-        <v>2023</v>
-      </c>
-      <c r="C167" t="s">
-        <v>190</v>
-      </c>
-      <c r="D167" t="s">
-        <v>196</v>
-      </c>
-      <c r="E167" t="s">
-        <v>225</v>
-      </c>
-      <c r="F167">
-        <v>3350.8</v>
-      </c>
-      <c r="H167" t="s">
-        <v>270</v>
-      </c>
-      <c r="J167" t="s">
-        <v>294</v>
-      </c>
-      <c r="K167" t="s">
-        <v>313</v>
-      </c>
-      <c r="L167">
-        <v>3350800</v>
-      </c>
-      <c r="M167" t="s">
-        <v>314</v>
-      </c>
-      <c r="N167" t="s">
-        <v>317</v>
-      </c>
-      <c r="O167" t="s">
-        <v>327</v>
-      </c>
-      <c r="P167" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16">
-      <c r="A168" t="s">
-        <v>182</v>
-      </c>
-      <c r="B168">
-        <v>2023</v>
-      </c>
-      <c r="C168" t="s">
-        <v>190</v>
-      </c>
-      <c r="D168" t="s">
-        <v>200</v>
-      </c>
-      <c r="E168" t="s">
-        <v>225</v>
-      </c>
-      <c r="F168">
-        <v>63958.3</v>
-      </c>
-      <c r="H168" t="s">
-        <v>270</v>
-      </c>
-      <c r="J168" t="s">
-        <v>294</v>
-      </c>
-      <c r="K168" t="s">
-        <v>313</v>
-      </c>
-      <c r="L168">
-        <v>63958300</v>
-      </c>
-      <c r="M168" t="s">
-        <v>314</v>
-      </c>
-      <c r="N168" t="s">
-        <v>317</v>
-      </c>
-      <c r="O168" t="s">
-        <v>327</v>
-      </c>
-      <c r="P168" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:16">
-      <c r="A169" t="s">
-        <v>183</v>
-      </c>
-      <c r="B169">
-        <v>2023</v>
-      </c>
-      <c r="C169" t="s">
-        <v>190</v>
-      </c>
-      <c r="D169" t="s">
-        <v>197</v>
-      </c>
-      <c r="E169" t="s">
-        <v>225</v>
-      </c>
-      <c r="F169">
-        <v>33</v>
-      </c>
-      <c r="H169" t="s">
-        <v>270</v>
-      </c>
-      <c r="J169" t="s">
-        <v>294</v>
-      </c>
-      <c r="K169" t="s">
-        <v>313</v>
-      </c>
-      <c r="L169">
-        <v>33000</v>
-      </c>
-      <c r="M169" t="s">
-        <v>314</v>
-      </c>
-      <c r="N169" t="s">
-        <v>317</v>
-      </c>
-      <c r="O169" t="s">
-        <v>327</v>
-      </c>
-      <c r="P169" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:16">
-      <c r="A170" t="s">
-        <v>184</v>
-      </c>
-      <c r="B170">
-        <v>2023</v>
-      </c>
-      <c r="C170" t="s">
-        <v>190</v>
-      </c>
-      <c r="D170" t="s">
-        <v>193</v>
-      </c>
-      <c r="E170" t="s">
-        <v>225</v>
-      </c>
-      <c r="F170">
-        <v>140100</v>
-      </c>
-      <c r="H170" t="s">
-        <v>271</v>
-      </c>
-      <c r="J170" t="s">
-        <v>285</v>
-      </c>
-      <c r="K170" t="s">
-        <v>303</v>
-      </c>
-      <c r="L170">
-        <v>140100000</v>
-      </c>
-      <c r="M170" t="s">
-        <v>314</v>
-      </c>
-      <c r="N170" t="s">
-        <v>317</v>
-      </c>
-      <c r="O170" t="s">
-        <v>327</v>
-      </c>
-      <c r="P170" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:16">
-      <c r="A171" t="s">
-        <v>185</v>
-      </c>
-      <c r="B171">
-        <v>2023</v>
-      </c>
-      <c r="C171" t="s">
-        <v>190</v>
-      </c>
-      <c r="D171" t="s">
-        <v>194</v>
-      </c>
-      <c r="E171" t="s">
-        <v>225</v>
-      </c>
-      <c r="F171">
-        <v>475</v>
-      </c>
-      <c r="H171" t="s">
-        <v>271</v>
-      </c>
-      <c r="J171" t="s">
-        <v>285</v>
-      </c>
-      <c r="K171" t="s">
-        <v>303</v>
-      </c>
-      <c r="L171">
-        <v>475000</v>
-      </c>
-      <c r="M171" t="s">
-        <v>314</v>
-      </c>
-      <c r="N171" t="s">
-        <v>317</v>
-      </c>
-      <c r="O171" t="s">
-        <v>327</v>
-      </c>
-      <c r="P171" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16">
-      <c r="A172" t="s">
-        <v>186</v>
-      </c>
-      <c r="B172">
-        <v>2023</v>
-      </c>
-      <c r="C172" t="s">
-        <v>190</v>
-      </c>
-      <c r="D172" t="s">
-        <v>195</v>
-      </c>
-      <c r="E172" t="s">
-        <v>225</v>
-      </c>
-      <c r="F172">
-        <v>960748</v>
-      </c>
-      <c r="H172" t="s">
-        <v>271</v>
-      </c>
-      <c r="J172" t="s">
-        <v>285</v>
-      </c>
-      <c r="K172" t="s">
-        <v>303</v>
-      </c>
-      <c r="L172">
-        <v>960748000</v>
-      </c>
-      <c r="M172" t="s">
-        <v>314</v>
-      </c>
-      <c r="N172" t="s">
-        <v>317</v>
-      </c>
-      <c r="O172" t="s">
-        <v>327</v>
-      </c>
-      <c r="P172" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:16">
-      <c r="A173" t="s">
-        <v>187</v>
-      </c>
-      <c r="B173">
-        <v>2023</v>
-      </c>
-      <c r="C173" t="s">
-        <v>190</v>
-      </c>
-      <c r="D173" t="s">
-        <v>196</v>
-      </c>
-      <c r="E173" t="s">
-        <v>225</v>
-      </c>
-      <c r="F173">
-        <v>2124</v>
-      </c>
-      <c r="H173" t="s">
-        <v>271</v>
-      </c>
-      <c r="J173" t="s">
-        <v>285</v>
-      </c>
-      <c r="K173" t="s">
-        <v>303</v>
-      </c>
-      <c r="L173">
-        <v>2124000</v>
-      </c>
-      <c r="M173" t="s">
-        <v>314</v>
-      </c>
-      <c r="N173" t="s">
-        <v>317</v>
-      </c>
-      <c r="O173" t="s">
-        <v>327</v>
-      </c>
-      <c r="P173" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16">
-      <c r="A174" t="s">
-        <v>188</v>
-      </c>
-      <c r="B174">
-        <v>2023</v>
-      </c>
-      <c r="C174" t="s">
-        <v>190</v>
-      </c>
-      <c r="D174" t="s">
-        <v>224</v>
-      </c>
-      <c r="E174" t="s">
-        <v>225</v>
-      </c>
-      <c r="F174">
-        <v>6344</v>
-      </c>
-      <c r="H174" t="s">
-        <v>271</v>
-      </c>
-      <c r="J174" t="s">
-        <v>285</v>
-      </c>
-      <c r="K174" t="s">
-        <v>303</v>
-      </c>
-      <c r="L174">
-        <v>6344000</v>
-      </c>
-      <c r="M174" t="s">
-        <v>314</v>
-      </c>
-      <c r="N174" t="s">
-        <v>317</v>
-      </c>
-      <c r="O174" t="s">
-        <v>327</v>
-      </c>
-      <c r="P174" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:16">
-      <c r="A175" t="s">
-        <v>189</v>
-      </c>
-      <c r="B175">
-        <v>2023</v>
-      </c>
-      <c r="C175" t="s">
-        <v>190</v>
-      </c>
-      <c r="D175" t="s">
-        <v>200</v>
-      </c>
-      <c r="E175" t="s">
-        <v>225</v>
-      </c>
-      <c r="F175">
-        <v>221612</v>
-      </c>
-      <c r="H175" t="s">
-        <v>271</v>
-      </c>
-      <c r="J175" t="s">
-        <v>285</v>
-      </c>
-      <c r="K175" t="s">
-        <v>303</v>
-      </c>
-      <c r="L175">
-        <v>221612000</v>
-      </c>
-      <c r="M175" t="s">
-        <v>314</v>
-      </c>
-      <c r="N175" t="s">
-        <v>317</v>
-      </c>
-      <c r="O175" t="s">
-        <v>327</v>
-      </c>
-      <c r="P175" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/MetalliCan/pre_cleaned_data/energy_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/energy_df.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_479102E418C3C8187B2D4CD215AB3FE57879A36C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38D17008-2F85-4517-8259-8B3600D61375}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$161</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -931,8 +940,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -995,13 +1004,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1039,7 +1056,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1073,6 +1090,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1107,9 +1125,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1282,11 +1301,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P161"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="193.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="72.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1336,7 +1374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1353,7 +1391,7 @@
         <v>205</v>
       </c>
       <c r="F2">
-        <v>18.475650648</v>
+        <v>18.475650647999998</v>
       </c>
       <c r="H2" t="s">
         <v>221</v>
@@ -1365,7 +1403,7 @@
         <v>272</v>
       </c>
       <c r="L2">
-        <v>18475.650648</v>
+        <v>18475.650647999999</v>
       </c>
       <c r="M2" t="s">
         <v>291</v>
@@ -1380,7 +1418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1397,7 +1435,7 @@
         <v>205</v>
       </c>
       <c r="F3">
-        <v>72676.1107896</v>
+        <v>72676.110789600003</v>
       </c>
       <c r="H3" t="s">
         <v>221</v>
@@ -1424,7 +1462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1441,7 +1479,7 @@
         <v>205</v>
       </c>
       <c r="F4">
-        <v>287042.447231542</v>
+        <v>287042.44723154203</v>
       </c>
       <c r="H4" t="s">
         <v>221</v>
@@ -1453,7 +1491,7 @@
         <v>272</v>
       </c>
       <c r="L4">
-        <v>287042447.2315421</v>
+        <v>287042447.23154211</v>
       </c>
       <c r="M4" t="s">
         <v>291</v>
@@ -1468,7 +1506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1485,7 +1523,7 @@
         <v>205</v>
       </c>
       <c r="F5">
-        <v>86225.1173956</v>
+        <v>86225.117395599998</v>
       </c>
       <c r="H5" t="s">
         <v>221</v>
@@ -1497,7 +1535,7 @@
         <v>272</v>
       </c>
       <c r="L5">
-        <v>86225117.39559999</v>
+        <v>86225117.395599991</v>
       </c>
       <c r="M5" t="s">
         <v>291</v>
@@ -1512,7 +1550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1529,7 +1567,7 @@
         <v>205</v>
       </c>
       <c r="F6">
-        <v>569009.5848</v>
+        <v>569009.58479999995</v>
       </c>
       <c r="H6" t="s">
         <v>221</v>
@@ -1541,7 +1579,7 @@
         <v>272</v>
       </c>
       <c r="L6">
-        <v>569009584.8</v>
+        <v>569009584.79999995</v>
       </c>
       <c r="M6" t="s">
         <v>291</v>
@@ -1556,7 +1594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1600,7 +1638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1617,7 +1655,7 @@
         <v>205</v>
       </c>
       <c r="F8">
-        <v>42071.0413</v>
+        <v>42071.041299999997</v>
       </c>
       <c r="H8" t="s">
         <v>221</v>
@@ -1629,7 +1667,7 @@
         <v>272</v>
       </c>
       <c r="L8">
-        <v>42071041.3</v>
+        <v>42071041.299999997</v>
       </c>
       <c r="M8" t="s">
         <v>291</v>
@@ -1644,7 +1682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1661,7 +1699,7 @@
         <v>205</v>
       </c>
       <c r="F9">
-        <v>2344.0244</v>
+        <v>2344.0243999999998</v>
       </c>
       <c r="H9" t="s">
         <v>221</v>
@@ -1688,7 +1726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1732,7 +1770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1761,7 +1799,7 @@
         <v>273</v>
       </c>
       <c r="L11">
-        <v>2428287789.6</v>
+        <v>2428287789.5999999</v>
       </c>
       <c r="M11" t="s">
         <v>291</v>
@@ -1776,7 +1814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1820,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -1864,7 +1902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1881,7 +1919,7 @@
         <v>205</v>
       </c>
       <c r="F14">
-        <v>1463.60937</v>
+        <v>1463.6093699999999</v>
       </c>
       <c r="H14" t="s">
         <v>222</v>
@@ -1908,7 +1946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1955,7 +1993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1984,7 +2022,7 @@
         <v>275</v>
       </c>
       <c r="L16">
-        <v>378542030.2939668</v>
+        <v>378542030.29396683</v>
       </c>
       <c r="M16" t="s">
         <v>292</v>
@@ -1999,7 +2037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -2028,7 +2066,7 @@
         <v>275</v>
       </c>
       <c r="L17">
-        <v>495635929.2</v>
+        <v>495635929.19999999</v>
       </c>
       <c r="M17" t="s">
         <v>291</v>
@@ -2043,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -2072,7 +2110,7 @@
         <v>275</v>
       </c>
       <c r="L18">
-        <v>17908178.0536758</v>
+        <v>17908178.053675801</v>
       </c>
       <c r="M18" t="s">
         <v>292</v>
@@ -2087,7 +2125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -2116,7 +2154,7 @@
         <v>275</v>
       </c>
       <c r="L19">
-        <v>42813081.77158993</v>
+        <v>42813081.771589927</v>
       </c>
       <c r="M19" t="s">
         <v>292</v>
@@ -2131,7 +2169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -2148,7 +2186,7 @@
         <v>209</v>
       </c>
       <c r="F20">
-        <v>80.95999999999999</v>
+        <v>80.959999999999994</v>
       </c>
       <c r="G20" t="s">
         <v>215</v>
@@ -2178,7 +2216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -2222,7 +2260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -2239,7 +2277,7 @@
         <v>209</v>
       </c>
       <c r="F22">
-        <v>0.368</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="G22" t="s">
         <v>215</v>
@@ -2269,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -2286,7 +2324,7 @@
         <v>209</v>
       </c>
       <c r="F23">
-        <v>10.12</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="G23" t="s">
         <v>215</v>
@@ -2316,7 +2354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -2360,7 +2398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -2389,7 +2427,7 @@
         <v>273</v>
       </c>
       <c r="L25">
-        <v>2991452173.2</v>
+        <v>2991452173.1999998</v>
       </c>
       <c r="M25" t="s">
         <v>291</v>
@@ -2404,7 +2442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -2448,7 +2486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -2492,7 +2530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2536,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -2553,7 +2591,7 @@
         <v>207</v>
       </c>
       <c r="F29">
-        <v>34190.62</v>
+        <v>34190.620000000003</v>
       </c>
       <c r="G29" t="s">
         <v>216</v>
@@ -2583,7 +2621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -2600,7 +2638,7 @@
         <v>207</v>
       </c>
       <c r="F30">
-        <v>38555.38</v>
+        <v>38555.379999999997</v>
       </c>
       <c r="G30" t="s">
         <v>216</v>
@@ -2630,7 +2668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -2674,7 +2712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -2703,7 +2741,7 @@
         <v>277</v>
       </c>
       <c r="L32">
-        <v>57828505.6</v>
+        <v>57828505.600000001</v>
       </c>
       <c r="M32" t="s">
         <v>292</v>
@@ -2718,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -2735,7 +2773,7 @@
         <v>205</v>
       </c>
       <c r="F33">
-        <v>21662.09888</v>
+        <v>21662.098880000001</v>
       </c>
       <c r="H33" t="s">
         <v>228</v>
@@ -2747,7 +2785,7 @@
         <v>272</v>
       </c>
       <c r="L33">
-        <v>21662098.88</v>
+        <v>21662098.879999999</v>
       </c>
       <c r="M33" t="s">
         <v>291</v>
@@ -2762,7 +2800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -2779,7 +2817,7 @@
         <v>205</v>
       </c>
       <c r="F34">
-        <v>385327.7974</v>
+        <v>385327.79739999998</v>
       </c>
       <c r="H34" t="s">
         <v>228</v>
@@ -2791,7 +2829,7 @@
         <v>272</v>
       </c>
       <c r="L34">
-        <v>385327797.4</v>
+        <v>385327797.39999998</v>
       </c>
       <c r="M34" t="s">
         <v>291</v>
@@ -2806,7 +2844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -2850,7 +2888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -2867,7 +2905,7 @@
         <v>205</v>
       </c>
       <c r="F36">
-        <v>892229.95044</v>
+        <v>892229.95044000004</v>
       </c>
       <c r="H36" t="s">
         <v>228</v>
@@ -2879,7 +2917,7 @@
         <v>272</v>
       </c>
       <c r="L36">
-        <v>892229950.4400001</v>
+        <v>892229950.44000006</v>
       </c>
       <c r="M36" t="s">
         <v>291</v>
@@ -2894,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -2911,7 +2949,7 @@
         <v>205</v>
       </c>
       <c r="F37">
-        <v>10018.1179</v>
+        <v>10018.117899999999</v>
       </c>
       <c r="H37" t="s">
         <v>228</v>
@@ -2938,7 +2976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>52</v>
       </c>
@@ -2955,7 +2993,7 @@
         <v>205</v>
       </c>
       <c r="F38">
-        <v>142393.17415</v>
+        <v>142393.17415000001</v>
       </c>
       <c r="H38" t="s">
         <v>228</v>
@@ -2967,7 +3005,7 @@
         <v>272</v>
       </c>
       <c r="L38">
-        <v>142393174.15</v>
+        <v>142393174.15000001</v>
       </c>
       <c r="M38" t="s">
         <v>291</v>
@@ -2982,7 +3020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -3026,7 +3064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -3070,7 +3108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -3114,7 +3152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>56</v>
       </c>
@@ -3158,7 +3196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>57</v>
       </c>
@@ -3202,7 +3240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -3246,7 +3284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -3290,7 +3328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -3334,7 +3372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -3378,7 +3416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>62</v>
       </c>
@@ -3422,7 +3460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>63</v>
       </c>
@@ -3466,7 +3504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>64</v>
       </c>
@@ -3510,7 +3548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>65</v>
       </c>
@@ -3554,7 +3592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -3598,7 +3636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>67</v>
       </c>
@@ -3642,7 +3680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -3686,7 +3724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>69</v>
       </c>
@@ -3715,7 +3753,7 @@
         <v>275</v>
       </c>
       <c r="L55">
-        <v>55697075.44526765</v>
+        <v>55697075.445267648</v>
       </c>
       <c r="M55" t="s">
         <v>292</v>
@@ -3730,7 +3768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -3759,7 +3797,7 @@
         <v>275</v>
       </c>
       <c r="L56">
-        <v>63343396.8</v>
+        <v>63343396.799999997</v>
       </c>
       <c r="M56" t="s">
         <v>291</v>
@@ -3774,7 +3812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>71</v>
       </c>
@@ -3803,7 +3841,7 @@
         <v>275</v>
       </c>
       <c r="L57">
-        <v>8333350.1134884</v>
+        <v>8333350.1134884004</v>
       </c>
       <c r="M57" t="s">
         <v>292</v>
@@ -3818,7 +3856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -3847,7 +3885,7 @@
         <v>275</v>
       </c>
       <c r="L58">
-        <v>36595602.20983067</v>
+        <v>36595602.209830672</v>
       </c>
       <c r="M58" t="s">
         <v>292</v>
@@ -3862,7 +3900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>73</v>
       </c>
@@ -3906,7 +3944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -3953,7 +3991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>75</v>
       </c>
@@ -4000,7 +4038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>76</v>
       </c>
@@ -4044,7 +4082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -4091,7 +4129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>78</v>
       </c>
@@ -4135,7 +4173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>79</v>
       </c>
@@ -4179,7 +4217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>80</v>
       </c>
@@ -4223,7 +4261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>81</v>
       </c>
@@ -4267,7 +4305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>82</v>
       </c>
@@ -4311,7 +4349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -4355,7 +4393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>84</v>
       </c>
@@ -4399,7 +4437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>85</v>
       </c>
@@ -4443,7 +4481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>86</v>
       </c>
@@ -4487,7 +4525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>87</v>
       </c>
@@ -4531,7 +4569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>88</v>
       </c>
@@ -4575,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>89</v>
       </c>
@@ -4619,7 +4657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>90</v>
       </c>
@@ -4663,7 +4701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>91</v>
       </c>
@@ -4707,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>92</v>
       </c>
@@ -4751,7 +4789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>93</v>
       </c>
@@ -4795,7 +4833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -4839,7 +4877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>95</v>
       </c>
@@ -4883,7 +4921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>96</v>
       </c>
@@ -4927,7 +4965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>97</v>
       </c>
@@ -4971,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -5000,7 +5038,7 @@
         <v>273</v>
       </c>
       <c r="L84">
-        <v>593954510.4</v>
+        <v>593954510.39999998</v>
       </c>
       <c r="M84" t="s">
         <v>291</v>
@@ -5015,7 +5053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>99</v>
       </c>
@@ -5059,7 +5097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>100</v>
       </c>
@@ -5103,7 +5141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>101</v>
       </c>
@@ -5147,7 +5185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>102</v>
       </c>
@@ -5191,7 +5229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>103</v>
       </c>
@@ -5220,7 +5258,7 @@
         <v>273</v>
       </c>
       <c r="L89">
-        <v>477755733.6</v>
+        <v>477755733.60000002</v>
       </c>
       <c r="M89" t="s">
         <v>291</v>
@@ -5235,7 +5273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>104</v>
       </c>
@@ -5279,7 +5317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>105</v>
       </c>
@@ -5296,7 +5334,7 @@
         <v>205</v>
       </c>
       <c r="F91">
-        <v>929608.636977058</v>
+        <v>929608.63697705802</v>
       </c>
       <c r="G91" t="s">
         <v>218</v>
@@ -5311,7 +5349,7 @@
         <v>283</v>
       </c>
       <c r="L91">
-        <v>929608636.9770581</v>
+        <v>929608636.97705805</v>
       </c>
       <c r="M91" t="s">
         <v>291</v>
@@ -5326,7 +5364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>106</v>
       </c>
@@ -5343,7 +5381,7 @@
         <v>205</v>
       </c>
       <c r="F92">
-        <v>365541.6666666667</v>
+        <v>365541.66666666669</v>
       </c>
       <c r="G92" t="s">
         <v>219</v>
@@ -5358,7 +5396,7 @@
         <v>283</v>
       </c>
       <c r="L92">
-        <v>365541666.6666667</v>
+        <v>365541666.66666669</v>
       </c>
       <c r="M92" t="s">
         <v>291</v>
@@ -5373,7 +5411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>107</v>
       </c>
@@ -5387,7 +5425,7 @@
         <v>205</v>
       </c>
       <c r="F93">
-        <v>36282.05128205128</v>
+        <v>36282.051282051281</v>
       </c>
       <c r="G93" t="s">
         <v>219</v>
@@ -5417,7 +5455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>108</v>
       </c>
@@ -5434,7 +5472,7 @@
         <v>205</v>
       </c>
       <c r="F94">
-        <v>21012.14574898786</v>
+        <v>21012.145748987859</v>
       </c>
       <c r="G94" t="s">
         <v>218</v>
@@ -5449,7 +5487,7 @@
         <v>283</v>
       </c>
       <c r="L94">
-        <v>21012145.74898786</v>
+        <v>21012145.748987861</v>
       </c>
       <c r="M94" t="s">
         <v>291</v>
@@ -5464,7 +5502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>109</v>
       </c>
@@ -5481,7 +5519,7 @@
         <v>205</v>
       </c>
       <c r="F95">
-        <v>22737.89649415693</v>
+        <v>22737.896494156928</v>
       </c>
       <c r="G95" t="s">
         <v>218</v>
@@ -5496,7 +5534,7 @@
         <v>283</v>
       </c>
       <c r="L95">
-        <v>22737896.49415693</v>
+        <v>22737896.494156931</v>
       </c>
       <c r="M95" t="s">
         <v>291</v>
@@ -5511,7 +5549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>110</v>
       </c>
@@ -5528,7 +5566,7 @@
         <v>205</v>
       </c>
       <c r="F96">
-        <v>27653.22904</v>
+        <v>27653.229039999998</v>
       </c>
       <c r="H96" t="s">
         <v>241</v>
@@ -5540,7 +5578,7 @@
         <v>272</v>
       </c>
       <c r="L96">
-        <v>27653229.04</v>
+        <v>27653229.039999999</v>
       </c>
       <c r="M96" t="s">
         <v>291</v>
@@ -5555,7 +5593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>111</v>
       </c>
@@ -5599,7 +5637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>112</v>
       </c>
@@ -5628,7 +5666,7 @@
         <v>272</v>
       </c>
       <c r="L98">
-        <v>308614730.821</v>
+        <v>308614730.82099998</v>
       </c>
       <c r="M98" t="s">
         <v>291</v>
@@ -5643,7 +5681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>113</v>
       </c>
@@ -5672,7 +5710,7 @@
         <v>272</v>
       </c>
       <c r="L99">
-        <v>3808984.28206273</v>
+        <v>3808984.2820627298</v>
       </c>
       <c r="M99" t="s">
         <v>291</v>
@@ -5687,7 +5725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>114</v>
       </c>
@@ -5731,7 +5769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>115</v>
       </c>
@@ -5748,7 +5786,7 @@
         <v>205</v>
       </c>
       <c r="F101">
-        <v>5437.635</v>
+        <v>5437.6350000000002</v>
       </c>
       <c r="H101" t="s">
         <v>241</v>
@@ -5775,7 +5813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>116</v>
       </c>
@@ -5804,7 +5842,7 @@
         <v>272</v>
       </c>
       <c r="L102">
-        <v>229891868.95</v>
+        <v>229891868.94999999</v>
       </c>
       <c r="M102" t="s">
         <v>291</v>
@@ -5819,7 +5857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>117</v>
       </c>
@@ -5863,7 +5901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>118</v>
       </c>
@@ -5880,7 +5918,7 @@
         <v>213</v>
       </c>
       <c r="F104">
-        <v>4761600.1</v>
+        <v>4761600.0999999996</v>
       </c>
       <c r="H104" t="s">
         <v>242</v>
@@ -5907,7 +5945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>119</v>
       </c>
@@ -5924,7 +5962,7 @@
         <v>205</v>
       </c>
       <c r="F105">
-        <v>56414.6765</v>
+        <v>56414.676500000001</v>
       </c>
       <c r="H105" t="s">
         <v>242</v>
@@ -5951,7 +5989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>120</v>
       </c>
@@ -5995,7 +6033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>121</v>
       </c>
@@ -6024,7 +6062,7 @@
         <v>284</v>
       </c>
       <c r="L107">
-        <v>3914535.152</v>
+        <v>3914535.1519999998</v>
       </c>
       <c r="M107" t="s">
         <v>292</v>
@@ -6039,7 +6077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>122</v>
       </c>
@@ -6083,7 +6121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>123</v>
       </c>
@@ -6112,7 +6150,7 @@
         <v>284</v>
       </c>
       <c r="L109">
-        <v>710263.5224</v>
+        <v>710263.52240000002</v>
       </c>
       <c r="M109" t="s">
         <v>292</v>
@@ -6127,7 +6165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>124</v>
       </c>
@@ -6144,7 +6182,7 @@
         <v>205</v>
       </c>
       <c r="F110">
-        <v>23524.436671511</v>
+        <v>23524.436671511001</v>
       </c>
       <c r="I110" t="s">
         <v>250</v>
@@ -6156,7 +6194,7 @@
         <v>272</v>
       </c>
       <c r="L110">
-        <v>23524436.671511</v>
+        <v>23524436.671510998</v>
       </c>
       <c r="M110" t="s">
         <v>291</v>
@@ -6171,7 +6209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>125</v>
       </c>
@@ -6188,7 +6226,7 @@
         <v>205</v>
       </c>
       <c r="F111">
-        <v>623021.8686160001</v>
+        <v>623021.86861600005</v>
       </c>
       <c r="I111" t="s">
         <v>250</v>
@@ -6200,7 +6238,7 @@
         <v>272</v>
       </c>
       <c r="L111">
-        <v>623021868.6160001</v>
+        <v>623021868.61600006</v>
       </c>
       <c r="M111" t="s">
         <v>291</v>
@@ -6215,7 +6253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>126</v>
       </c>
@@ -6232,7 +6270,7 @@
         <v>205</v>
       </c>
       <c r="F112">
-        <v>91025.4822599152</v>
+        <v>91025.482259915196</v>
       </c>
       <c r="I112" t="s">
         <v>250</v>
@@ -6244,7 +6282,7 @@
         <v>272</v>
       </c>
       <c r="L112">
-        <v>91025482.2599152</v>
+        <v>91025482.259915203</v>
       </c>
       <c r="M112" t="s">
         <v>291</v>
@@ -6259,7 +6297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>127</v>
       </c>
@@ -6303,7 +6341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>128</v>
       </c>
@@ -6347,7 +6385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>129</v>
       </c>
@@ -6391,7 +6429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>130</v>
       </c>
@@ -6408,7 +6446,7 @@
         <v>205</v>
       </c>
       <c r="F116">
-        <v>6336.0580703</v>
+        <v>6336.0580702999996</v>
       </c>
       <c r="I116" t="s">
         <v>250</v>
@@ -6420,7 +6458,7 @@
         <v>272</v>
       </c>
       <c r="L116">
-        <v>6336058.0703</v>
+        <v>6336058.0702999998</v>
       </c>
       <c r="M116" t="s">
         <v>291</v>
@@ -6435,7 +6473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>131</v>
       </c>
@@ -6452,7 +6490,7 @@
         <v>213</v>
       </c>
       <c r="F117">
-        <v>42378137.86</v>
+        <v>42378137.859999999</v>
       </c>
       <c r="H117" t="s">
         <v>243</v>
@@ -6464,7 +6502,7 @@
         <v>284</v>
       </c>
       <c r="L117">
-        <v>1521587039.8633</v>
+        <v>1521587039.8633001</v>
       </c>
       <c r="M117" t="s">
         <v>292</v>
@@ -6479,7 +6517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>132</v>
       </c>
@@ -6523,7 +6561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>133</v>
       </c>
@@ -6540,7 +6578,7 @@
         <v>213</v>
       </c>
       <c r="F119">
-        <v>1147190.1</v>
+        <v>1147190.1000000001</v>
       </c>
       <c r="H119" t="s">
         <v>243</v>
@@ -6567,7 +6605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>134</v>
       </c>
@@ -6596,7 +6634,7 @@
         <v>284</v>
       </c>
       <c r="L120">
-        <v>84441809.056336</v>
+        <v>84441809.056336001</v>
       </c>
       <c r="M120" t="s">
         <v>292</v>
@@ -6611,7 +6649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>135</v>
       </c>
@@ -6655,7 +6693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>136</v>
       </c>
@@ -6672,7 +6710,7 @@
         <v>205</v>
       </c>
       <c r="F122">
-        <v>121071.915388</v>
+        <v>121071.91538799999</v>
       </c>
       <c r="H122" t="s">
         <v>244</v>
@@ -6699,7 +6737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>137</v>
       </c>
@@ -6716,7 +6754,7 @@
         <v>205</v>
       </c>
       <c r="F123">
-        <v>1361713.858312</v>
+        <v>1361713.8583120001</v>
       </c>
       <c r="H123" t="s">
         <v>244</v>
@@ -6743,7 +6781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>138</v>
       </c>
@@ -6760,7 +6798,7 @@
         <v>205</v>
       </c>
       <c r="F124">
-        <v>5528.5667</v>
+        <v>5528.5667000000003</v>
       </c>
       <c r="H124" t="s">
         <v>244</v>
@@ -6772,7 +6810,7 @@
         <v>272</v>
       </c>
       <c r="L124">
-        <v>5528566.7</v>
+        <v>5528566.7000000002</v>
       </c>
       <c r="M124" t="s">
         <v>291</v>
@@ -6787,7 +6825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>139</v>
       </c>
@@ -6804,7 +6842,7 @@
         <v>205</v>
       </c>
       <c r="F125">
-        <v>1274584.3416</v>
+        <v>1274584.3415999999</v>
       </c>
       <c r="H125" t="s">
         <v>244</v>
@@ -6816,7 +6854,7 @@
         <v>272</v>
       </c>
       <c r="L125">
-        <v>1274584341.6</v>
+        <v>1274584341.5999999</v>
       </c>
       <c r="M125" t="s">
         <v>291</v>
@@ -6831,7 +6869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>140</v>
       </c>
@@ -6875,7 +6913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>141</v>
       </c>
@@ -6892,7 +6930,7 @@
         <v>205</v>
       </c>
       <c r="F127">
-        <v>80313.18580000001</v>
+        <v>80313.185800000007</v>
       </c>
       <c r="H127" t="s">
         <v>244</v>
@@ -6904,7 +6942,7 @@
         <v>272</v>
       </c>
       <c r="L127">
-        <v>80313185.80000001</v>
+        <v>80313185.800000012</v>
       </c>
       <c r="M127" t="s">
         <v>291</v>
@@ -6919,7 +6957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>142</v>
       </c>
@@ -6963,7 +7001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>143</v>
       </c>
@@ -6992,7 +7030,7 @@
         <v>285</v>
       </c>
       <c r="L129">
-        <v>893875119.6906</v>
+        <v>893875119.69060004</v>
       </c>
       <c r="M129" t="s">
         <v>291</v>
@@ -7007,7 +7045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>144</v>
       </c>
@@ -7051,7 +7089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -7080,7 +7118,7 @@
         <v>285</v>
       </c>
       <c r="L131">
-        <v>14655632.81055998</v>
+        <v>14655632.810559981</v>
       </c>
       <c r="M131" t="s">
         <v>292</v>
@@ -7095,7 +7133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>146</v>
       </c>
@@ -7139,7 +7177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>147</v>
       </c>
@@ -7183,7 +7221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>148</v>
       </c>
@@ -7227,7 +7265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>149</v>
       </c>
@@ -7271,7 +7309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>150</v>
       </c>
@@ -7315,7 +7353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>151</v>
       </c>
@@ -7359,7 +7397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>152</v>
       </c>
@@ -7403,7 +7441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>153</v>
       </c>
@@ -7447,7 +7485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>154</v>
       </c>
@@ -7476,7 +7514,7 @@
         <v>288</v>
       </c>
       <c r="L140">
-        <v>193225046.4</v>
+        <v>193225046.40000001</v>
       </c>
       <c r="M140" t="s">
         <v>291</v>
@@ -7491,7 +7529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>155</v>
       </c>
@@ -7538,7 +7576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>156</v>
       </c>
@@ -7582,7 +7620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -7629,7 +7667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>158</v>
       </c>
@@ -7673,7 +7711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>159</v>
       </c>
@@ -7720,7 +7758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>160</v>
       </c>
@@ -7767,7 +7805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>161</v>
       </c>
@@ -7811,7 +7849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>162</v>
       </c>
@@ -7855,7 +7893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>163</v>
       </c>
@@ -7899,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>164</v>
       </c>
@@ -7916,7 +7954,7 @@
         <v>205</v>
       </c>
       <c r="F150">
-        <v>159325.59885</v>
+        <v>159325.59885000001</v>
       </c>
       <c r="I150" t="s">
         <v>253</v>
@@ -7928,7 +7966,7 @@
         <v>289</v>
       </c>
       <c r="L150">
-        <v>159325598.85</v>
+        <v>159325598.84999999</v>
       </c>
       <c r="M150" t="s">
         <v>291</v>
@@ -7943,7 +7981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>165</v>
       </c>
@@ -7987,7 +8025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>166</v>
       </c>
@@ -8004,7 +8042,7 @@
         <v>205</v>
       </c>
       <c r="F152">
-        <v>525946.7</v>
+        <v>525946.69999999995</v>
       </c>
       <c r="H152" t="s">
         <v>247</v>
@@ -8016,7 +8054,7 @@
         <v>290</v>
       </c>
       <c r="L152">
-        <v>525946699.9999999</v>
+        <v>525946699.99999988</v>
       </c>
       <c r="M152" t="s">
         <v>291</v>
@@ -8031,7 +8069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>167</v>
       </c>
@@ -8075,7 +8113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>168</v>
       </c>
@@ -8119,7 +8157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>169</v>
       </c>
@@ -8163,7 +8201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>170</v>
       </c>
@@ -8207,7 +8245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>171</v>
       </c>
@@ -8251,7 +8289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>172</v>
       </c>
@@ -8295,7 +8333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>173</v>
       </c>
@@ -8339,7 +8377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>174</v>
       </c>
@@ -8383,7 +8421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>175</v>
       </c>
@@ -8428,6 +8466,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P161" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="GRP-14bfbb82"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MetalliCan/pre_cleaned_data/energy_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/energy_df.xlsx
@@ -1,24 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_479102E418C3C8187B2D4CD215AB3FE57879A36C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38D17008-2F85-4517-8259-8B3600D61375}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$161</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -940,8 +931,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1004,21 +995,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1056,7 +1039,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1090,7 +1073,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1125,10 +1107,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1301,30 +1282,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P161"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="193.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="72.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1374,7 +1336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1391,7 +1353,7 @@
         <v>205</v>
       </c>
       <c r="F2">
-        <v>18.475650647999998</v>
+        <v>18.475650648</v>
       </c>
       <c r="H2" t="s">
         <v>221</v>
@@ -1403,7 +1365,7 @@
         <v>272</v>
       </c>
       <c r="L2">
-        <v>18475.650647999999</v>
+        <v>18475.650648</v>
       </c>
       <c r="M2" t="s">
         <v>291</v>
@@ -1418,7 +1380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1435,7 +1397,7 @@
         <v>205</v>
       </c>
       <c r="F3">
-        <v>72676.110789600003</v>
+        <v>72676.1107896</v>
       </c>
       <c r="H3" t="s">
         <v>221</v>
@@ -1462,7 +1424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1479,7 +1441,7 @@
         <v>205</v>
       </c>
       <c r="F4">
-        <v>287042.44723154203</v>
+        <v>287042.447231542</v>
       </c>
       <c r="H4" t="s">
         <v>221</v>
@@ -1491,7 +1453,7 @@
         <v>272</v>
       </c>
       <c r="L4">
-        <v>287042447.23154211</v>
+        <v>287042447.2315421</v>
       </c>
       <c r="M4" t="s">
         <v>291</v>
@@ -1506,7 +1468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1523,7 +1485,7 @@
         <v>205</v>
       </c>
       <c r="F5">
-        <v>86225.117395599998</v>
+        <v>86225.1173956</v>
       </c>
       <c r="H5" t="s">
         <v>221</v>
@@ -1535,7 +1497,7 @@
         <v>272</v>
       </c>
       <c r="L5">
-        <v>86225117.395599991</v>
+        <v>86225117.39559999</v>
       </c>
       <c r="M5" t="s">
         <v>291</v>
@@ -1550,7 +1512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1567,7 +1529,7 @@
         <v>205</v>
       </c>
       <c r="F6">
-        <v>569009.58479999995</v>
+        <v>569009.5848</v>
       </c>
       <c r="H6" t="s">
         <v>221</v>
@@ -1579,7 +1541,7 @@
         <v>272</v>
       </c>
       <c r="L6">
-        <v>569009584.79999995</v>
+        <v>569009584.8</v>
       </c>
       <c r="M6" t="s">
         <v>291</v>
@@ -1594,7 +1556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1638,7 +1600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1655,7 +1617,7 @@
         <v>205</v>
       </c>
       <c r="F8">
-        <v>42071.041299999997</v>
+        <v>42071.0413</v>
       </c>
       <c r="H8" t="s">
         <v>221</v>
@@ -1667,7 +1629,7 @@
         <v>272</v>
       </c>
       <c r="L8">
-        <v>42071041.299999997</v>
+        <v>42071041.3</v>
       </c>
       <c r="M8" t="s">
         <v>291</v>
@@ -1682,7 +1644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1699,7 +1661,7 @@
         <v>205</v>
       </c>
       <c r="F9">
-        <v>2344.0243999999998</v>
+        <v>2344.0244</v>
       </c>
       <c r="H9" t="s">
         <v>221</v>
@@ -1726,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1770,7 +1732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1799,7 +1761,7 @@
         <v>273</v>
       </c>
       <c r="L11">
-        <v>2428287789.5999999</v>
+        <v>2428287789.6</v>
       </c>
       <c r="M11" t="s">
         <v>291</v>
@@ -1814,7 +1776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1858,7 +1820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -1902,7 +1864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1919,7 +1881,7 @@
         <v>205</v>
       </c>
       <c r="F14">
-        <v>1463.6093699999999</v>
+        <v>1463.60937</v>
       </c>
       <c r="H14" t="s">
         <v>222</v>
@@ -1946,7 +1908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1993,7 +1955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2022,7 +1984,7 @@
         <v>275</v>
       </c>
       <c r="L16">
-        <v>378542030.29396683</v>
+        <v>378542030.2939668</v>
       </c>
       <c r="M16" t="s">
         <v>292</v>
@@ -2037,7 +1999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -2066,7 +2028,7 @@
         <v>275</v>
       </c>
       <c r="L17">
-        <v>495635929.19999999</v>
+        <v>495635929.2</v>
       </c>
       <c r="M17" t="s">
         <v>291</v>
@@ -2081,7 +2043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -2110,7 +2072,7 @@
         <v>275</v>
       </c>
       <c r="L18">
-        <v>17908178.053675801</v>
+        <v>17908178.0536758</v>
       </c>
       <c r="M18" t="s">
         <v>292</v>
@@ -2125,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -2154,7 +2116,7 @@
         <v>275</v>
       </c>
       <c r="L19">
-        <v>42813081.771589927</v>
+        <v>42813081.77158993</v>
       </c>
       <c r="M19" t="s">
         <v>292</v>
@@ -2169,7 +2131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -2186,7 +2148,7 @@
         <v>209</v>
       </c>
       <c r="F20">
-        <v>80.959999999999994</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="G20" t="s">
         <v>215</v>
@@ -2216,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -2260,7 +2222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -2277,7 +2239,7 @@
         <v>209</v>
       </c>
       <c r="F22">
-        <v>0.36799999999999999</v>
+        <v>0.368</v>
       </c>
       <c r="G22" t="s">
         <v>215</v>
@@ -2307,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -2324,7 +2286,7 @@
         <v>209</v>
       </c>
       <c r="F23">
-        <v>10.119999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="G23" t="s">
         <v>215</v>
@@ -2354,7 +2316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -2398,7 +2360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -2427,7 +2389,7 @@
         <v>273</v>
       </c>
       <c r="L25">
-        <v>2991452173.1999998</v>
+        <v>2991452173.2</v>
       </c>
       <c r="M25" t="s">
         <v>291</v>
@@ -2442,7 +2404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -2486,7 +2448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -2530,7 +2492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2574,7 +2536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -2591,7 +2553,7 @@
         <v>207</v>
       </c>
       <c r="F29">
-        <v>34190.620000000003</v>
+        <v>34190.62</v>
       </c>
       <c r="G29" t="s">
         <v>216</v>
@@ -2621,7 +2583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -2638,7 +2600,7 @@
         <v>207</v>
       </c>
       <c r="F30">
-        <v>38555.379999999997</v>
+        <v>38555.38</v>
       </c>
       <c r="G30" t="s">
         <v>216</v>
@@ -2668,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -2712,7 +2674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -2741,7 +2703,7 @@
         <v>277</v>
       </c>
       <c r="L32">
-        <v>57828505.600000001</v>
+        <v>57828505.6</v>
       </c>
       <c r="M32" t="s">
         <v>292</v>
@@ -2756,7 +2718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -2773,7 +2735,7 @@
         <v>205</v>
       </c>
       <c r="F33">
-        <v>21662.098880000001</v>
+        <v>21662.09888</v>
       </c>
       <c r="H33" t="s">
         <v>228</v>
@@ -2785,7 +2747,7 @@
         <v>272</v>
       </c>
       <c r="L33">
-        <v>21662098.879999999</v>
+        <v>21662098.88</v>
       </c>
       <c r="M33" t="s">
         <v>291</v>
@@ -2800,7 +2762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -2817,7 +2779,7 @@
         <v>205</v>
       </c>
       <c r="F34">
-        <v>385327.79739999998</v>
+        <v>385327.7974</v>
       </c>
       <c r="H34" t="s">
         <v>228</v>
@@ -2829,7 +2791,7 @@
         <v>272</v>
       </c>
       <c r="L34">
-        <v>385327797.39999998</v>
+        <v>385327797.4</v>
       </c>
       <c r="M34" t="s">
         <v>291</v>
@@ -2844,7 +2806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -2888,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -2905,7 +2867,7 @@
         <v>205</v>
       </c>
       <c r="F36">
-        <v>892229.95044000004</v>
+        <v>892229.95044</v>
       </c>
       <c r="H36" t="s">
         <v>228</v>
@@ -2917,7 +2879,7 @@
         <v>272</v>
       </c>
       <c r="L36">
-        <v>892229950.44000006</v>
+        <v>892229950.4400001</v>
       </c>
       <c r="M36" t="s">
         <v>291</v>
@@ -2932,7 +2894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -2949,7 +2911,7 @@
         <v>205</v>
       </c>
       <c r="F37">
-        <v>10018.117899999999</v>
+        <v>10018.1179</v>
       </c>
       <c r="H37" t="s">
         <v>228</v>
@@ -2976,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>52</v>
       </c>
@@ -2993,7 +2955,7 @@
         <v>205</v>
       </c>
       <c r="F38">
-        <v>142393.17415000001</v>
+        <v>142393.17415</v>
       </c>
       <c r="H38" t="s">
         <v>228</v>
@@ -3005,7 +2967,7 @@
         <v>272</v>
       </c>
       <c r="L38">
-        <v>142393174.15000001</v>
+        <v>142393174.15</v>
       </c>
       <c r="M38" t="s">
         <v>291</v>
@@ -3020,7 +2982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -3064,7 +3026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -3108,7 +3070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -3152,7 +3114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>56</v>
       </c>
@@ -3196,7 +3158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>57</v>
       </c>
@@ -3240,7 +3202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -3284,7 +3246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -3328,7 +3290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -3372,7 +3334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -3416,7 +3378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>62</v>
       </c>
@@ -3460,7 +3422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16">
       <c r="A49" t="s">
         <v>63</v>
       </c>
@@ -3504,7 +3466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16">
       <c r="A50" t="s">
         <v>64</v>
       </c>
@@ -3548,7 +3510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16">
       <c r="A51" t="s">
         <v>65</v>
       </c>
@@ -3592,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -3636,7 +3598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16">
       <c r="A53" t="s">
         <v>67</v>
       </c>
@@ -3680,7 +3642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -3724,7 +3686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16">
       <c r="A55" t="s">
         <v>69</v>
       </c>
@@ -3753,7 +3715,7 @@
         <v>275</v>
       </c>
       <c r="L55">
-        <v>55697075.445267648</v>
+        <v>55697075.44526765</v>
       </c>
       <c r="M55" t="s">
         <v>292</v>
@@ -3768,7 +3730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -3797,7 +3759,7 @@
         <v>275</v>
       </c>
       <c r="L56">
-        <v>63343396.799999997</v>
+        <v>63343396.8</v>
       </c>
       <c r="M56" t="s">
         <v>291</v>
@@ -3812,7 +3774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16">
       <c r="A57" t="s">
         <v>71</v>
       </c>
@@ -3841,7 +3803,7 @@
         <v>275</v>
       </c>
       <c r="L57">
-        <v>8333350.1134884004</v>
+        <v>8333350.1134884</v>
       </c>
       <c r="M57" t="s">
         <v>292</v>
@@ -3856,7 +3818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -3885,7 +3847,7 @@
         <v>275</v>
       </c>
       <c r="L58">
-        <v>36595602.209830672</v>
+        <v>36595602.20983067</v>
       </c>
       <c r="M58" t="s">
         <v>292</v>
@@ -3900,7 +3862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16">
       <c r="A59" t="s">
         <v>73</v>
       </c>
@@ -3944,7 +3906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -3991,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16">
       <c r="A61" t="s">
         <v>75</v>
       </c>
@@ -4038,7 +4000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16">
       <c r="A62" t="s">
         <v>76</v>
       </c>
@@ -4082,7 +4044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -4129,7 +4091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16">
       <c r="A64" t="s">
         <v>78</v>
       </c>
@@ -4173,7 +4135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16">
       <c r="A65" t="s">
         <v>79</v>
       </c>
@@ -4217,7 +4179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16">
       <c r="A66" t="s">
         <v>80</v>
       </c>
@@ -4261,7 +4223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16">
       <c r="A67" t="s">
         <v>81</v>
       </c>
@@ -4305,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16">
       <c r="A68" t="s">
         <v>82</v>
       </c>
@@ -4349,7 +4311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -4393,7 +4355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16">
       <c r="A70" t="s">
         <v>84</v>
       </c>
@@ -4437,7 +4399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16">
       <c r="A71" t="s">
         <v>85</v>
       </c>
@@ -4481,7 +4443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16">
       <c r="A72" t="s">
         <v>86</v>
       </c>
@@ -4525,7 +4487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16">
       <c r="A73" t="s">
         <v>87</v>
       </c>
@@ -4569,7 +4531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16">
       <c r="A74" t="s">
         <v>88</v>
       </c>
@@ -4613,7 +4575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16">
       <c r="A75" t="s">
         <v>89</v>
       </c>
@@ -4657,7 +4619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16">
       <c r="A76" t="s">
         <v>90</v>
       </c>
@@ -4701,7 +4663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16">
       <c r="A77" t="s">
         <v>91</v>
       </c>
@@ -4745,7 +4707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16">
       <c r="A78" t="s">
         <v>92</v>
       </c>
@@ -4789,7 +4751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16">
       <c r="A79" t="s">
         <v>93</v>
       </c>
@@ -4833,7 +4795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -4877,7 +4839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16">
       <c r="A81" t="s">
         <v>95</v>
       </c>
@@ -4921,7 +4883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16">
       <c r="A82" t="s">
         <v>96</v>
       </c>
@@ -4965,7 +4927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16">
       <c r="A83" t="s">
         <v>97</v>
       </c>
@@ -5009,7 +4971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -5038,7 +5000,7 @@
         <v>273</v>
       </c>
       <c r="L84">
-        <v>593954510.39999998</v>
+        <v>593954510.4</v>
       </c>
       <c r="M84" t="s">
         <v>291</v>
@@ -5053,7 +5015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16">
       <c r="A85" t="s">
         <v>99</v>
       </c>
@@ -5097,7 +5059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16">
       <c r="A86" t="s">
         <v>100</v>
       </c>
@@ -5141,7 +5103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16">
       <c r="A87" t="s">
         <v>101</v>
       </c>
@@ -5185,7 +5147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16">
       <c r="A88" t="s">
         <v>102</v>
       </c>
@@ -5229,7 +5191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16">
       <c r="A89" t="s">
         <v>103</v>
       </c>
@@ -5258,7 +5220,7 @@
         <v>273</v>
       </c>
       <c r="L89">
-        <v>477755733.60000002</v>
+        <v>477755733.6</v>
       </c>
       <c r="M89" t="s">
         <v>291</v>
@@ -5273,7 +5235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16">
       <c r="A90" t="s">
         <v>104</v>
       </c>
@@ -5317,7 +5279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16">
       <c r="A91" t="s">
         <v>105</v>
       </c>
@@ -5334,7 +5296,7 @@
         <v>205</v>
       </c>
       <c r="F91">
-        <v>929608.63697705802</v>
+        <v>929608.636977058</v>
       </c>
       <c r="G91" t="s">
         <v>218</v>
@@ -5349,7 +5311,7 @@
         <v>283</v>
       </c>
       <c r="L91">
-        <v>929608636.97705805</v>
+        <v>929608636.9770581</v>
       </c>
       <c r="M91" t="s">
         <v>291</v>
@@ -5364,7 +5326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16">
       <c r="A92" t="s">
         <v>106</v>
       </c>
@@ -5381,7 +5343,7 @@
         <v>205</v>
       </c>
       <c r="F92">
-        <v>365541.66666666669</v>
+        <v>365541.6666666667</v>
       </c>
       <c r="G92" t="s">
         <v>219</v>
@@ -5396,7 +5358,7 @@
         <v>283</v>
       </c>
       <c r="L92">
-        <v>365541666.66666669</v>
+        <v>365541666.6666667</v>
       </c>
       <c r="M92" t="s">
         <v>291</v>
@@ -5411,7 +5373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16">
       <c r="A93" t="s">
         <v>107</v>
       </c>
@@ -5425,7 +5387,7 @@
         <v>205</v>
       </c>
       <c r="F93">
-        <v>36282.051282051281</v>
+        <v>36282.05128205128</v>
       </c>
       <c r="G93" t="s">
         <v>219</v>
@@ -5455,7 +5417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16">
       <c r="A94" t="s">
         <v>108</v>
       </c>
@@ -5472,7 +5434,7 @@
         <v>205</v>
       </c>
       <c r="F94">
-        <v>21012.145748987859</v>
+        <v>21012.14574898786</v>
       </c>
       <c r="G94" t="s">
         <v>218</v>
@@ -5487,7 +5449,7 @@
         <v>283</v>
       </c>
       <c r="L94">
-        <v>21012145.748987861</v>
+        <v>21012145.74898786</v>
       </c>
       <c r="M94" t="s">
         <v>291</v>
@@ -5502,7 +5464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16">
       <c r="A95" t="s">
         <v>109</v>
       </c>
@@ -5519,7 +5481,7 @@
         <v>205</v>
       </c>
       <c r="F95">
-        <v>22737.896494156928</v>
+        <v>22737.89649415693</v>
       </c>
       <c r="G95" t="s">
         <v>218</v>
@@ -5534,7 +5496,7 @@
         <v>283</v>
       </c>
       <c r="L95">
-        <v>22737896.494156931</v>
+        <v>22737896.49415693</v>
       </c>
       <c r="M95" t="s">
         <v>291</v>
@@ -5549,7 +5511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16">
       <c r="A96" t="s">
         <v>110</v>
       </c>
@@ -5566,7 +5528,7 @@
         <v>205</v>
       </c>
       <c r="F96">
-        <v>27653.229039999998</v>
+        <v>27653.22904</v>
       </c>
       <c r="H96" t="s">
         <v>241</v>
@@ -5578,7 +5540,7 @@
         <v>272</v>
       </c>
       <c r="L96">
-        <v>27653229.039999999</v>
+        <v>27653229.04</v>
       </c>
       <c r="M96" t="s">
         <v>291</v>
@@ -5593,7 +5555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16">
       <c r="A97" t="s">
         <v>111</v>
       </c>
@@ -5637,7 +5599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16">
       <c r="A98" t="s">
         <v>112</v>
       </c>
@@ -5666,7 +5628,7 @@
         <v>272</v>
       </c>
       <c r="L98">
-        <v>308614730.82099998</v>
+        <v>308614730.821</v>
       </c>
       <c r="M98" t="s">
         <v>291</v>
@@ -5681,7 +5643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16">
       <c r="A99" t="s">
         <v>113</v>
       </c>
@@ -5710,7 +5672,7 @@
         <v>272</v>
       </c>
       <c r="L99">
-        <v>3808984.2820627298</v>
+        <v>3808984.28206273</v>
       </c>
       <c r="M99" t="s">
         <v>291</v>
@@ -5725,7 +5687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16">
       <c r="A100" t="s">
         <v>114</v>
       </c>
@@ -5769,7 +5731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16">
       <c r="A101" t="s">
         <v>115</v>
       </c>
@@ -5786,7 +5748,7 @@
         <v>205</v>
       </c>
       <c r="F101">
-        <v>5437.6350000000002</v>
+        <v>5437.635</v>
       </c>
       <c r="H101" t="s">
         <v>241</v>
@@ -5813,7 +5775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16">
       <c r="A102" t="s">
         <v>116</v>
       </c>
@@ -5842,7 +5804,7 @@
         <v>272</v>
       </c>
       <c r="L102">
-        <v>229891868.94999999</v>
+        <v>229891868.95</v>
       </c>
       <c r="M102" t="s">
         <v>291</v>
@@ -5857,7 +5819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16">
       <c r="A103" t="s">
         <v>117</v>
       </c>
@@ -5901,7 +5863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16">
       <c r="A104" t="s">
         <v>118</v>
       </c>
@@ -5918,7 +5880,7 @@
         <v>213</v>
       </c>
       <c r="F104">
-        <v>4761600.0999999996</v>
+        <v>4761600.1</v>
       </c>
       <c r="H104" t="s">
         <v>242</v>
@@ -5945,7 +5907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16">
       <c r="A105" t="s">
         <v>119</v>
       </c>
@@ -5962,7 +5924,7 @@
         <v>205</v>
       </c>
       <c r="F105">
-        <v>56414.676500000001</v>
+        <v>56414.6765</v>
       </c>
       <c r="H105" t="s">
         <v>242</v>
@@ -5989,7 +5951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16">
       <c r="A106" t="s">
         <v>120</v>
       </c>
@@ -6033,7 +5995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16">
       <c r="A107" t="s">
         <v>121</v>
       </c>
@@ -6062,7 +6024,7 @@
         <v>284</v>
       </c>
       <c r="L107">
-        <v>3914535.1519999998</v>
+        <v>3914535.152</v>
       </c>
       <c r="M107" t="s">
         <v>292</v>
@@ -6077,7 +6039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16">
       <c r="A108" t="s">
         <v>122</v>
       </c>
@@ -6121,7 +6083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16">
       <c r="A109" t="s">
         <v>123</v>
       </c>
@@ -6150,7 +6112,7 @@
         <v>284</v>
       </c>
       <c r="L109">
-        <v>710263.52240000002</v>
+        <v>710263.5224</v>
       </c>
       <c r="M109" t="s">
         <v>292</v>
@@ -6165,7 +6127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16">
       <c r="A110" t="s">
         <v>124</v>
       </c>
@@ -6182,7 +6144,7 @@
         <v>205</v>
       </c>
       <c r="F110">
-        <v>23524.436671511001</v>
+        <v>23524.436671511</v>
       </c>
       <c r="I110" t="s">
         <v>250</v>
@@ -6194,7 +6156,7 @@
         <v>272</v>
       </c>
       <c r="L110">
-        <v>23524436.671510998</v>
+        <v>23524436.671511</v>
       </c>
       <c r="M110" t="s">
         <v>291</v>
@@ -6209,7 +6171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16">
       <c r="A111" t="s">
         <v>125</v>
       </c>
@@ -6226,7 +6188,7 @@
         <v>205</v>
       </c>
       <c r="F111">
-        <v>623021.86861600005</v>
+        <v>623021.8686160001</v>
       </c>
       <c r="I111" t="s">
         <v>250</v>
@@ -6238,7 +6200,7 @@
         <v>272</v>
       </c>
       <c r="L111">
-        <v>623021868.61600006</v>
+        <v>623021868.6160001</v>
       </c>
       <c r="M111" t="s">
         <v>291</v>
@@ -6253,7 +6215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16">
       <c r="A112" t="s">
         <v>126</v>
       </c>
@@ -6270,7 +6232,7 @@
         <v>205</v>
       </c>
       <c r="F112">
-        <v>91025.482259915196</v>
+        <v>91025.4822599152</v>
       </c>
       <c r="I112" t="s">
         <v>250</v>
@@ -6282,7 +6244,7 @@
         <v>272</v>
       </c>
       <c r="L112">
-        <v>91025482.259915203</v>
+        <v>91025482.2599152</v>
       </c>
       <c r="M112" t="s">
         <v>291</v>
@@ -6297,7 +6259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16">
       <c r="A113" t="s">
         <v>127</v>
       </c>
@@ -6341,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16">
       <c r="A114" t="s">
         <v>128</v>
       </c>
@@ -6385,7 +6347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16">
       <c r="A115" t="s">
         <v>129</v>
       </c>
@@ -6429,7 +6391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16">
       <c r="A116" t="s">
         <v>130</v>
       </c>
@@ -6446,7 +6408,7 @@
         <v>205</v>
       </c>
       <c r="F116">
-        <v>6336.0580702999996</v>
+        <v>6336.0580703</v>
       </c>
       <c r="I116" t="s">
         <v>250</v>
@@ -6458,7 +6420,7 @@
         <v>272</v>
       </c>
       <c r="L116">
-        <v>6336058.0702999998</v>
+        <v>6336058.0703</v>
       </c>
       <c r="M116" t="s">
         <v>291</v>
@@ -6473,7 +6435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16">
       <c r="A117" t="s">
         <v>131</v>
       </c>
@@ -6490,7 +6452,7 @@
         <v>213</v>
       </c>
       <c r="F117">
-        <v>42378137.859999999</v>
+        <v>42378137.86</v>
       </c>
       <c r="H117" t="s">
         <v>243</v>
@@ -6502,7 +6464,7 @@
         <v>284</v>
       </c>
       <c r="L117">
-        <v>1521587039.8633001</v>
+        <v>1521587039.8633</v>
       </c>
       <c r="M117" t="s">
         <v>292</v>
@@ -6517,7 +6479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16">
       <c r="A118" t="s">
         <v>132</v>
       </c>
@@ -6561,7 +6523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16">
       <c r="A119" t="s">
         <v>133</v>
       </c>
@@ -6578,7 +6540,7 @@
         <v>213</v>
       </c>
       <c r="F119">
-        <v>1147190.1000000001</v>
+        <v>1147190.1</v>
       </c>
       <c r="H119" t="s">
         <v>243</v>
@@ -6605,7 +6567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16">
       <c r="A120" t="s">
         <v>134</v>
       </c>
@@ -6634,7 +6596,7 @@
         <v>284</v>
       </c>
       <c r="L120">
-        <v>84441809.056336001</v>
+        <v>84441809.056336</v>
       </c>
       <c r="M120" t="s">
         <v>292</v>
@@ -6649,7 +6611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16">
       <c r="A121" t="s">
         <v>135</v>
       </c>
@@ -6693,7 +6655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16">
       <c r="A122" t="s">
         <v>136</v>
       </c>
@@ -6710,7 +6672,7 @@
         <v>205</v>
       </c>
       <c r="F122">
-        <v>121071.91538799999</v>
+        <v>121071.915388</v>
       </c>
       <c r="H122" t="s">
         <v>244</v>
@@ -6737,7 +6699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16">
       <c r="A123" t="s">
         <v>137</v>
       </c>
@@ -6754,7 +6716,7 @@
         <v>205</v>
       </c>
       <c r="F123">
-        <v>1361713.8583120001</v>
+        <v>1361713.858312</v>
       </c>
       <c r="H123" t="s">
         <v>244</v>
@@ -6781,7 +6743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16">
       <c r="A124" t="s">
         <v>138</v>
       </c>
@@ -6798,7 +6760,7 @@
         <v>205</v>
       </c>
       <c r="F124">
-        <v>5528.5667000000003</v>
+        <v>5528.5667</v>
       </c>
       <c r="H124" t="s">
         <v>244</v>
@@ -6810,7 +6772,7 @@
         <v>272</v>
       </c>
       <c r="L124">
-        <v>5528566.7000000002</v>
+        <v>5528566.7</v>
       </c>
       <c r="M124" t="s">
         <v>291</v>
@@ -6825,7 +6787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16">
       <c r="A125" t="s">
         <v>139</v>
       </c>
@@ -6842,7 +6804,7 @@
         <v>205</v>
       </c>
       <c r="F125">
-        <v>1274584.3415999999</v>
+        <v>1274584.3416</v>
       </c>
       <c r="H125" t="s">
         <v>244</v>
@@ -6854,7 +6816,7 @@
         <v>272</v>
       </c>
       <c r="L125">
-        <v>1274584341.5999999</v>
+        <v>1274584341.6</v>
       </c>
       <c r="M125" t="s">
         <v>291</v>
@@ -6869,7 +6831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16">
       <c r="A126" t="s">
         <v>140</v>
       </c>
@@ -6913,7 +6875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16">
       <c r="A127" t="s">
         <v>141</v>
       </c>
@@ -6930,7 +6892,7 @@
         <v>205</v>
       </c>
       <c r="F127">
-        <v>80313.185800000007</v>
+        <v>80313.18580000001</v>
       </c>
       <c r="H127" t="s">
         <v>244</v>
@@ -6942,7 +6904,7 @@
         <v>272</v>
       </c>
       <c r="L127">
-        <v>80313185.800000012</v>
+        <v>80313185.80000001</v>
       </c>
       <c r="M127" t="s">
         <v>291</v>
@@ -6957,7 +6919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16">
       <c r="A128" t="s">
         <v>142</v>
       </c>
@@ -7001,7 +6963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16">
       <c r="A129" t="s">
         <v>143</v>
       </c>
@@ -7030,7 +6992,7 @@
         <v>285</v>
       </c>
       <c r="L129">
-        <v>893875119.69060004</v>
+        <v>893875119.6906</v>
       </c>
       <c r="M129" t="s">
         <v>291</v>
@@ -7045,7 +7007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16">
       <c r="A130" t="s">
         <v>144</v>
       </c>
@@ -7089,7 +7051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -7118,7 +7080,7 @@
         <v>285</v>
       </c>
       <c r="L131">
-        <v>14655632.810559981</v>
+        <v>14655632.81055998</v>
       </c>
       <c r="M131" t="s">
         <v>292</v>
@@ -7133,7 +7095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16">
       <c r="A132" t="s">
         <v>146</v>
       </c>
@@ -7177,7 +7139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16">
       <c r="A133" t="s">
         <v>147</v>
       </c>
@@ -7221,7 +7183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16">
       <c r="A134" t="s">
         <v>148</v>
       </c>
@@ -7265,7 +7227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16">
       <c r="A135" t="s">
         <v>149</v>
       </c>
@@ -7309,7 +7271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16">
       <c r="A136" t="s">
         <v>150</v>
       </c>
@@ -7353,7 +7315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16">
       <c r="A137" t="s">
         <v>151</v>
       </c>
@@ -7397,7 +7359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16">
       <c r="A138" t="s">
         <v>152</v>
       </c>
@@ -7441,7 +7403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16">
       <c r="A139" t="s">
         <v>153</v>
       </c>
@@ -7485,7 +7447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16">
       <c r="A140" t="s">
         <v>154</v>
       </c>
@@ -7514,7 +7476,7 @@
         <v>288</v>
       </c>
       <c r="L140">
-        <v>193225046.40000001</v>
+        <v>193225046.4</v>
       </c>
       <c r="M140" t="s">
         <v>291</v>
@@ -7529,7 +7491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16">
       <c r="A141" t="s">
         <v>155</v>
       </c>
@@ -7576,7 +7538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16">
       <c r="A142" t="s">
         <v>156</v>
       </c>
@@ -7620,7 +7582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -7667,7 +7629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16">
       <c r="A144" t="s">
         <v>158</v>
       </c>
@@ -7711,7 +7673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16">
       <c r="A145" t="s">
         <v>159</v>
       </c>
@@ -7758,7 +7720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16">
       <c r="A146" t="s">
         <v>160</v>
       </c>
@@ -7805,7 +7767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16">
       <c r="A147" t="s">
         <v>161</v>
       </c>
@@ -7849,7 +7811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16">
       <c r="A148" t="s">
         <v>162</v>
       </c>
@@ -7893,7 +7855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16">
       <c r="A149" t="s">
         <v>163</v>
       </c>
@@ -7937,7 +7899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16">
       <c r="A150" t="s">
         <v>164</v>
       </c>
@@ -7954,7 +7916,7 @@
         <v>205</v>
       </c>
       <c r="F150">
-        <v>159325.59885000001</v>
+        <v>159325.59885</v>
       </c>
       <c r="I150" t="s">
         <v>253</v>
@@ -7966,7 +7928,7 @@
         <v>289</v>
       </c>
       <c r="L150">
-        <v>159325598.84999999</v>
+        <v>159325598.85</v>
       </c>
       <c r="M150" t="s">
         <v>291</v>
@@ -7981,7 +7943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16">
       <c r="A151" t="s">
         <v>165</v>
       </c>
@@ -8025,7 +7987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16">
       <c r="A152" t="s">
         <v>166</v>
       </c>
@@ -8042,7 +8004,7 @@
         <v>205</v>
       </c>
       <c r="F152">
-        <v>525946.69999999995</v>
+        <v>525946.7</v>
       </c>
       <c r="H152" t="s">
         <v>247</v>
@@ -8054,7 +8016,7 @@
         <v>290</v>
       </c>
       <c r="L152">
-        <v>525946699.99999988</v>
+        <v>525946699.9999999</v>
       </c>
       <c r="M152" t="s">
         <v>291</v>
@@ -8069,7 +8031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16">
       <c r="A153" t="s">
         <v>167</v>
       </c>
@@ -8113,7 +8075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16">
       <c r="A154" t="s">
         <v>168</v>
       </c>
@@ -8157,7 +8119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16">
       <c r="A155" t="s">
         <v>169</v>
       </c>
@@ -8201,7 +8163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16">
       <c r="A156" t="s">
         <v>170</v>
       </c>
@@ -8245,7 +8207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16">
       <c r="A157" t="s">
         <v>171</v>
       </c>
@@ -8289,7 +8251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16">
       <c r="A158" t="s">
         <v>172</v>
       </c>
@@ -8333,7 +8295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16">
       <c r="A159" t="s">
         <v>173</v>
       </c>
@@ -8377,7 +8339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16">
       <c r="A160" t="s">
         <v>174</v>
       </c>
@@ -8421,7 +8383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16">
       <c r="A161" t="s">
         <v>175</v>
       </c>
@@ -8466,13 +8428,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P161" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="GRP-14bfbb82"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>